--- a/input/reg_education.xlsx
+++ b/input/reg_education.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D85F0C01-C5F2-47EE-9788-DD0950B0F55D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06213481-F875-47C4-A649-318919CF0EDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -152,15 +152,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -216,12 +211,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2084,14 +2078,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="22.86328125" customWidth="1"/>
     <col min="2" max="2" width="13.265625" customWidth="1"/>
+    <col min="10" max="10" width="20.06640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>10</v>
       </c>
@@ -2134,12 +2129,8 @@
       <c r="N1" t="s">
         <v>28</v>
       </c>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -2183,7 +2174,7 @@
         <v>1.6080806168536667E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>40</v>
       </c>
@@ -2227,7 +2218,7 @@
         <v>-2.2350063256210682</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>34</v>
       </c>
@@ -2271,7 +2262,7 @@
         <v>5.1751452567861234E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -2315,7 +2306,7 @@
         <v>-9.0028535514479049E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -2359,7 +2350,7 @@
         <v>7.3753253703915014E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -2403,7 +2394,7 @@
         <v>-2.3582040298859908E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -2447,7 +2438,7 @@
         <v>-5.8122855107039101E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>39</v>
       </c>
@@ -2491,7 +2482,7 @@
         <v>-7.575077380311197E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -2535,7 +2526,7 @@
         <v>-6.9655217486060406E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -2579,7 +2570,7 @@
         <v>-6.8713031914267558E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -2623,7 +2614,7 @@
         <v>23.932897346374034</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -2666,22 +2657,6 @@
       <c r="N13">
         <v>29.51973160464496</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/input/reg_education.xlsx
+++ b/input/reg_education.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pineapple/IdeaProjects/ESPONmodels/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06213481-F875-47C4-A649-318919CF0EDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDE477F8-1D5B-0C4C-9B03-68300D726D84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="42">
   <si>
     <t>Description:</t>
   </si>
@@ -145,14 +145,17 @@
     <t>Year_transformed_</t>
   </si>
   <si>
-    <t>Dag_</t>
+    <t>Dag_Low</t>
+  </si>
+  <si>
+    <t>Dag_Medium</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -165,6 +168,11 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -211,11 +219,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -551,9 +560,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -561,7 +570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -569,7 +578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -577,7 +586,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -585,7 +594,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -593,7 +602,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
@@ -609,12 +618,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M12"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.53125" customWidth="1"/>
+    <col min="1" max="1" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>10</v>
       </c>
@@ -655,7 +664,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -696,7 +705,7 @@
         <v>-1.3359609148359927E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -737,7 +746,7 @@
         <v>-7.2277855207773675E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -778,7 +787,7 @@
         <v>1.6684656836818469E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>29</v>
       </c>
@@ -819,7 +828,7 @@
         <v>-2.0099407435794974E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -860,7 +869,7 @@
         <v>-1.3199881490738653E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -901,7 +910,7 @@
         <v>-2.3492937485129518E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>32</v>
       </c>
@@ -942,7 +951,7 @@
         <v>-1.2950633218948662E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -983,7 +992,7 @@
         <v>-3.8626841323309791E-4</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -1024,7 +1033,7 @@
         <v>5.0088271207424572E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -1065,7 +1074,7 @@
         <v>-4.2876388871140479E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -1114,12 +1123,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:R17"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.265625" customWidth="1"/>
+    <col min="1" max="1" width="25.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>10</v>
       </c>
@@ -1175,7 +1184,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1231,7 +1240,7 @@
         <v>-3.4126254766013507E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1287,7 +1296,7 @@
         <v>-5.1539753384105644E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1343,7 +1352,7 @@
         <v>9.4505907422043236E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -1399,7 +1408,7 @@
         <v>1.8663959943310813E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -1455,7 +1464,7 @@
         <v>-9.4429115965450096E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -1511,7 +1520,7 @@
         <v>-2.3590724324437824E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -1567,7 +1576,7 @@
         <v>6.5198187941972589E-4</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -1623,7 +1632,7 @@
         <v>9.0076524435265398E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -1679,7 +1688,7 @@
         <v>4.6190788354832949E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -1735,7 +1744,7 @@
         <v>6.5693578990619669E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>31</v>
       </c>
@@ -1791,7 +1800,7 @@
         <v>6.7678432814534655E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -1847,7 +1856,7 @@
         <v>1.0544468102314164E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -1903,7 +1912,7 @@
         <v>-8.0760920427191962E-5</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -1959,7 +1968,7 @@
         <v>-4.1003434434182043E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -2015,7 +2024,7 @@
         <v>-9.8739195725258272E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -2078,583 +2087,669 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:N13"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:O14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.86328125" customWidth="1"/>
-    <col min="2" max="2" width="13.265625" customWidth="1"/>
-    <col min="10" max="10" width="20.06640625" customWidth="1"/>
+    <col min="1" max="1" width="22.83203125" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J1" t="s">
-        <v>39</v>
-      </c>
-      <c r="K1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" t="s">
+      <c r="M1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="O1" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="4">
         <v>-0.19475685081635269</v>
       </c>
       <c r="C2">
         <v>1.3409123708389424E-2</v>
       </c>
       <c r="D2">
+        <v>2.1576896824549521E-5</v>
+      </c>
+      <c r="E2">
+        <v>2.9127905724396839E-3</v>
+      </c>
+      <c r="F2">
+        <v>7.590689442179921E-4</v>
+      </c>
+      <c r="G2">
+        <v>1.7422960648879335E-4</v>
+      </c>
+      <c r="H2">
+        <v>7.6344826969746251E-4</v>
+      </c>
+      <c r="I2">
+        <v>9.843075038158493E-5</v>
+      </c>
+      <c r="J2">
+        <v>1.4115207494679497E-4</v>
+      </c>
+      <c r="K2">
+        <v>-2.8238345284652662E-3</v>
+      </c>
+      <c r="L2">
         <v>-9.2143051036281342E-4</v>
-      </c>
-      <c r="E2">
-        <v>2.1576896824549521E-5</v>
-      </c>
-      <c r="F2">
-        <v>2.9127905724396839E-3</v>
-      </c>
-      <c r="G2">
-        <v>7.590689442179921E-4</v>
-      </c>
-      <c r="H2">
-        <v>1.7422960648879335E-4</v>
-      </c>
-      <c r="I2">
-        <v>7.6344826969746251E-4</v>
-      </c>
-      <c r="J2">
-        <v>9.843075038158493E-5</v>
-      </c>
-      <c r="K2">
-        <v>1.4115207494679497E-4</v>
-      </c>
-      <c r="L2">
-        <v>-2.8238345284652662E-3</v>
       </c>
       <c r="M2">
         <v>-6.5626185107372191E-4</v>
       </c>
       <c r="N2">
+        <v>-9.0485190649986424E-4</v>
+      </c>
+      <c r="O2">
         <v>1.6080806168536667E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="4">
+        <v>-5.5563641405503239E-2</v>
+      </c>
+      <c r="C3">
+        <v>2.1576896824549521E-5</v>
+      </c>
+      <c r="D3">
+        <v>9.4364827372930198E-5</v>
+      </c>
+      <c r="E3">
+        <v>-1.7608613444121315E-4</v>
+      </c>
+      <c r="F3">
+        <v>1.3714411702458627E-4</v>
+      </c>
+      <c r="G3">
+        <v>-1.6527567791614628E-6</v>
+      </c>
+      <c r="H3">
+        <v>-9.1313247325957442E-6</v>
+      </c>
+      <c r="I3">
+        <v>-7.7886325005704742E-6</v>
+      </c>
+      <c r="J3">
+        <v>-1.6533215482391738E-4</v>
+      </c>
+      <c r="K3">
+        <v>-1.4305423316045458E-4</v>
+      </c>
+      <c r="L3">
+        <v>-4.069997414187055E-3</v>
+      </c>
+      <c r="M3">
+        <v>4.3427464948995548E-2</v>
+      </c>
+      <c r="N3">
+        <v>-4.4294521495035696E-3</v>
+      </c>
+      <c r="O3">
+        <v>5.1751452567861234E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="4">
+        <v>-0.60866789995718118</v>
+      </c>
+      <c r="C4">
+        <v>2.9127905724396839E-3</v>
+      </c>
+      <c r="D4">
+        <v>-1.7608613444121315E-4</v>
+      </c>
+      <c r="E4">
+        <v>2.9927155670560233E-2</v>
+      </c>
+      <c r="F4">
+        <v>1.6379728915963614E-2</v>
+      </c>
+      <c r="G4">
+        <v>1.5504687985643029E-2</v>
+      </c>
+      <c r="H4">
+        <v>1.6277254518985727E-2</v>
+      </c>
+      <c r="I4">
+        <v>5.0716817343063368E-5</v>
+      </c>
+      <c r="J4">
+        <v>1.5455314641815753E-3</v>
+      </c>
+      <c r="K4">
+        <v>4.0685488155021475E-3</v>
+      </c>
+      <c r="L4">
+        <v>6.810199211806367E-3</v>
+      </c>
+      <c r="M4">
+        <v>-8.456836762273226E-2</v>
+      </c>
+      <c r="N4">
+        <v>7.2602172131255079E-3</v>
+      </c>
+      <c r="O4">
+        <v>-9.0028535514479049E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="4">
+        <v>-0.70324366588634069</v>
+      </c>
+      <c r="C5">
+        <v>7.590689442179921E-4</v>
+      </c>
+      <c r="D5">
+        <v>1.3714411702458627E-4</v>
+      </c>
+      <c r="E5">
+        <v>1.6379728915963614E-2</v>
+      </c>
+      <c r="F5">
+        <v>4.4022227139688515E-2</v>
+      </c>
+      <c r="G5">
+        <v>1.5621390335502134E-2</v>
+      </c>
+      <c r="H5">
+        <v>1.5972370954907458E-2</v>
+      </c>
+      <c r="I5">
+        <v>5.5134637278203493E-5</v>
+      </c>
+      <c r="J5">
+        <v>-6.7291293666023062E-4</v>
+      </c>
+      <c r="K5">
+        <v>7.3454735056977406E-3</v>
+      </c>
+      <c r="L5">
+        <v>-5.8090593335331821E-3</v>
+      </c>
+      <c r="M5">
+        <v>4.2720539798672852E-2</v>
+      </c>
+      <c r="N5">
+        <v>-7.0623214131569807E-3</v>
+      </c>
+      <c r="O5">
+        <v>7.3753253703915014E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.42000823658457415</v>
+      </c>
+      <c r="C6">
+        <v>1.7422960648879335E-4</v>
+      </c>
+      <c r="D6">
+        <v>-1.6527567791614628E-6</v>
+      </c>
+      <c r="E6">
+        <v>1.5504687985643029E-2</v>
+      </c>
+      <c r="F6">
+        <v>1.5621390335502134E-2</v>
+      </c>
+      <c r="G6">
+        <v>2.9378407483991294E-2</v>
+      </c>
+      <c r="H6">
+        <v>1.600243822879166E-2</v>
+      </c>
+      <c r="I6">
+        <v>-3.1583697777708814E-4</v>
+      </c>
+      <c r="J6">
+        <v>-3.0196271770003126E-4</v>
+      </c>
+      <c r="K6">
+        <v>2.5851565590439807E-3</v>
+      </c>
+      <c r="L6">
+        <v>-1.646121953855495E-4</v>
+      </c>
+      <c r="M6">
+        <v>-6.2211762017819958E-3</v>
+      </c>
+      <c r="N6">
+        <v>5.2558639108341455E-4</v>
+      </c>
+      <c r="O6">
+        <v>-2.3582040298859908E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="4">
+        <v>-0.12703292623853815</v>
+      </c>
+      <c r="C7">
+        <v>7.6344826969746251E-4</v>
+      </c>
+      <c r="D7">
+        <v>-9.1313247325957442E-6</v>
+      </c>
+      <c r="E7">
+        <v>1.6277254518985727E-2</v>
+      </c>
+      <c r="F7">
+        <v>1.5972370954907458E-2</v>
+      </c>
+      <c r="G7">
+        <v>1.600243822879166E-2</v>
+      </c>
+      <c r="H7">
+        <v>2.8194910082764035E-2</v>
+      </c>
+      <c r="I7">
+        <v>-2.9840957813235158E-4</v>
+      </c>
+      <c r="J7">
+        <v>-4.8818753259096542E-4</v>
+      </c>
+      <c r="K7">
+        <v>3.5584930954063519E-3</v>
+      </c>
+      <c r="L7">
+        <v>-2.3329930256899001E-4</v>
+      </c>
+      <c r="M7">
+        <v>-2.8467612703106659E-3</v>
+      </c>
+      <c r="N7">
+        <v>-3.8159618061404423E-5</v>
+      </c>
+      <c r="O7">
+        <v>-5.8122855107039101E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="4">
+        <v>-6.0248291948669666E-2</v>
+      </c>
+      <c r="C8">
+        <v>9.843075038158493E-5</v>
+      </c>
+      <c r="D8">
+        <v>-7.7886325005704742E-6</v>
+      </c>
+      <c r="E8">
+        <v>5.0716817343063368E-5</v>
+      </c>
+      <c r="F8">
+        <v>5.5134637278203493E-5</v>
+      </c>
+      <c r="G8">
+        <v>-3.1583697777708814E-4</v>
+      </c>
+      <c r="H8">
+        <v>-2.9840957813235158E-4</v>
+      </c>
+      <c r="I8">
+        <v>3.2266894705745256E-4</v>
+      </c>
+      <c r="J8">
+        <v>-1.5890851266514414E-3</v>
+      </c>
+      <c r="K8">
+        <v>-1.958201772702521E-3</v>
+      </c>
+      <c r="L8">
+        <v>2.8625146749584884E-4</v>
+      </c>
+      <c r="M8">
+        <v>-7.47212173378577E-3</v>
+      </c>
+      <c r="N8">
+        <v>3.0554670858922025E-4</v>
+      </c>
+      <c r="O8">
+        <v>-7.575077380311197E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="4">
+        <v>0.12532596776269456</v>
+      </c>
+      <c r="C9">
+        <v>1.4115207494679497E-4</v>
+      </c>
+      <c r="D9">
+        <v>-1.6533215482391738E-4</v>
+      </c>
+      <c r="E9">
+        <v>1.5455314641815753E-3</v>
+      </c>
+      <c r="F9">
+        <v>-6.7291293666023062E-4</v>
+      </c>
+      <c r="G9">
+        <v>-3.0196271770003126E-4</v>
+      </c>
+      <c r="H9">
+        <v>-4.8818753259096542E-4</v>
+      </c>
+      <c r="I9">
+        <v>-1.5890851266514414E-3</v>
+      </c>
+      <c r="J9">
+        <v>5.5472330377570732E-2</v>
+      </c>
+      <c r="K9">
+        <v>1.1412873152831213E-2</v>
+      </c>
+      <c r="L9">
+        <v>7.1361350383652711E-3</v>
+      </c>
+      <c r="M9">
+        <v>-5.6170545883362594E-2</v>
+      </c>
+      <c r="N9">
+        <v>7.7771235852395811E-3</v>
+      </c>
+      <c r="O9">
+        <v>-6.9655217486060406E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="4">
+        <v>1.2255113266353119</v>
+      </c>
+      <c r="C10">
+        <v>-2.8238345284652662E-3</v>
+      </c>
+      <c r="D10">
+        <v>-1.4305423316045458E-4</v>
+      </c>
+      <c r="E10">
+        <v>4.0685488155021475E-3</v>
+      </c>
+      <c r="F10">
+        <v>7.3454735056977406E-3</v>
+      </c>
+      <c r="G10">
+        <v>2.5851565590439807E-3</v>
+      </c>
+      <c r="H10">
+        <v>3.5584930954063519E-3</v>
+      </c>
+      <c r="I10">
+        <v>-1.958201772702521E-3</v>
+      </c>
+      <c r="J10">
+        <v>1.1412873152831213E-2</v>
+      </c>
+      <c r="K10">
+        <v>0.20402924290055638</v>
+      </c>
+      <c r="L10">
+        <v>6.0308263338469947E-3</v>
+      </c>
+      <c r="M10">
+        <v>-3.6383421002764219E-2</v>
+      </c>
+      <c r="N10">
+        <v>7.2281855639998293E-3</v>
+      </c>
+      <c r="O10">
+        <v>-6.8713031914267558E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B3">
+      <c r="B11" s="4">
         <v>3.0179729767868051</v>
       </c>
-      <c r="C3">
+      <c r="C11">
         <v>-9.2143051036281342E-4</v>
       </c>
-      <c r="D3">
+      <c r="D11">
+        <v>-4.069997414187055E-3</v>
+      </c>
+      <c r="E11">
+        <v>6.810199211806367E-3</v>
+      </c>
+      <c r="F11">
+        <v>-5.8090593335331821E-3</v>
+      </c>
+      <c r="G11">
+        <v>-1.646121953855495E-4</v>
+      </c>
+      <c r="H11">
+        <v>-2.3329930256899001E-4</v>
+      </c>
+      <c r="I11">
+        <v>2.8625146749584884E-4</v>
+      </c>
+      <c r="J11">
+        <v>7.1361350383652711E-3</v>
+      </c>
+      <c r="K11">
+        <v>6.0308263338469947E-3</v>
+      </c>
+      <c r="L11">
         <v>0.17666099300091753</v>
       </c>
-      <c r="E3">
-        <v>-4.069997414187055E-3</v>
-      </c>
-      <c r="F3">
-        <v>6.810199211806367E-3</v>
-      </c>
-      <c r="G3">
-        <v>-5.8090593335331821E-3</v>
-      </c>
-      <c r="H3">
-        <v>-1.646121953855495E-4</v>
-      </c>
-      <c r="I3">
-        <v>-2.3329930256899001E-4</v>
-      </c>
-      <c r="J3">
-        <v>2.8625146749584884E-4</v>
-      </c>
-      <c r="K3">
-        <v>7.1361350383652711E-3</v>
-      </c>
-      <c r="L3">
-        <v>6.0308263338469947E-3</v>
-      </c>
-      <c r="M3">
+      <c r="M11">
         <v>-1.8943742662098764</v>
       </c>
-      <c r="N3">
+      <c r="N11">
+        <v>0.19122788087141718</v>
+      </c>
+      <c r="O11">
         <v>-2.2350063256210682</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4">
-        <v>-5.5563641405503239E-2</v>
-      </c>
-      <c r="C4">
-        <v>2.1576896824549521E-5</v>
-      </c>
-      <c r="D4">
-        <v>-4.069997414187055E-3</v>
-      </c>
-      <c r="E4">
-        <v>9.4364827372930198E-5</v>
-      </c>
-      <c r="F4">
-        <v>-1.7608613444121315E-4</v>
-      </c>
-      <c r="G4">
-        <v>1.3714411702458627E-4</v>
-      </c>
-      <c r="H4">
-        <v>-1.6527567791614628E-6</v>
-      </c>
-      <c r="I4">
-        <v>-9.1313247325957442E-6</v>
-      </c>
-      <c r="J4">
-        <v>-7.7886325005704742E-6</v>
-      </c>
-      <c r="K4">
-        <v>-1.6533215482391738E-4</v>
-      </c>
-      <c r="L4">
-        <v>-1.4305423316045458E-4</v>
-      </c>
-      <c r="M4">
-        <v>4.3427464948995548E-2</v>
-      </c>
-      <c r="N4">
-        <v>5.1751452567861234E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5">
-        <v>-0.60866789995718118</v>
-      </c>
-      <c r="C5">
-        <v>2.9127905724396839E-3</v>
-      </c>
-      <c r="D5">
-        <v>6.810199211806367E-3</v>
-      </c>
-      <c r="E5">
-        <v>-1.7608613444121315E-4</v>
-      </c>
-      <c r="F5">
-        <v>2.9927155670560233E-2</v>
-      </c>
-      <c r="G5">
-        <v>1.6379728915963614E-2</v>
-      </c>
-      <c r="H5">
-        <v>1.5504687985643029E-2</v>
-      </c>
-      <c r="I5">
-        <v>1.6277254518985727E-2</v>
-      </c>
-      <c r="J5">
-        <v>5.0716817343063368E-5</v>
-      </c>
-      <c r="K5">
-        <v>1.5455314641815753E-3</v>
-      </c>
-      <c r="L5">
-        <v>4.0685488155021475E-3</v>
-      </c>
-      <c r="M5">
-        <v>-8.456836762273226E-2</v>
-      </c>
-      <c r="N5">
-        <v>-9.0028535514479049E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6">
-        <v>-0.70324366588634069</v>
-      </c>
-      <c r="C6">
-        <v>7.590689442179921E-4</v>
-      </c>
-      <c r="D6">
-        <v>-5.8090593335331821E-3</v>
-      </c>
-      <c r="E6">
-        <v>1.3714411702458627E-4</v>
-      </c>
-      <c r="F6">
-        <v>1.6379728915963614E-2</v>
-      </c>
-      <c r="G6">
-        <v>4.4022227139688515E-2</v>
-      </c>
-      <c r="H6">
-        <v>1.5621390335502134E-2</v>
-      </c>
-      <c r="I6">
-        <v>1.5972370954907458E-2</v>
-      </c>
-      <c r="J6">
-        <v>5.5134637278203493E-5</v>
-      </c>
-      <c r="K6">
-        <v>-6.7291293666023062E-4</v>
-      </c>
-      <c r="L6">
-        <v>7.3454735056977406E-3</v>
-      </c>
-      <c r="M6">
-        <v>4.2720539798672852E-2</v>
-      </c>
-      <c r="N6">
-        <v>7.3753253703915014E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7">
-        <v>0.42000823658457415</v>
-      </c>
-      <c r="C7">
-        <v>1.7422960648879335E-4</v>
-      </c>
-      <c r="D7">
-        <v>-1.646121953855495E-4</v>
-      </c>
-      <c r="E7">
-        <v>-1.6527567791614628E-6</v>
-      </c>
-      <c r="F7">
-        <v>1.5504687985643029E-2</v>
-      </c>
-      <c r="G7">
-        <v>1.5621390335502134E-2</v>
-      </c>
-      <c r="H7">
-        <v>2.9378407483991294E-2</v>
-      </c>
-      <c r="I7">
-        <v>1.600243822879166E-2</v>
-      </c>
-      <c r="J7">
-        <v>-3.1583697777708814E-4</v>
-      </c>
-      <c r="K7">
-        <v>-3.0196271770003126E-4</v>
-      </c>
-      <c r="L7">
-        <v>2.5851565590439807E-3</v>
-      </c>
-      <c r="M7">
-        <v>-6.2211762017819958E-3</v>
-      </c>
-      <c r="N7">
-        <v>-2.3582040298859908E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8">
-        <v>-0.12703292623853815</v>
-      </c>
-      <c r="C8">
-        <v>7.6344826969746251E-4</v>
-      </c>
-      <c r="D8">
-        <v>-2.3329930256899001E-4</v>
-      </c>
-      <c r="E8">
-        <v>-9.1313247325957442E-6</v>
-      </c>
-      <c r="F8">
-        <v>1.6277254518985727E-2</v>
-      </c>
-      <c r="G8">
-        <v>1.5972370954907458E-2</v>
-      </c>
-      <c r="H8">
-        <v>1.600243822879166E-2</v>
-      </c>
-      <c r="I8">
-        <v>2.8194910082764035E-2</v>
-      </c>
-      <c r="J8">
-        <v>-2.9840957813235158E-4</v>
-      </c>
-      <c r="K8">
-        <v>-4.8818753259096542E-4</v>
-      </c>
-      <c r="L8">
-        <v>3.5584930954063519E-3</v>
-      </c>
-      <c r="M8">
-        <v>-2.8467612703106659E-3</v>
-      </c>
-      <c r="N8">
-        <v>-5.8122855107039101E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9">
-        <v>-6.0248291948669666E-2</v>
-      </c>
-      <c r="C9">
-        <v>9.843075038158493E-5</v>
-      </c>
-      <c r="D9">
-        <v>2.8625146749584884E-4</v>
-      </c>
-      <c r="E9">
-        <v>-7.7886325005704742E-6</v>
-      </c>
-      <c r="F9">
-        <v>5.0716817343063368E-5</v>
-      </c>
-      <c r="G9">
-        <v>5.5134637278203493E-5</v>
-      </c>
-      <c r="H9">
-        <v>-3.1583697777708814E-4</v>
-      </c>
-      <c r="I9">
-        <v>-2.9840957813235158E-4</v>
-      </c>
-      <c r="J9">
-        <v>3.2266894705745256E-4</v>
-      </c>
-      <c r="K9">
-        <v>-1.5890851266514414E-3</v>
-      </c>
-      <c r="L9">
-        <v>-1.958201772702521E-3</v>
-      </c>
-      <c r="M9">
-        <v>-7.47212173378577E-3</v>
-      </c>
-      <c r="N9">
-        <v>-7.575077380311197E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10">
-        <v>0.12532596776269456</v>
-      </c>
-      <c r="C10">
-        <v>1.4115207494679497E-4</v>
-      </c>
-      <c r="D10">
-        <v>7.1361350383652711E-3</v>
-      </c>
-      <c r="E10">
-        <v>-1.6533215482391738E-4</v>
-      </c>
-      <c r="F10">
-        <v>1.5455314641815753E-3</v>
-      </c>
-      <c r="G10">
-        <v>-6.7291293666023062E-4</v>
-      </c>
-      <c r="H10">
-        <v>-3.0196271770003126E-4</v>
-      </c>
-      <c r="I10">
-        <v>-4.8818753259096542E-4</v>
-      </c>
-      <c r="J10">
-        <v>-1.5890851266514414E-3</v>
-      </c>
-      <c r="K10">
-        <v>5.5472330377570732E-2</v>
-      </c>
-      <c r="L10">
-        <v>1.1412873152831213E-2</v>
-      </c>
-      <c r="M10">
-        <v>-5.6170545883362594E-2</v>
-      </c>
-      <c r="N10">
-        <v>-6.9655217486060406E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11">
-        <v>1.2255113266353119</v>
-      </c>
-      <c r="C11">
-        <v>-2.8238345284652662E-3</v>
-      </c>
-      <c r="D11">
-        <v>6.0308263338469947E-3</v>
-      </c>
-      <c r="E11">
-        <v>-1.4305423316045458E-4</v>
-      </c>
-      <c r="F11">
-        <v>4.0685488155021475E-3</v>
-      </c>
-      <c r="G11">
-        <v>7.3454735056977406E-3</v>
-      </c>
-      <c r="H11">
-        <v>2.5851565590439807E-3</v>
-      </c>
-      <c r="I11">
-        <v>3.5584930954063519E-3</v>
-      </c>
-      <c r="J11">
-        <v>-1.958201772702521E-3</v>
-      </c>
-      <c r="K11">
-        <v>1.1412873152831213E-2</v>
-      </c>
-      <c r="L11">
-        <v>0.20402924290055638</v>
-      </c>
-      <c r="M11">
-        <v>-3.6383421002764219E-2</v>
-      </c>
-      <c r="N11">
-        <v>-6.8713031914267558E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="4">
         <v>-35.999775981072666</v>
       </c>
       <c r="C12">
         <v>-6.5626185107372191E-4</v>
       </c>
       <c r="D12">
+        <v>4.3427464948995548E-2</v>
+      </c>
+      <c r="E12">
+        <v>-8.456836762273226E-2</v>
+      </c>
+      <c r="F12">
+        <v>4.2720539798672852E-2</v>
+      </c>
+      <c r="G12">
+        <v>-6.2211762017819958E-3</v>
+      </c>
+      <c r="H12">
+        <v>-2.8467612703106659E-3</v>
+      </c>
+      <c r="I12">
+        <v>-7.47212173378577E-3</v>
+      </c>
+      <c r="J12">
+        <v>-5.6170545883362594E-2</v>
+      </c>
+      <c r="K12">
+        <v>-3.6383421002764219E-2</v>
+      </c>
+      <c r="L12">
         <v>-1.8943742662098764</v>
-      </c>
-      <c r="E12">
-        <v>4.3427464948995548E-2</v>
-      </c>
-      <c r="F12">
-        <v>-8.456836762273226E-2</v>
-      </c>
-      <c r="G12">
-        <v>4.2720539798672852E-2</v>
-      </c>
-      <c r="H12">
-        <v>-6.2211762017819958E-3</v>
-      </c>
-      <c r="I12">
-        <v>-2.8467612703106659E-3</v>
-      </c>
-      <c r="J12">
-        <v>-7.47212173378577E-3</v>
-      </c>
-      <c r="K12">
-        <v>-5.6170545883362594E-2</v>
-      </c>
-      <c r="L12">
-        <v>-3.6383421002764219E-2</v>
       </c>
       <c r="M12">
         <v>20.488600015981518</v>
       </c>
       <c r="N12">
+        <v>-2.0408408628839201</v>
+      </c>
+      <c r="O12">
         <v>23.932897346374034</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="4">
+        <v>3.463843445576031</v>
+      </c>
+      <c r="C13">
+        <v>-9.0485190649986424E-4</v>
+      </c>
+      <c r="D13">
+        <v>-4.4294521495035696E-3</v>
+      </c>
+      <c r="E13">
+        <v>7.2602172131255079E-3</v>
+      </c>
+      <c r="F13">
+        <v>-7.0623214131569807E-3</v>
+      </c>
+      <c r="G13">
+        <v>5.2558639108341455E-4</v>
+      </c>
+      <c r="H13">
+        <v>-3.8159618061404423E-5</v>
+      </c>
+      <c r="I13">
+        <v>3.0554670858922025E-4</v>
+      </c>
+      <c r="J13">
+        <v>7.7771235852395811E-3</v>
+      </c>
+      <c r="K13">
+        <v>7.2281855639998293E-3</v>
+      </c>
+      <c r="L13">
+        <v>0.19122788087141718</v>
+      </c>
+      <c r="M13">
+        <v>-2.0408408628839201</v>
+      </c>
+      <c r="N13">
+        <v>0.20978342293176833</v>
+      </c>
+      <c r="O13">
+        <v>-2.4733730279631736</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B13">
+      <c r="B14" s="4">
         <v>-50.492821427610203</v>
       </c>
-      <c r="C13">
+      <c r="C14">
         <v>1.6080806168536667E-3</v>
       </c>
-      <c r="D13">
+      <c r="D14">
+        <v>5.1751452567861234E-2</v>
+      </c>
+      <c r="E14">
+        <v>-9.0028535514479049E-2</v>
+      </c>
+      <c r="F14">
+        <v>7.3753253703915014E-2</v>
+      </c>
+      <c r="G14">
+        <v>-2.3582040298859908E-2</v>
+      </c>
+      <c r="H14">
+        <v>-5.8122855107039101E-3</v>
+      </c>
+      <c r="I14">
+        <v>-7.575077380311197E-3</v>
+      </c>
+      <c r="J14">
+        <v>-6.9655217486060406E-2</v>
+      </c>
+      <c r="K14">
+        <v>-6.8713031914267558E-2</v>
+      </c>
+      <c r="L14">
         <v>-2.2350063256210682</v>
       </c>
-      <c r="E13">
-        <v>5.1751452567861234E-2</v>
-      </c>
-      <c r="F13">
-        <v>-9.0028535514479049E-2</v>
-      </c>
-      <c r="G13">
-        <v>7.3753253703915014E-2</v>
-      </c>
-      <c r="H13">
-        <v>-2.3582040298859908E-2</v>
-      </c>
-      <c r="I13">
-        <v>-5.8122855107039101E-3</v>
-      </c>
-      <c r="J13">
-        <v>-7.575077380311197E-3</v>
-      </c>
-      <c r="K13">
-        <v>-6.9655217486060406E-2</v>
-      </c>
-      <c r="L13">
-        <v>-6.8713031914267558E-2</v>
-      </c>
-      <c r="M13">
+      <c r="M14">
         <v>23.932897346374034</v>
       </c>
-      <c r="N13">
+      <c r="N14">
+        <v>-2.4733730279631736</v>
+      </c>
+      <c r="O14">
         <v>29.51973160464496</v>
       </c>
     </row>

--- a/input/reg_education.xlsx
+++ b/input/reg_education.xlsx
@@ -8,10 +8,10 @@
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId2"/>
     <sheet name="Gof" sheetId="2" r:id="rId4"/>
-    <sheet name="E1a" sheetId="3" r:id="rId5"/>
-    <sheet name="E1b" sheetId="4" r:id="rId6"/>
+    <sheet name="UK_E1a" sheetId="3" r:id="rId5"/>
+    <sheet name="UK_E1b" sheetId="4" r:id="rId6"/>
     <sheet name="E2a_raw" sheetId="5" r:id="rId7"/>
-    <sheet name="E2a" sheetId="6" r:id="rId8"/>
+    <sheet name="UK_E2a" sheetId="6" r:id="rId8"/>
   </sheets>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -2324,13 +2324,13 @@
         <v>66</v>
       </c>
       <c r="B5">
-        <v>0.041717374056221002</v>
+        <v>0.041663827975436551</v>
       </c>
       <c r="E5" t="s">
         <v>68</v>
       </c>
       <c r="F5">
-        <v>567.11718157335406</v>
+        <v>566.14741607222493</v>
       </c>
     </row>
     <row r="6">
@@ -2338,13 +2338,13 @@
         <v>67</v>
       </c>
       <c r="B6">
-        <v>15875</v>
+        <v>15872</v>
       </c>
       <c r="E6" t="s">
         <v>69</v>
       </c>
       <c r="F6">
-        <v>-9833.1920178883138</v>
+        <v>-9832.9118485546423</v>
       </c>
     </row>
     <row r="8">
@@ -2357,13 +2357,13 @@
         <v>66</v>
       </c>
       <c r="B10">
-        <v>0.13888916301703635</v>
+        <v>0.13952378637986818</v>
       </c>
       <c r="E10" t="s">
         <v>68</v>
       </c>
       <c r="F10">
-        <v>704.2681215110041</v>
+        <v>700.81685105164104</v>
       </c>
     </row>
     <row r="11">
@@ -2371,13 +2371,13 @@
         <v>67</v>
       </c>
       <c r="B11">
-        <v>49725</v>
+        <v>49724</v>
       </c>
       <c r="E11" t="s">
         <v>69</v>
       </c>
       <c r="F11">
-        <v>-3986.6399839647438</v>
+        <v>-3983.6778057276783</v>
       </c>
     </row>
     <row r="13">
@@ -2390,7 +2390,7 @@
         <v>66</v>
       </c>
       <c r="B15">
-        <v>0.44653849649386845</v>
+        <v>0.44601910529091759</v>
       </c>
     </row>
     <row r="16">
@@ -2492,76 +2492,76 @@
         <v>41</v>
       </c>
       <c r="B2" s="8">
-        <v>0.016138165287586211</v>
+        <v>0.016386560865015574</v>
       </c>
       <c r="C2">
-        <v>0.00066078582738912249</v>
+        <v>0.00066259507225523682</v>
       </c>
       <c r="D2">
-        <v>6.4155241396107718e-005</v>
+        <v>6.3785394926255706e-005</v>
       </c>
       <c r="E2">
-        <v>-1.5779985163566429e-006</v>
+        <v>-1.5699640533426898e-006</v>
       </c>
       <c r="F2">
-        <v>3.0338910359335021e-005</v>
+        <v>3.2433924797005894e-005</v>
       </c>
       <c r="G2">
-        <v>1.5182892439297773e-005</v>
+        <v>1.5518059820433122e-005</v>
       </c>
       <c r="H2">
-        <v>7.8530006911892766e-005</v>
+        <v>8.8054006019607943e-005</v>
       </c>
       <c r="I2">
-        <v>1.6945001281416225e-005</v>
+        <v>2.5110993926796805e-005</v>
       </c>
       <c r="J2">
-        <v>-1.9745129917372645e-005</v>
+        <v>-1.1211817781242963e-005</v>
       </c>
       <c r="K2">
-        <v>3.7349660767643507e-006</v>
+        <v>1.1289327901656612e-005</v>
       </c>
       <c r="L2">
-        <v>1.2831945580238824e-005</v>
+        <v>2.0523253617862002e-005</v>
       </c>
       <c r="M2">
-        <v>7.7310665142270936e-006</v>
+        <v>1.179258102289478e-005</v>
       </c>
       <c r="N2">
-        <v>-1.0423416371074194e-005</v>
+        <v>-3.209111760149369e-006</v>
       </c>
       <c r="O2">
-        <v>4.6104970659479163e-007</v>
+        <v>8.607056069037482e-006</v>
       </c>
       <c r="P2">
-        <v>5.6834157460924255e-006</v>
+        <v>1.3479753071126885e-005</v>
       </c>
       <c r="Q2">
-        <v>3.3127159134330316e-005</v>
+        <v>4.2987971079150062e-005</v>
       </c>
       <c r="R2">
-        <v>5.4614740811253842e-006</v>
+        <v>1.7077066370552391e-005</v>
       </c>
       <c r="S2">
-        <v>3.355212684105317e-006</v>
+        <v>3.5207297846996311e-006</v>
       </c>
       <c r="T2">
-        <v>-1.1649247648609424e-005</v>
+        <v>-1.3076995499241727e-005</v>
       </c>
       <c r="U2">
-        <v>-4.8917685846798455e-006</v>
+        <v>-1.0300189624248086e-005</v>
       </c>
       <c r="V2">
-        <v>-1.5824312400950164e-005</v>
+        <v>-9.8776665445880112e-006</v>
       </c>
       <c r="W2">
-        <v>2.5906171669126525e-005</v>
+        <v>3.4627830156438457e-005</v>
       </c>
       <c r="X2">
-        <v>2.2893919529594258e-005</v>
+        <v>9.305646594547098e-005</v>
       </c>
       <c r="Y2">
-        <v>-0.0010355903812184026</v>
+        <v>-0.0010467990983319257</v>
       </c>
     </row>
     <row r="3">
@@ -2569,76 +2569,76 @@
         <v>42</v>
       </c>
       <c r="B3" s="10">
-        <v>-0.055144139339499833</v>
+        <v>-0.05167058301092952</v>
       </c>
       <c r="C3">
-        <v>6.4155241396107718e-005</v>
+        <v>6.3785394926255706e-005</v>
       </c>
       <c r="D3">
-        <v>0.011573035679291974</v>
+        <v>0.011572894672292238</v>
       </c>
       <c r="E3">
-        <v>-0.00028925924829073383</v>
+        <v>-0.00028927584309575144</v>
       </c>
       <c r="F3">
-        <v>-5.189065195863006e-005</v>
+        <v>-5.4428205914738848e-005</v>
       </c>
       <c r="G3">
-        <v>3.5803369033285751e-005</v>
+        <v>3.3886720275485421e-005</v>
       </c>
       <c r="H3">
-        <v>-5.3170630484621062e-005</v>
+        <v>-4.234381777742241e-005</v>
       </c>
       <c r="I3">
-        <v>3.2114936293757557e-005</v>
+        <v>4.4831299410311165e-005</v>
       </c>
       <c r="J3">
-        <v>3.1368943343192124e-005</v>
+        <v>3.9029671570225966e-005</v>
       </c>
       <c r="K3">
-        <v>-0.0001189276815121848</v>
+        <v>-0.00011501030367995491</v>
       </c>
       <c r="L3">
-        <v>7.2259270930592062e-005</v>
+        <v>8.1689875615950647e-005</v>
       </c>
       <c r="M3">
-        <v>5.7299737823493513e-006</v>
+        <v>2.3773061689200126e-005</v>
       </c>
       <c r="N3">
-        <v>3.7775412417485887e-005</v>
+        <v>4.5002489494100351e-005</v>
       </c>
       <c r="O3">
-        <v>0.0001019702820789295</v>
+        <v>0.00010843773914718385</v>
       </c>
       <c r="P3">
-        <v>1.3928830479709164e-005</v>
+        <v>2.0308149543554754e-005</v>
       </c>
       <c r="Q3">
-        <v>6.2120099936974205e-005</v>
+        <v>7.0184240495735351e-005</v>
       </c>
       <c r="R3">
-        <v>-8.5256474315689723e-005</v>
+        <v>-7.8701397094135817e-005</v>
       </c>
       <c r="S3">
-        <v>-2.0512752272886653e-005</v>
+        <v>-2.0675960633132449e-005</v>
       </c>
       <c r="T3">
-        <v>9.214173861424443e-005</v>
+        <v>9.208952169528317e-005</v>
       </c>
       <c r="U3">
-        <v>-3.6452887206750093e-005</v>
+        <v>-3.9094936917765527e-005</v>
       </c>
       <c r="V3">
-        <v>-1.7332175635417779e-005</v>
+        <v>-1.2589456054451498e-005</v>
       </c>
       <c r="W3">
-        <v>9.715422726781775e-005</v>
+        <v>0.0001057553590540633</v>
       </c>
       <c r="X3">
-        <v>-0.00028925674890907527</v>
+        <v>-6.6514137259568451e-005</v>
       </c>
       <c r="Y3">
-        <v>-0.11409029022333123</v>
+        <v>-0.11408708249946239</v>
       </c>
     </row>
     <row r="4">
@@ -2646,76 +2646,76 @@
         <v>43</v>
       </c>
       <c r="B4" s="12">
-        <v>-0.0018767236504209049</v>
+        <v>-0.0019606651544823994</v>
       </c>
       <c r="C4">
-        <v>-1.5779985163566429e-006</v>
+        <v>-1.5699640533426898e-006</v>
       </c>
       <c r="D4">
-        <v>-0.00028925924829073383</v>
+        <v>-0.00028927584309575144</v>
       </c>
       <c r="E4">
-        <v>7.2574991013909273e-006</v>
+        <v>7.2584372146596662e-006</v>
       </c>
       <c r="F4">
-        <v>1.4290304988286715e-006</v>
+        <v>1.4756641756880621e-006</v>
       </c>
       <c r="G4">
-        <v>-2.4687138348562874e-007</v>
+        <v>-2.1285782003774463e-007</v>
       </c>
       <c r="H4">
-        <v>1.5803103227966971e-006</v>
+        <v>1.3019720823642493e-006</v>
       </c>
       <c r="I4">
-        <v>-4.9155780290947252e-007</v>
+        <v>-8.1709136014412962e-007</v>
       </c>
       <c r="J4">
-        <v>-5.8739945444372457e-007</v>
+        <v>-7.8960291557137255e-007</v>
       </c>
       <c r="K4">
-        <v>3.2971068242911451e-006</v>
+        <v>3.1868186249833048e-006</v>
       </c>
       <c r="L4">
-        <v>-1.4271734121089168e-006</v>
+        <v>-1.6515278283826471e-006</v>
       </c>
       <c r="M4">
-        <v>1.2226648857065463e-007</v>
+        <v>-3.1712856277176047e-007</v>
       </c>
       <c r="N4">
-        <v>-7.7252462345384944e-007</v>
+        <v>-9.608915909142075e-007</v>
       </c>
       <c r="O4">
-        <v>-2.1332292295939397e-006</v>
+        <v>-2.308341353561864e-006</v>
       </c>
       <c r="P4">
-        <v>-2.9563713511006166e-007</v>
+        <v>-4.6657288984316807e-007</v>
       </c>
       <c r="Q4">
-        <v>-1.3077945046509592e-006</v>
+        <v>-1.5214142980982028e-006</v>
       </c>
       <c r="R4">
-        <v>1.8954773059534635e-006</v>
+        <v>1.7125873124058076e-006</v>
       </c>
       <c r="S4">
-        <v>4.9742038680115398e-007</v>
+        <v>5.0198177744319801e-007</v>
       </c>
       <c r="T4">
-        <v>-2.3225687146184376e-006</v>
+        <v>-2.3271949377979661e-006</v>
       </c>
       <c r="U4">
-        <v>6.4132760511519159e-007</v>
+        <v>7.0738823975519637e-007</v>
       </c>
       <c r="V4">
-        <v>-2.3512379681970598e-007</v>
+        <v>-3.6647406570890564e-007</v>
       </c>
       <c r="W4">
-        <v>-3.202508576675674e-006</v>
+        <v>-3.4301520417611385e-006</v>
       </c>
       <c r="X4">
-        <v>6.6171393625453698e-006</v>
+        <v>1.2473459119589718e-006</v>
       </c>
       <c r="Y4">
-        <v>0.0028413931176680014</v>
+        <v>0.0028415250943395398</v>
       </c>
     </row>
     <row r="5">
@@ -2723,76 +2723,76 @@
         <v>44</v>
       </c>
       <c r="B5" s="14">
-        <v>-0.31704023050487368</v>
+        <v>-0.31394371147081063</v>
       </c>
       <c r="C5">
-        <v>3.0338910359335021e-005</v>
+        <v>3.2433924797005894e-005</v>
       </c>
       <c r="D5">
-        <v>-5.189065195863006e-005</v>
+        <v>-5.4428205914738848e-005</v>
       </c>
       <c r="E5">
-        <v>1.4290304988286715e-006</v>
+        <v>1.4756641756880621e-006</v>
       </c>
       <c r="F5">
-        <v>0.0012141802450366913</v>
+        <v>0.0012169204233057117</v>
       </c>
       <c r="G5">
-        <v>0.00096322413957500655</v>
+        <v>0.0009649371239688182</v>
       </c>
       <c r="H5">
-        <v>-0.00011488669041486934</v>
+        <v>-9.5747742381156471e-005</v>
       </c>
       <c r="I5">
-        <v>-0.00013598203729982172</v>
+        <v>-0.0001193239080165387</v>
       </c>
       <c r="J5">
-        <v>-0.00013558980746938436</v>
+        <v>-0.00011863256946075353</v>
       </c>
       <c r="K5">
-        <v>-0.00013870155451066723</v>
+        <v>-0.00012450080445714298</v>
       </c>
       <c r="L5">
-        <v>-0.00012745055600902201</v>
+        <v>-0.00011712103510713918</v>
       </c>
       <c r="M5">
-        <v>-0.00010684104006801817</v>
+        <v>-9.3988189795396883e-005</v>
       </c>
       <c r="N5">
-        <v>-0.00010539891301574792</v>
+        <v>-9.0223813215301258e-005</v>
       </c>
       <c r="O5">
-        <v>-7.458128623583245e-005</v>
+        <v>-5.7388204167171898e-005</v>
       </c>
       <c r="P5">
-        <v>-0.00020875185920708446</v>
+        <v>-0.00019005877907182593</v>
       </c>
       <c r="Q5">
-        <v>-3.7392547512917298e-006</v>
+        <v>1.2634692756757586e-005</v>
       </c>
       <c r="R5">
-        <v>-0.00016051346604921608</v>
+        <v>-0.00013865567458408814</v>
       </c>
       <c r="S5">
-        <v>1.4801494815579037e-005</v>
+        <v>1.4996419981522707e-005</v>
       </c>
       <c r="T5">
-        <v>-2.2189762251310767e-005</v>
+        <v>-2.4209693501479426e-005</v>
       </c>
       <c r="U5">
-        <v>-2.6082402041990735e-005</v>
+        <v>-2.4286248399856664e-005</v>
       </c>
       <c r="V5">
-        <v>-7.2753685744639403e-005</v>
+        <v>-6.1177138584190497e-005</v>
       </c>
       <c r="W5">
-        <v>-1.0445039848163383e-005</v>
+        <v>6.6877046789943139e-006</v>
       </c>
       <c r="X5">
-        <v>-6.5074822922562458e-005</v>
+        <v>0.00011121288711122961</v>
       </c>
       <c r="Y5">
-        <v>-0.00061097093425310854</v>
+        <v>-0.00060677992294312524</v>
       </c>
     </row>
     <row r="6">
@@ -2800,76 +2800,76 @@
         <v>45</v>
       </c>
       <c r="B6" s="16">
-        <v>-0.46923099604753599</v>
+        <v>-0.46752614077482374</v>
       </c>
       <c r="C6">
-        <v>1.5182892439297773e-005</v>
+        <v>1.5518059820433122e-005</v>
       </c>
       <c r="D6">
-        <v>3.5803369033285751e-005</v>
+        <v>3.3886720275485421e-005</v>
       </c>
       <c r="E6">
-        <v>-2.4687138348562874e-007</v>
+        <v>-2.1285782003774463e-007</v>
       </c>
       <c r="F6">
-        <v>0.00096322413957500655</v>
+        <v>0.0009649371239688182</v>
       </c>
       <c r="G6">
-        <v>0.0018613287084840407</v>
+        <v>0.0018631917863134641</v>
       </c>
       <c r="H6">
-        <v>-0.00023571508725103729</v>
+        <v>-0.00022096781986109869</v>
       </c>
       <c r="I6">
-        <v>-0.00013448265347890299</v>
+        <v>-0.00012065195372773643</v>
       </c>
       <c r="J6">
-        <v>-0.00017422011256950471</v>
+        <v>-0.00016095860836540525</v>
       </c>
       <c r="K6">
-        <v>-0.00016049099343122422</v>
+        <v>-0.00015023714871447694</v>
       </c>
       <c r="L6">
-        <v>-0.00013955074269763912</v>
+        <v>-0.00013531779222460686</v>
       </c>
       <c r="M6">
-        <v>-0.00013820640550137617</v>
+        <v>-0.00012792421765780418</v>
       </c>
       <c r="N6">
-        <v>-7.9334947126789347e-005</v>
+        <v>-6.7271055140766234e-005</v>
       </c>
       <c r="O6">
-        <v>-2.6671941996797002e-005</v>
+        <v>-1.454536156544103e-005</v>
       </c>
       <c r="P6">
-        <v>-0.00024207136183737664</v>
+        <v>-0.00022405659626915995</v>
       </c>
       <c r="Q6">
-        <v>2.7204264707562042e-005</v>
+        <v>4.0522127301537017e-005</v>
       </c>
       <c r="R6">
-        <v>-0.00032042144169939927</v>
+        <v>-0.00030482875548267473</v>
       </c>
       <c r="S6">
-        <v>1.9386667897896583e-005</v>
+        <v>1.9443875997707474e-005</v>
       </c>
       <c r="T6">
-        <v>3.0222265157433763e-005</v>
+        <v>2.7604867187547742e-005</v>
       </c>
       <c r="U6">
-        <v>-9.5363102747571249e-006</v>
+        <v>-5.0205218557215076e-006</v>
       </c>
       <c r="V6">
-        <v>-0.00042525604367541425</v>
+        <v>-0.00041648222479118634</v>
       </c>
       <c r="W6">
-        <v>-0.00015439126567166526</v>
+        <v>-0.00014103805833221798</v>
       </c>
       <c r="X6">
-        <v>1.7996835095897187e-005</v>
+        <v>0.00011685243338232639</v>
       </c>
       <c r="Y6">
-        <v>-0.0017068928893956858</v>
+        <v>-0.0017015524945483489</v>
       </c>
     </row>
     <row r="7">
@@ -2877,76 +2877,76 @@
         <v>46</v>
       </c>
       <c r="B7" s="18">
-        <v>-0.018276030160151047</v>
+        <v>-0.011330843622714509</v>
       </c>
       <c r="C7">
-        <v>7.8530006911892766e-005</v>
+        <v>8.8054006019607943e-005</v>
       </c>
       <c r="D7">
-        <v>-5.3170630484621062e-005</v>
+        <v>-4.234381777742241e-005</v>
       </c>
       <c r="E7">
-        <v>1.5803103227966971e-006</v>
+        <v>1.3019720823642493e-006</v>
       </c>
       <c r="F7">
-        <v>-0.00011488669041486934</v>
+        <v>-9.5747742381156471e-005</v>
       </c>
       <c r="G7">
-        <v>-0.00023571508725103729</v>
+        <v>-0.00022096781986109869</v>
       </c>
       <c r="H7">
-        <v>0.0057610030220210948</v>
+        <v>0.005793779469180335</v>
       </c>
       <c r="I7">
-        <v>0.0019795419761635376</v>
+        <v>0.0020156944761266084</v>
       </c>
       <c r="J7">
-        <v>0.0019636482588189169</v>
+        <v>0.0019946236621383381</v>
       </c>
       <c r="K7">
-        <v>0.0019809168901508234</v>
+        <v>0.0020104262637568745</v>
       </c>
       <c r="L7">
-        <v>0.0019369453829088919</v>
+        <v>0.00196176542317659</v>
       </c>
       <c r="M7">
-        <v>0.0019886949606083932</v>
+        <v>0.0020072391539432701</v>
       </c>
       <c r="N7">
-        <v>0.0019909151303093395</v>
+        <v>0.0020139238657201292</v>
       </c>
       <c r="O7">
-        <v>0.0020242329708238397</v>
+        <v>0.0020587096950381019</v>
       </c>
       <c r="P7">
-        <v>0.0020567857738642181</v>
+        <v>0.0020955941745505894</v>
       </c>
       <c r="Q7">
-        <v>0.0020189715606656537</v>
+        <v>0.0020668961867740328</v>
       </c>
       <c r="R7">
-        <v>0.0020961228289893908</v>
+        <v>0.0021409644132197848</v>
       </c>
       <c r="S7">
-        <v>-1.3327636060269379e-005</v>
+        <v>-1.3411224423321694e-005</v>
       </c>
       <c r="T7">
-        <v>3.0548649253697062e-005</v>
+        <v>2.1828568155369853e-005</v>
       </c>
       <c r="U7">
-        <v>2.1724118246523613e-005</v>
+        <v>-1.0018622210449543e-006</v>
       </c>
       <c r="V7">
-        <v>0.00073795152092020035</v>
+        <v>0.0007685725367742027</v>
       </c>
       <c r="W7">
-        <v>0.0014450055846210556</v>
+        <v>0.0014844645098649901</v>
       </c>
       <c r="X7">
-        <v>0.00099076631170471143</v>
+        <v>0.00074486311562003244</v>
       </c>
       <c r="Y7">
-        <v>-0.0013647071269125017</v>
+        <v>-0.0015327863749833069</v>
       </c>
     </row>
     <row r="8">
@@ -2954,76 +2954,76 @@
         <v>47</v>
       </c>
       <c r="B8" s="20">
-        <v>-0.087015707767301997</v>
+        <v>-0.077561628406992683</v>
       </c>
       <c r="C8">
-        <v>1.6945001281416225e-005</v>
+        <v>2.5110993926796805e-005</v>
       </c>
       <c r="D8">
-        <v>3.2114936293757557e-005</v>
+        <v>4.4831299410311165e-005</v>
       </c>
       <c r="E8">
-        <v>-4.9155780290947252e-007</v>
+        <v>-8.1709136014412962e-007</v>
       </c>
       <c r="F8">
-        <v>-0.00013598203729982172</v>
+        <v>-0.0001193239080165387</v>
       </c>
       <c r="G8">
-        <v>-0.00013448265347890299</v>
+        <v>-0.00012065195372773643</v>
       </c>
       <c r="H8">
-        <v>0.0019795419761635376</v>
+        <v>0.0020156944761266084</v>
       </c>
       <c r="I8">
-        <v>0.0035601536260646762</v>
+        <v>0.0035989707933230049</v>
       </c>
       <c r="J8">
-        <v>0.0019012134226995873</v>
+        <v>0.0019337001639587164</v>
       </c>
       <c r="K8">
-        <v>0.0019127515157924234</v>
+        <v>0.0019436166068398692</v>
       </c>
       <c r="L8">
-        <v>0.0018824684744441949</v>
+        <v>0.0019086428677388822</v>
       </c>
       <c r="M8">
-        <v>0.0019162818611167349</v>
+        <v>0.0019369717847491997</v>
       </c>
       <c r="N8">
-        <v>0.0019242256501633013</v>
+        <v>0.0019492419006614209</v>
       </c>
       <c r="O8">
-        <v>0.0019557090086298259</v>
+        <v>0.0019914741812718092</v>
       </c>
       <c r="P8">
-        <v>0.0019735241395350449</v>
+        <v>0.0020140804369284063</v>
       </c>
       <c r="Q8">
-        <v>0.0019446351977012279</v>
+        <v>0.0019930951277967331</v>
       </c>
       <c r="R8">
-        <v>0.0019958817287596452</v>
+        <v>0.0020417663485555438</v>
       </c>
       <c r="S8">
-        <v>-1.2754729762091461e-005</v>
+        <v>-1.2709029045523273e-005</v>
       </c>
       <c r="T8">
-        <v>-2.9861164506118198e-006</v>
+        <v>-1.3525404375949563e-005</v>
       </c>
       <c r="U8">
-        <v>2.4173416988282744e-005</v>
+        <v>-5.2729124418718007e-006</v>
       </c>
       <c r="V8">
-        <v>0.00058969645155697976</v>
+        <v>0.00062122937902196957</v>
       </c>
       <c r="W8">
-        <v>0.0013013865071150295</v>
+        <v>0.0013418053644588333</v>
       </c>
       <c r="X8">
-        <v>0.00090856082090092763</v>
+        <v>0.00071209907591048764</v>
       </c>
       <c r="Y8">
-        <v>-0.0021257602710622347</v>
+        <v>-0.0023131031216598917</v>
       </c>
     </row>
     <row r="9">
@@ -3031,76 +3031,76 @@
         <v>48</v>
       </c>
       <c r="B9" s="22">
-        <v>-0.052871483802678684</v>
+        <v>-0.044807368282650757</v>
       </c>
       <c r="C9">
-        <v>-1.9745129917372645e-005</v>
+        <v>-1.1211817781242963e-005</v>
       </c>
       <c r="D9">
-        <v>3.1368943343192124e-005</v>
+        <v>3.9029671570225966e-005</v>
       </c>
       <c r="E9">
-        <v>-5.8739945444372457e-007</v>
+        <v>-7.8960291557137255e-007</v>
       </c>
       <c r="F9">
-        <v>-0.00013558980746938436</v>
+        <v>-0.00011863256946075353</v>
       </c>
       <c r="G9">
-        <v>-0.00017422011256950471</v>
+        <v>-0.00016095860836540525</v>
       </c>
       <c r="H9">
-        <v>0.0019636482588189169</v>
+        <v>0.0019946236621383381</v>
       </c>
       <c r="I9">
-        <v>0.0019012134226995873</v>
+        <v>0.0019337001639587164</v>
       </c>
       <c r="J9">
-        <v>0.0037341322665114399</v>
+        <v>0.0037644649836973284</v>
       </c>
       <c r="K9">
-        <v>0.0018987809867850971</v>
+        <v>0.0019253012133488307</v>
       </c>
       <c r="L9">
-        <v>0.0018715020344129999</v>
+        <v>0.0018943572201044277</v>
       </c>
       <c r="M9">
-        <v>0.0019048347072657852</v>
+        <v>0.0019219372745289413</v>
       </c>
       <c r="N9">
-        <v>0.0019108886307841887</v>
+        <v>0.0019315351810674057</v>
       </c>
       <c r="O9">
-        <v>0.0019357413253468692</v>
+        <v>0.0019665651194882604</v>
       </c>
       <c r="P9">
-        <v>0.0019586722037141313</v>
+        <v>0.0019939137303531594</v>
       </c>
       <c r="Q9">
-        <v>0.0019262089661830227</v>
+        <v>0.0019692963383101786</v>
       </c>
       <c r="R9">
-        <v>0.0019851134433040143</v>
+        <v>0.0020251979165013274</v>
       </c>
       <c r="S9">
-        <v>-1.4497090700137376e-005</v>
+        <v>-1.4386116832962356e-005</v>
       </c>
       <c r="T9">
-        <v>-1.5556866885543091e-005</v>
+        <v>-2.538016892196359e-005</v>
       </c>
       <c r="U9">
-        <v>4.1764547889529131e-005</v>
+        <v>1.7919883683758102e-005</v>
       </c>
       <c r="V9">
-        <v>0.00054118672022085011</v>
+        <v>0.0005694725589640362</v>
       </c>
       <c r="W9">
-        <v>0.0012740909981960196</v>
+        <v>0.0013099897202201835</v>
       </c>
       <c r="X9">
-        <v>0.00087869778535027516</v>
+        <v>0.0006593671290352726</v>
       </c>
       <c r="Y9">
-        <v>-0.0020080157220545699</v>
+        <v>-0.0021396886179511935</v>
       </c>
     </row>
     <row r="10">
@@ -3108,76 +3108,76 @@
         <v>49</v>
       </c>
       <c r="B10" s="24">
-        <v>-0.035440989781883814</v>
+        <v>-0.030346218766493363</v>
       </c>
       <c r="C10">
-        <v>3.7349660767643507e-006</v>
+        <v>1.1289327901656612e-005</v>
       </c>
       <c r="D10">
-        <v>-0.0001189276815121848</v>
+        <v>-0.00011501030367995491</v>
       </c>
       <c r="E10">
-        <v>3.2971068242911451e-006</v>
+        <v>3.1868186249833048e-006</v>
       </c>
       <c r="F10">
-        <v>-0.00013870155451066723</v>
+        <v>-0.00012450080445714298</v>
       </c>
       <c r="G10">
-        <v>-0.00016049099343122422</v>
+        <v>-0.00015023714871447694</v>
       </c>
       <c r="H10">
-        <v>0.0019809168901508234</v>
+        <v>0.0020104262637568745</v>
       </c>
       <c r="I10">
-        <v>0.0019127515157924234</v>
+        <v>0.0019436166068398692</v>
       </c>
       <c r="J10">
-        <v>0.0018987809867850971</v>
+        <v>0.0019253012133488307</v>
       </c>
       <c r="K10">
-        <v>0.004014575082236199</v>
+        <v>0.0040428169504498459</v>
       </c>
       <c r="L10">
-        <v>0.0018762812769575741</v>
+        <v>0.0018981398972518651</v>
       </c>
       <c r="M10">
-        <v>0.0019189942719256999</v>
+        <v>0.0019349121553748645</v>
       </c>
       <c r="N10">
-        <v>0.0019285007213221627</v>
+        <v>0.0019481235337819799</v>
       </c>
       <c r="O10">
-        <v>0.0019573364809239045</v>
+        <v>0.0019865437137925922</v>
       </c>
       <c r="P10">
-        <v>0.0019881774820181726</v>
+        <v>0.0020219242207811187</v>
       </c>
       <c r="Q10">
-        <v>0.001946506952459949</v>
+        <v>0.0019866963616740826</v>
       </c>
       <c r="R10">
-        <v>0.0020064059673394865</v>
+        <v>0.0020446799073110394</v>
       </c>
       <c r="S10">
-        <v>-4.271249259942131e-006</v>
+        <v>-4.1161217684595319e-006</v>
       </c>
       <c r="T10">
-        <v>-9.3846167512535079e-006</v>
+        <v>-1.8591529992707848e-005</v>
       </c>
       <c r="U10">
-        <v>6.3803596491869189e-005</v>
+        <v>4.0688111772389779e-005</v>
       </c>
       <c r="V10">
-        <v>0.00062968557862745991</v>
+        <v>0.00065737216048338692</v>
       </c>
       <c r="W10">
-        <v>0.001264291855265273</v>
+        <v>0.0012946337991289398</v>
       </c>
       <c r="X10">
-        <v>0.00080911798647472313</v>
+        <v>0.00061522110320758386</v>
       </c>
       <c r="Y10">
-        <v>-0.00076465093317661537</v>
+        <v>-0.00085443346765786917</v>
       </c>
     </row>
     <row r="11">
@@ -3185,76 +3185,76 @@
         <v>50</v>
       </c>
       <c r="B11" s="26">
-        <v>0.0094735905330814944</v>
+        <v>0.0098051511401524398</v>
       </c>
       <c r="C11">
-        <v>1.2831945580238824e-005</v>
+        <v>2.0523253617862002e-005</v>
       </c>
       <c r="D11">
-        <v>7.2259270930592062e-005</v>
+        <v>8.1689875615950647e-005</v>
       </c>
       <c r="E11">
-        <v>-1.4271734121089168e-006</v>
+        <v>-1.6515278283826471e-006</v>
       </c>
       <c r="F11">
-        <v>-0.00012745055600902201</v>
+        <v>-0.00011712103510713918</v>
       </c>
       <c r="G11">
-        <v>-0.00013955074269763912</v>
+        <v>-0.00013531779222460686</v>
       </c>
       <c r="H11">
-        <v>0.0019369453829088919</v>
+        <v>0.00196176542317659</v>
       </c>
       <c r="I11">
-        <v>0.0018824684744441949</v>
+        <v>0.0019086428677388822</v>
       </c>
       <c r="J11">
-        <v>0.0018715020344129999</v>
+        <v>0.0018943572201044277</v>
       </c>
       <c r="K11">
-        <v>0.0018762812769575741</v>
+        <v>0.0018981398972518651</v>
       </c>
       <c r="L11">
-        <v>0.003868730057153717</v>
+        <v>0.0038855767703935115</v>
       </c>
       <c r="M11">
-        <v>0.0018816166318741205</v>
+        <v>0.0018958660027927269</v>
       </c>
       <c r="N11">
-        <v>0.001888395068204897</v>
+        <v>0.0019048131352990241</v>
       </c>
       <c r="O11">
-        <v>0.0019128294704987006</v>
+        <v>0.0019363799272484601</v>
       </c>
       <c r="P11">
-        <v>0.0019322830241121445</v>
+        <v>0.0019601974024510771</v>
       </c>
       <c r="Q11">
-        <v>0.0019031249909651888</v>
+        <v>0.0019378423829073169</v>
       </c>
       <c r="R11">
-        <v>0.0019498888032485711</v>
+        <v>0.0019818739574310002</v>
       </c>
       <c r="S11">
-        <v>-1.1544969643090752e-005</v>
+        <v>-1.1387193017088225e-005</v>
       </c>
       <c r="T11">
-        <v>9.2881899480022888e-005</v>
+        <v>7.9871391370819116e-005</v>
       </c>
       <c r="U11">
-        <v>5.757026810524965e-005</v>
+        <v>3.2109616694534957e-005</v>
       </c>
       <c r="V11">
-        <v>0.00040779584259810454</v>
+        <v>0.00042793714238739233</v>
       </c>
       <c r="W11">
-        <v>0.0012564790722820499</v>
+        <v>0.0012847316493765741</v>
       </c>
       <c r="X11">
-        <v>0.00085094929683886429</v>
+        <v>0.00061025379604819888</v>
       </c>
       <c r="Y11">
-        <v>-0.0025277854504054558</v>
+        <v>-0.0026705539023951039</v>
       </c>
     </row>
     <row r="12">
@@ -3262,76 +3262,76 @@
         <v>51</v>
       </c>
       <c r="B12" s="28">
-        <v>-0.04835255150710846</v>
+        <v>-0.0421451173094365</v>
       </c>
       <c r="C12">
-        <v>7.7310665142270936e-006</v>
+        <v>1.179258102289478e-005</v>
       </c>
       <c r="D12">
-        <v>5.7299737823493513e-006</v>
+        <v>2.3773061689200126e-005</v>
       </c>
       <c r="E12">
-        <v>1.2226648857065463e-007</v>
+        <v>-3.1712856277176047e-007</v>
       </c>
       <c r="F12">
-        <v>-0.00010684104006801817</v>
+        <v>-9.3988189795396883e-005</v>
       </c>
       <c r="G12">
-        <v>-0.00013820640550137617</v>
+        <v>-0.00012792421765780418</v>
       </c>
       <c r="H12">
-        <v>0.0019886949606083932</v>
+        <v>0.0020072391539432701</v>
       </c>
       <c r="I12">
-        <v>0.0019162818611167349</v>
+        <v>0.0019369717847491997</v>
       </c>
       <c r="J12">
-        <v>0.0019048347072657852</v>
+        <v>0.0019219372745289413</v>
       </c>
       <c r="K12">
-        <v>0.0019189942719256999</v>
+        <v>0.0019349121553748645</v>
       </c>
       <c r="L12">
-        <v>0.0018816166318741205</v>
+        <v>0.0018958660027927269</v>
       </c>
       <c r="M12">
-        <v>0.003878041032220227</v>
+        <v>0.0038773541425030852</v>
       </c>
       <c r="N12">
-        <v>0.0019318245162973885</v>
+        <v>0.001943041498685343</v>
       </c>
       <c r="O12">
-        <v>0.0019656130945422869</v>
+        <v>0.001985009507900609</v>
       </c>
       <c r="P12">
-        <v>0.001983822222961438</v>
+        <v>0.0020060197550444041</v>
       </c>
       <c r="Q12">
-        <v>0.0019562840380260051</v>
+        <v>0.0019855190806233676</v>
       </c>
       <c r="R12">
-        <v>0.0020118988103619605</v>
+        <v>0.002037294748373187</v>
       </c>
       <c r="S12">
-        <v>-1.5580940637572319e-005</v>
+        <v>-1.6098334336056853e-005</v>
       </c>
       <c r="T12">
-        <v>5.0202665607835956e-005</v>
+        <v>4.5270096436028907e-005</v>
       </c>
       <c r="U12">
-        <v>6.9422958561764686e-005</v>
+        <v>5.4183179226284062e-005</v>
       </c>
       <c r="V12">
-        <v>0.00065669880127735831</v>
+        <v>0.000674869096085896</v>
       </c>
       <c r="W12">
-        <v>0.0012853368104977303</v>
+        <v>0.0013110395515903521</v>
       </c>
       <c r="X12">
-        <v>0.00076289681721374882</v>
+        <v>0.00050884816323414008</v>
       </c>
       <c r="Y12">
-        <v>-0.0018360516625129317</v>
+        <v>-0.0020491136542521368</v>
       </c>
     </row>
     <row r="13">
@@ -3339,76 +3339,76 @@
         <v>52</v>
       </c>
       <c r="B13" s="30">
-        <v>-0.012421781550390634</v>
+        <v>-0.007335671443874473</v>
       </c>
       <c r="C13">
-        <v>-1.0423416371074194e-005</v>
+        <v>-3.209111760149369e-006</v>
       </c>
       <c r="D13">
-        <v>3.7775412417485887e-005</v>
+        <v>4.5002489494100351e-005</v>
       </c>
       <c r="E13">
-        <v>-7.7252462345384944e-007</v>
+        <v>-9.608915909142075e-007</v>
       </c>
       <c r="F13">
-        <v>-0.00010539891301574792</v>
+        <v>-9.0223813215301258e-005</v>
       </c>
       <c r="G13">
-        <v>-7.9334947126789347e-005</v>
+        <v>-6.7271055140766234e-005</v>
       </c>
       <c r="H13">
-        <v>0.0019909151303093395</v>
+        <v>0.0020139238657201292</v>
       </c>
       <c r="I13">
-        <v>0.0019242256501633013</v>
+        <v>0.0019492419006614209</v>
       </c>
       <c r="J13">
-        <v>0.0019108886307841887</v>
+        <v>0.0019315351810674057</v>
       </c>
       <c r="K13">
-        <v>0.0019285007213221627</v>
+        <v>0.0019481235337819799</v>
       </c>
       <c r="L13">
-        <v>0.001888395068204897</v>
+        <v>0.0019048131352990241</v>
       </c>
       <c r="M13">
-        <v>0.0019318245162973885</v>
+        <v>0.001943041498685343</v>
       </c>
       <c r="N13">
-        <v>0.0032995850781887591</v>
+        <v>0.003314316306467632</v>
       </c>
       <c r="O13">
-        <v>0.0019772144913514666</v>
+        <v>0.0020002338898940683</v>
       </c>
       <c r="P13">
-        <v>0.0019968860505909227</v>
+        <v>0.0020245281173722502</v>
       </c>
       <c r="Q13">
-        <v>0.0019691388945638185</v>
+        <v>0.002003903689536052</v>
       </c>
       <c r="R13">
-        <v>0.0020142962711370243</v>
+        <v>0.0020454359304940446</v>
       </c>
       <c r="S13">
-        <v>-5.3705534220362095e-006</v>
+        <v>-5.2988970696433296e-006</v>
       </c>
       <c r="T13">
-        <v>-1.0498948426102513e-005</v>
+        <v>-1.9778772664653104e-005</v>
       </c>
       <c r="U13">
-        <v>3.3704327661159125e-005</v>
+        <v>1.0387359183996802e-005</v>
       </c>
       <c r="V13">
-        <v>0.00062997862594279196</v>
+        <v>0.0006535184633649771</v>
       </c>
       <c r="W13">
-        <v>0.001329891386379272</v>
+        <v>0.0013583066388588453</v>
       </c>
       <c r="X13">
-        <v>0.00086749109494471601</v>
+        <v>0.0005987517298693322</v>
       </c>
       <c r="Y13">
-        <v>-0.0022839752853169274</v>
+        <v>-0.0024006673650027086</v>
       </c>
     </row>
     <row r="14">
@@ -3416,76 +3416,76 @@
         <v>53</v>
       </c>
       <c r="B14" s="32">
-        <v>-0.14505188519393486</v>
+        <v>-0.13692001081504124</v>
       </c>
       <c r="C14">
-        <v>4.6104970659479163e-007</v>
+        <v>8.607056069037482e-006</v>
       </c>
       <c r="D14">
-        <v>0.0001019702820789295</v>
+        <v>0.00010843773914718385</v>
       </c>
       <c r="E14">
-        <v>-2.1332292295939397e-006</v>
+        <v>-2.308341353561864e-006</v>
       </c>
       <c r="F14">
-        <v>-7.458128623583245e-005</v>
+        <v>-5.7388204167171898e-005</v>
       </c>
       <c r="G14">
-        <v>-2.6671941996797002e-005</v>
+        <v>-1.454536156544103e-005</v>
       </c>
       <c r="H14">
-        <v>0.0020242329708238397</v>
+        <v>0.0020587096950381019</v>
       </c>
       <c r="I14">
-        <v>0.0019557090086298259</v>
+        <v>0.0019914741812718092</v>
       </c>
       <c r="J14">
-        <v>0.0019357413253468692</v>
+        <v>0.0019665651194882604</v>
       </c>
       <c r="K14">
-        <v>0.0019573364809239045</v>
+        <v>0.0019865437137925922</v>
       </c>
       <c r="L14">
-        <v>0.0019128294704987006</v>
+        <v>0.0019363799272484601</v>
       </c>
       <c r="M14">
-        <v>0.0019656130945422869</v>
+        <v>0.001985009507900609</v>
       </c>
       <c r="N14">
-        <v>0.0019772144913514666</v>
+        <v>0.0020002338898940683</v>
       </c>
       <c r="O14">
-        <v>0.0041295486015777202</v>
+        <v>0.0041647606177115668</v>
       </c>
       <c r="P14">
-        <v>0.0020260961267421097</v>
+        <v>0.0020649485607586397</v>
       </c>
       <c r="Q14">
-        <v>0.0020080536786757485</v>
+        <v>0.0020546954647645268</v>
       </c>
       <c r="R14">
-        <v>0.0020451861320513473</v>
+        <v>0.0020892489337236307</v>
       </c>
       <c r="S14">
-        <v>-1.1307832707402223e-005</v>
+        <v>-1.1632925658420885e-005</v>
       </c>
       <c r="T14">
-        <v>2.787989817337493e-005</v>
+        <v>1.9405220694317118e-005</v>
       </c>
       <c r="U14">
-        <v>7.3655288604050785e-005</v>
+        <v>4.8355250230264983e-005</v>
       </c>
       <c r="V14">
-        <v>0.00071017730092825669</v>
+        <v>0.00074251961712835978</v>
       </c>
       <c r="W14">
-        <v>0.0013481071073372843</v>
+        <v>0.0013868547789416413</v>
       </c>
       <c r="X14">
-        <v>0.00094918758233899288</v>
+        <v>0.00071442841954395234</v>
       </c>
       <c r="Y14">
-        <v>-0.0029928396134509894</v>
+        <v>-0.0031087019318487546</v>
       </c>
     </row>
     <row r="15">
@@ -3493,76 +3493,76 @@
         <v>54</v>
       </c>
       <c r="B15" s="34">
-        <v>-0.041116510708296035</v>
+        <v>-0.035869169139455995</v>
       </c>
       <c r="C15">
-        <v>5.6834157460924255e-006</v>
+        <v>1.3479753071126885e-005</v>
       </c>
       <c r="D15">
-        <v>1.3928830479709164e-005</v>
+        <v>2.0308149543554754e-005</v>
       </c>
       <c r="E15">
-        <v>-2.9563713511006166e-007</v>
+        <v>-4.6657288984316807e-007</v>
       </c>
       <c r="F15">
-        <v>-0.00020875185920708446</v>
+        <v>-0.00019005877907182593</v>
       </c>
       <c r="G15">
-        <v>-0.00024207136183737664</v>
+        <v>-0.00022405659626915995</v>
       </c>
       <c r="H15">
-        <v>0.0020567857738642181</v>
+        <v>0.0020955941745505894</v>
       </c>
       <c r="I15">
-        <v>0.0019735241395350449</v>
+        <v>0.0020140804369284063</v>
       </c>
       <c r="J15">
-        <v>0.0019586722037141313</v>
+        <v>0.0019939137303531594</v>
       </c>
       <c r="K15">
-        <v>0.0019881774820181726</v>
+        <v>0.0020219242207811187</v>
       </c>
       <c r="L15">
-        <v>0.0019322830241121445</v>
+        <v>0.0019601974024510771</v>
       </c>
       <c r="M15">
-        <v>0.001983822222961438</v>
+        <v>0.0020060197550444041</v>
       </c>
       <c r="N15">
-        <v>0.0019968860505909227</v>
+        <v>0.0020245281173722502</v>
       </c>
       <c r="O15">
-        <v>0.0020260961267421097</v>
+        <v>0.0020649485607586397</v>
       </c>
       <c r="P15">
-        <v>0.0044299625447378199</v>
+        <v>0.0044805684411535632</v>
       </c>
       <c r="Q15">
-        <v>0.0020144357218184962</v>
+        <v>0.0020657308617753143</v>
       </c>
       <c r="R15">
-        <v>0.0020928265746113779</v>
+        <v>0.0021417650687312641</v>
       </c>
       <c r="S15">
-        <v>2.170996855223904e-006</v>
+        <v>2.1081742755446527e-006</v>
       </c>
       <c r="T15">
-        <v>-4.4074508368009498e-006</v>
+        <v>-1.326308728040407e-005</v>
       </c>
       <c r="U15">
-        <v>-1.7679303037746201e-006</v>
+        <v>-1.3074680443933611e-005</v>
       </c>
       <c r="V15">
-        <v>0.00076072411200987637</v>
+        <v>0.00079191835004788907</v>
       </c>
       <c r="W15">
-        <v>0.0014482603656574039</v>
+        <v>0.0014896280138059414</v>
       </c>
       <c r="X15">
-        <v>0.00092211717353658839</v>
+        <v>0.00074448058901216028</v>
       </c>
       <c r="Y15">
-        <v>-0.0020947180758441467</v>
+        <v>-0.0022224268835616713</v>
       </c>
     </row>
     <row r="16">
@@ -3570,76 +3570,76 @@
         <v>55</v>
       </c>
       <c r="B16" s="36">
-        <v>-0.076111204586776116</v>
+        <v>-0.066704878126102915</v>
       </c>
       <c r="C16">
-        <v>3.3127159134330316e-005</v>
+        <v>4.2987971079150062e-005</v>
       </c>
       <c r="D16">
-        <v>6.2120099936974205e-005</v>
+        <v>7.0184240495735351e-005</v>
       </c>
       <c r="E16">
-        <v>-1.3077945046509592e-006</v>
+        <v>-1.5214142980982028e-006</v>
       </c>
       <c r="F16">
-        <v>-3.7392547512917298e-006</v>
+        <v>1.2634692756757586e-005</v>
       </c>
       <c r="G16">
-        <v>2.7204264707562042e-005</v>
+        <v>4.0522127301537017e-005</v>
       </c>
       <c r="H16">
-        <v>0.0020189715606656537</v>
+        <v>0.0020668961867740328</v>
       </c>
       <c r="I16">
-        <v>0.0019446351977012279</v>
+        <v>0.0019930951277967331</v>
       </c>
       <c r="J16">
-        <v>0.0019262089661830227</v>
+        <v>0.0019692963383101786</v>
       </c>
       <c r="K16">
-        <v>0.001946506952459949</v>
+        <v>0.0019866963616740826</v>
       </c>
       <c r="L16">
-        <v>0.0019031249909651888</v>
+        <v>0.0019378423829073169</v>
       </c>
       <c r="M16">
-        <v>0.0019562840380260051</v>
+        <v>0.0019855190806233676</v>
       </c>
       <c r="N16">
-        <v>0.0019691388945638185</v>
+        <v>0.002003903689536052</v>
       </c>
       <c r="O16">
-        <v>0.0020080536786757485</v>
+        <v>0.0020546954647645268</v>
       </c>
       <c r="P16">
-        <v>0.0020144357218184962</v>
+        <v>0.0020657308617753143</v>
       </c>
       <c r="Q16">
-        <v>0.00383535061179705</v>
+        <v>0.0038904049945123337</v>
       </c>
       <c r="R16">
-        <v>0.0020357536873930018</v>
+        <v>0.0020937566474299439</v>
       </c>
       <c r="S16">
-        <v>-5.2537263873023707e-006</v>
+        <v>-5.6487790249949005e-006</v>
       </c>
       <c r="T16">
-        <v>-3.4647540591679726e-005</v>
+        <v>-4.1323661599292275e-005</v>
       </c>
       <c r="U16">
-        <v>-5.3750126778896604e-005</v>
+        <v>-7.2677222202786928e-005</v>
       </c>
       <c r="V16">
-        <v>0.00071215327505665994</v>
+        <v>0.00074727715013049286</v>
       </c>
       <c r="W16">
-        <v>0.0014125691723430116</v>
+        <v>0.0014632895012737675</v>
       </c>
       <c r="X16">
-        <v>0.00082741303640826869</v>
+        <v>0.00074209461309381649</v>
       </c>
       <c r="Y16">
-        <v>-0.0026831384243376534</v>
+        <v>-0.0028293279057869311</v>
       </c>
     </row>
     <row r="17">
@@ -3647,76 +3647,76 @@
         <v>56</v>
       </c>
       <c r="B17" s="38">
-        <v>0.19117446942902569</v>
+        <v>0.19591369156146515</v>
       </c>
       <c r="C17">
-        <v>5.4614740811253842e-006</v>
+        <v>1.7077066370552391e-005</v>
       </c>
       <c r="D17">
-        <v>-8.5256474315689723e-005</v>
+        <v>-7.8701397094135817e-005</v>
       </c>
       <c r="E17">
-        <v>1.8954773059534635e-006</v>
+        <v>1.7125873124058076e-006</v>
       </c>
       <c r="F17">
-        <v>-0.00016051346604921608</v>
+        <v>-0.00013865567458408814</v>
       </c>
       <c r="G17">
-        <v>-0.00032042144169939927</v>
+        <v>-0.00030482875548267473</v>
       </c>
       <c r="H17">
-        <v>0.0020961228289893908</v>
+        <v>0.0021409644132197848</v>
       </c>
       <c r="I17">
-        <v>0.0019958817287596452</v>
+        <v>0.0020417663485555438</v>
       </c>
       <c r="J17">
-        <v>0.0019851134433040143</v>
+        <v>0.0020251979165013274</v>
       </c>
       <c r="K17">
-        <v>0.0020064059673394865</v>
+        <v>0.0020446799073110394</v>
       </c>
       <c r="L17">
-        <v>0.0019498888032485711</v>
+        <v>0.0019818739574310002</v>
       </c>
       <c r="M17">
-        <v>0.0020118988103619605</v>
+        <v>0.002037294748373187</v>
       </c>
       <c r="N17">
-        <v>0.0020142962711370243</v>
+        <v>0.0020454359304940446</v>
       </c>
       <c r="O17">
-        <v>0.0020451861320513473</v>
+        <v>0.0020892489337236307</v>
       </c>
       <c r="P17">
-        <v>0.0020928265746113779</v>
+        <v>0.0021417650687312641</v>
       </c>
       <c r="Q17">
-        <v>0.0020357536873930018</v>
+        <v>0.0020937566474299439</v>
       </c>
       <c r="R17">
-        <v>0.0038191716689746718</v>
+        <v>0.003874600674682037</v>
       </c>
       <c r="S17">
-        <v>-1.2418027650534411e-005</v>
+        <v>-1.2245243776892938e-005</v>
       </c>
       <c r="T17">
-        <v>2.2199785298967817e-005</v>
+        <v>1.0245634607973694e-005</v>
       </c>
       <c r="U17">
-        <v>4.6974531191106571e-005</v>
+        <v>1.8844491050873891e-005</v>
       </c>
       <c r="V17">
-        <v>0.00085679845633657235</v>
+        <v>0.00089375723726435531</v>
       </c>
       <c r="W17">
-        <v>0.0014883750314830585</v>
+        <v>0.0015374831280887949</v>
       </c>
       <c r="X17">
-        <v>0.0010150786098990403</v>
+        <v>0.00082502346876541172</v>
       </c>
       <c r="Y17">
-        <v>-0.00083613873693785606</v>
+        <v>-0.00097595339758657141</v>
       </c>
     </row>
     <row r="18">
@@ -3724,76 +3724,76 @@
         <v>57</v>
       </c>
       <c r="B18" s="40">
-        <v>-0.015267459103458305</v>
+        <v>-0.015542822940790426</v>
       </c>
       <c r="C18">
-        <v>3.355212684105317e-006</v>
+        <v>3.5207297846996311e-006</v>
       </c>
       <c r="D18">
-        <v>-2.0512752272886653e-005</v>
+        <v>-2.0675960633132449e-005</v>
       </c>
       <c r="E18">
-        <v>4.9742038680115398e-007</v>
+        <v>5.0198177744319801e-007</v>
       </c>
       <c r="F18">
-        <v>1.4801494815579037e-005</v>
+        <v>1.4996419981522707e-005</v>
       </c>
       <c r="G18">
-        <v>1.9386667897896583e-005</v>
+        <v>1.9443875997707474e-005</v>
       </c>
       <c r="H18">
-        <v>-1.3327636060269379e-005</v>
+        <v>-1.3411224423321694e-005</v>
       </c>
       <c r="I18">
-        <v>-1.2754729762091461e-005</v>
+        <v>-1.2709029045523273e-005</v>
       </c>
       <c r="J18">
-        <v>-1.4497090700137376e-005</v>
+        <v>-1.4386116832962356e-005</v>
       </c>
       <c r="K18">
-        <v>-4.271249259942131e-006</v>
+        <v>-4.1161217684595319e-006</v>
       </c>
       <c r="L18">
-        <v>-1.1544969643090752e-005</v>
+        <v>-1.1387193017088225e-005</v>
       </c>
       <c r="M18">
-        <v>-1.5580940637572319e-005</v>
+        <v>-1.6098334336056853e-005</v>
       </c>
       <c r="N18">
-        <v>-5.3705534220362095e-006</v>
+        <v>-5.2988970696433296e-006</v>
       </c>
       <c r="O18">
-        <v>-1.1307832707402223e-005</v>
+        <v>-1.1632925658420885e-005</v>
       </c>
       <c r="P18">
-        <v>2.170996855223904e-006</v>
+        <v>2.1081742755446527e-006</v>
       </c>
       <c r="Q18">
-        <v>-5.2537263873023707e-006</v>
+        <v>-5.6487790249949005e-006</v>
       </c>
       <c r="R18">
-        <v>-1.2418027650534411e-005</v>
+        <v>-1.2245243776892938e-005</v>
       </c>
       <c r="S18">
-        <v>2.2753673312712819e-005</v>
+        <v>2.2802424611971048e-005</v>
       </c>
       <c r="T18">
-        <v>-0.0001161219795886391</v>
+        <v>-0.0001164418313308821</v>
       </c>
       <c r="U18">
-        <v>-0.0001383930010073337</v>
+        <v>-0.00013892495950608205</v>
       </c>
       <c r="V18">
-        <v>-1.3825261228110944e-005</v>
+        <v>-1.3940265366807432e-005</v>
       </c>
       <c r="W18">
-        <v>1.0250522829824172e-005</v>
+        <v>1.0207193409467674e-005</v>
       </c>
       <c r="X18">
-        <v>-5.7989656202164848e-006</v>
+        <v>3.3458913281948145e-006</v>
       </c>
       <c r="Y18">
-        <v>-0.00013402273981353609</v>
+        <v>-0.00013352900393857913</v>
       </c>
     </row>
     <row r="19">
@@ -3801,76 +3801,76 @@
         <v>58</v>
       </c>
       <c r="B19" s="42">
-        <v>-0.0092342860975116615</v>
+        <v>-0.0080200321795995365</v>
       </c>
       <c r="C19">
-        <v>-1.1649247648609424e-005</v>
+        <v>-1.3076995499241727e-005</v>
       </c>
       <c r="D19">
-        <v>9.214173861424443e-005</v>
+        <v>9.208952169528317e-005</v>
       </c>
       <c r="E19">
-        <v>-2.3225687146184376e-006</v>
+        <v>-2.3271949377979661e-006</v>
       </c>
       <c r="F19">
-        <v>-2.2189762251310767e-005</v>
+        <v>-2.4209693501479426e-005</v>
       </c>
       <c r="G19">
-        <v>3.0222265157433763e-005</v>
+        <v>2.7604867187547742e-005</v>
       </c>
       <c r="H19">
-        <v>3.0548649253697062e-005</v>
+        <v>2.1828568155369853e-005</v>
       </c>
       <c r="I19">
-        <v>-2.9861164506118198e-006</v>
+        <v>-1.3525404375949563e-005</v>
       </c>
       <c r="J19">
-        <v>-1.5556866885543091e-005</v>
+        <v>-2.538016892196359e-005</v>
       </c>
       <c r="K19">
-        <v>-9.3846167512535079e-006</v>
+        <v>-1.8591529992707848e-005</v>
       </c>
       <c r="L19">
-        <v>9.2881899480022888e-005</v>
+        <v>7.9871391370819116e-005</v>
       </c>
       <c r="M19">
-        <v>5.0202665607835956e-005</v>
+        <v>4.5270096436028907e-005</v>
       </c>
       <c r="N19">
-        <v>-1.0498948426102513e-005</v>
+        <v>-1.9778772664653104e-005</v>
       </c>
       <c r="O19">
-        <v>2.787989817337493e-005</v>
+        <v>1.9405220694317118e-005</v>
       </c>
       <c r="P19">
-        <v>-4.4074508368009498e-006</v>
+        <v>-1.326308728040407e-005</v>
       </c>
       <c r="Q19">
-        <v>-3.4647540591679726e-005</v>
+        <v>-4.1323661599292275e-005</v>
       </c>
       <c r="R19">
-        <v>2.2199785298967817e-005</v>
+        <v>1.0245634607973694e-005</v>
       </c>
       <c r="S19">
-        <v>-0.0001161219795886391</v>
+        <v>-0.0001164418313308821</v>
       </c>
       <c r="T19">
-        <v>0.0040007514167836331</v>
+        <v>0.0039945073564953085</v>
       </c>
       <c r="U19">
-        <v>0.00090528745959765177</v>
+        <v>0.00090952958455816843</v>
       </c>
       <c r="V19">
-        <v>-6.7276626782212081e-005</v>
+        <v>-7.0992332157964518e-005</v>
       </c>
       <c r="W19">
-        <v>-7.182244561981712e-005</v>
+        <v>-8.0123487799195654e-005</v>
       </c>
       <c r="X19">
-        <v>0.00010395863221910326</v>
+        <v>-5.6196228945409779e-005</v>
       </c>
       <c r="Y19">
-        <v>0.00064489286383876538</v>
+        <v>0.00066630802387617502</v>
       </c>
     </row>
     <row r="20">
@@ -3878,76 +3878,76 @@
         <v>59</v>
       </c>
       <c r="B20" s="44">
-        <v>-0.055793136149141331</v>
+        <v>-0.059855633011205882</v>
       </c>
       <c r="C20">
-        <v>-4.8917685846798455e-006</v>
+        <v>-1.0300189624248086e-005</v>
       </c>
       <c r="D20">
-        <v>-3.6452887206750093e-005</v>
+        <v>-3.9094936917765527e-005</v>
       </c>
       <c r="E20">
-        <v>6.4132760511519159e-007</v>
+        <v>7.0738823975519637e-007</v>
       </c>
       <c r="F20">
-        <v>-2.6082402041990735e-005</v>
+        <v>-2.4286248399856664e-005</v>
       </c>
       <c r="G20">
-        <v>-9.5363102747571249e-006</v>
+        <v>-5.0205218557215076e-006</v>
       </c>
       <c r="H20">
-        <v>2.1724118246523613e-005</v>
+        <v>-1.0018622210449543e-006</v>
       </c>
       <c r="I20">
-        <v>2.4173416988282744e-005</v>
+        <v>-5.2729124418718007e-006</v>
       </c>
       <c r="J20">
-        <v>4.1764547889529131e-005</v>
+        <v>1.7919883683758102e-005</v>
       </c>
       <c r="K20">
-        <v>6.3803596491869189e-005</v>
+        <v>4.0688111772389779e-005</v>
       </c>
       <c r="L20">
-        <v>5.757026810524965e-005</v>
+        <v>3.2109616694534957e-005</v>
       </c>
       <c r="M20">
-        <v>6.9422958561764686e-005</v>
+        <v>5.4183179226284062e-005</v>
       </c>
       <c r="N20">
-        <v>3.3704327661159125e-005</v>
+        <v>1.0387359183996802e-005</v>
       </c>
       <c r="O20">
-        <v>7.3655288604050785e-005</v>
+        <v>4.8355250230264983e-005</v>
       </c>
       <c r="P20">
-        <v>-1.7679303037746201e-006</v>
+        <v>-1.3074680443933611e-005</v>
       </c>
       <c r="Q20">
-        <v>-5.3750126778896604e-005</v>
+        <v>-7.2677222202786928e-005</v>
       </c>
       <c r="R20">
-        <v>4.6974531191106571e-005</v>
+        <v>1.8844491050873891e-005</v>
       </c>
       <c r="S20">
-        <v>-0.0001383930010073337</v>
+        <v>-0.00013892495950608205</v>
       </c>
       <c r="T20">
-        <v>0.00090528745959765177</v>
+        <v>0.00090952958455816843</v>
       </c>
       <c r="U20">
-        <v>0.0050217568512442596</v>
+        <v>0.0050232979914455788</v>
       </c>
       <c r="V20">
-        <v>-3.4348301395933836e-005</v>
+        <v>-4.4740543315813707e-005</v>
       </c>
       <c r="W20">
-        <v>-8.7317659090298131e-005</v>
+        <v>-0.00010756429799058088</v>
       </c>
       <c r="X20">
-        <v>0.0002509161093790798</v>
+        <v>-5.5385040726977264e-005</v>
       </c>
       <c r="Y20">
-        <v>0.0023224973979459299</v>
+        <v>0.0023838481364170743</v>
       </c>
     </row>
     <row r="21">
@@ -3955,76 +3955,76 @@
         <v>60</v>
       </c>
       <c r="B21" s="46">
-        <v>0.40496674432956786</v>
+        <v>0.40951985210286718</v>
       </c>
       <c r="C21">
-        <v>-1.5824312400950164e-005</v>
+        <v>-9.8776665445880112e-006</v>
       </c>
       <c r="D21">
-        <v>-1.7332175635417779e-005</v>
+        <v>-1.2589456054451498e-005</v>
       </c>
       <c r="E21">
-        <v>-2.3512379681970598e-007</v>
+        <v>-3.6647406570890564e-007</v>
       </c>
       <c r="F21">
-        <v>-7.2753685744639403e-005</v>
+        <v>-6.1177138584190497e-005</v>
       </c>
       <c r="G21">
-        <v>-0.00042525604367541425</v>
+        <v>-0.00041648222479118634</v>
       </c>
       <c r="H21">
-        <v>0.00073795152092020035</v>
+        <v>0.0007685725367742027</v>
       </c>
       <c r="I21">
-        <v>0.00058969645155697976</v>
+        <v>0.00062122937902196957</v>
       </c>
       <c r="J21">
-        <v>0.00054118672022085011</v>
+        <v>0.0005694725589640362</v>
       </c>
       <c r="K21">
-        <v>0.00062968557862745991</v>
+        <v>0.00065737216048338692</v>
       </c>
       <c r="L21">
-        <v>0.00040779584259810454</v>
+        <v>0.00042793714238739233</v>
       </c>
       <c r="M21">
-        <v>0.00065669880127735831</v>
+        <v>0.000674869096085896</v>
       </c>
       <c r="N21">
-        <v>0.00062997862594279196</v>
+        <v>0.0006535184633649771</v>
       </c>
       <c r="O21">
-        <v>0.00071017730092825669</v>
+        <v>0.00074251961712835978</v>
       </c>
       <c r="P21">
-        <v>0.00076072411200987637</v>
+        <v>0.00079191835004788907</v>
       </c>
       <c r="Q21">
-        <v>0.00071215327505665994</v>
+        <v>0.00074727715013049286</v>
       </c>
       <c r="R21">
-        <v>0.00085679845633657235</v>
+        <v>0.00089375723726435531</v>
       </c>
       <c r="S21">
-        <v>-1.3825261228110944e-005</v>
+        <v>-1.3940265366807432e-005</v>
       </c>
       <c r="T21">
-        <v>-6.7276626782212081e-005</v>
+        <v>-7.0992332157964518e-005</v>
       </c>
       <c r="U21">
-        <v>-3.4348301395933836e-005</v>
+        <v>-4.4740543315813707e-005</v>
       </c>
       <c r="V21">
-        <v>0.0018861301850228236</v>
+        <v>0.0019080275910161829</v>
       </c>
       <c r="W21">
-        <v>0.00065959039418554319</v>
+        <v>0.00069022399816354597</v>
       </c>
       <c r="X21">
-        <v>0.00046317685470327814</v>
+        <v>0.00043171961229125828</v>
       </c>
       <c r="Y21">
-        <v>-4.8579953204957251e-005</v>
+        <v>-0.00013825023746867865</v>
       </c>
     </row>
     <row r="22">
@@ -4032,76 +4032,76 @@
         <v>61</v>
       </c>
       <c r="B22" s="48">
-        <v>0.25666732876247855</v>
+        <v>0.26309515882156476</v>
       </c>
       <c r="C22">
-        <v>2.5906171669126525e-005</v>
+        <v>3.4627830156438457e-005</v>
       </c>
       <c r="D22">
-        <v>9.715422726781775e-005</v>
+        <v>0.0001057553590540633</v>
       </c>
       <c r="E22">
-        <v>-3.202508576675674e-006</v>
+        <v>-3.4301520417611385e-006</v>
       </c>
       <c r="F22">
-        <v>-1.0445039848163383e-005</v>
+        <v>6.6877046789943139e-006</v>
       </c>
       <c r="G22">
-        <v>-0.00015439126567166526</v>
+        <v>-0.00014103805833221798</v>
       </c>
       <c r="H22">
-        <v>0.0014450055846210556</v>
+        <v>0.0014844645098649901</v>
       </c>
       <c r="I22">
-        <v>0.0013013865071150295</v>
+        <v>0.0013418053644588333</v>
       </c>
       <c r="J22">
-        <v>0.0012740909981960196</v>
+        <v>0.0013099897202201835</v>
       </c>
       <c r="K22">
-        <v>0.001264291855265273</v>
+        <v>0.0012946337991289398</v>
       </c>
       <c r="L22">
-        <v>0.0012564790722820499</v>
+        <v>0.0012847316493765741</v>
       </c>
       <c r="M22">
-        <v>0.0012853368104977303</v>
+        <v>0.0013110395515903521</v>
       </c>
       <c r="N22">
-        <v>0.001329891386379272</v>
+        <v>0.0013583066388588453</v>
       </c>
       <c r="O22">
-        <v>0.0013481071073372843</v>
+        <v>0.0013868547789416413</v>
       </c>
       <c r="P22">
-        <v>0.0014482603656574039</v>
+        <v>0.0014896280138059414</v>
       </c>
       <c r="Q22">
-        <v>0.0014125691723430116</v>
+        <v>0.0014632895012737675</v>
       </c>
       <c r="R22">
-        <v>0.0014883750314830585</v>
+        <v>0.0015374831280887949</v>
       </c>
       <c r="S22">
-        <v>1.0250522829824172e-005</v>
+        <v>1.0207193409467674e-005</v>
       </c>
       <c r="T22">
-        <v>-7.182244561981712e-005</v>
+        <v>-8.0123487799195654e-005</v>
       </c>
       <c r="U22">
-        <v>-8.7317659090298131e-005</v>
+        <v>-0.00010756429799058088</v>
       </c>
       <c r="V22">
-        <v>0.00065959039418554319</v>
+        <v>0.00069022399816354597</v>
       </c>
       <c r="W22">
-        <v>0.0042739470088409542</v>
+        <v>0.0043119752338681471</v>
       </c>
       <c r="X22">
-        <v>0.00077538220137592984</v>
+        <v>0.00066507668324857242</v>
       </c>
       <c r="Y22">
-        <v>-0.0022728966306490251</v>
+        <v>-0.0024197667005215464</v>
       </c>
     </row>
     <row r="23">
@@ -4109,76 +4109,76 @@
         <v>62</v>
       </c>
       <c r="B23" s="50">
-        <v>0.21305130596023092</v>
+        <v>0.14137730215235852</v>
       </c>
       <c r="C23">
-        <v>2.2893919529594258e-005</v>
+        <v>9.305646594547098e-005</v>
       </c>
       <c r="D23">
-        <v>-0.00028925674890907527</v>
+        <v>-6.6514137259568451e-005</v>
       </c>
       <c r="E23">
-        <v>6.6171393625453698e-006</v>
+        <v>1.2473459119589718e-006</v>
       </c>
       <c r="F23">
-        <v>-6.5074822922562458e-005</v>
+        <v>0.00011121288711122961</v>
       </c>
       <c r="G23">
-        <v>1.7996835095897187e-005</v>
+        <v>0.00011685243338232639</v>
       </c>
       <c r="H23">
-        <v>0.00099076631170471143</v>
+        <v>0.00074486311562003244</v>
       </c>
       <c r="I23">
-        <v>0.00090856082090092763</v>
+        <v>0.00071209907591048764</v>
       </c>
       <c r="J23">
-        <v>0.00087869778535027516</v>
+        <v>0.0006593671290352726</v>
       </c>
       <c r="K23">
-        <v>0.00080911798647472313</v>
+        <v>0.00061522110320758386</v>
       </c>
       <c r="L23">
-        <v>0.00085094929683886429</v>
+        <v>0.00061025379604819888</v>
       </c>
       <c r="M23">
-        <v>0.00076289681721374882</v>
+        <v>0.00050884816323414008</v>
       </c>
       <c r="N23">
-        <v>0.00086749109494471601</v>
+        <v>0.0005987517298693322</v>
       </c>
       <c r="O23">
-        <v>0.00094918758233899288</v>
+        <v>0.00071442841954395234</v>
       </c>
       <c r="P23">
-        <v>0.00092211717353658839</v>
+        <v>0.00074448058901216028</v>
       </c>
       <c r="Q23">
-        <v>0.00082741303640826869</v>
+        <v>0.00074209461309381649</v>
       </c>
       <c r="R23">
-        <v>0.0010150786098990403</v>
+        <v>0.00082502346876541172</v>
       </c>
       <c r="S23">
-        <v>-5.7989656202164848e-006</v>
+        <v>3.3458913281948145e-006</v>
       </c>
       <c r="T23">
-        <v>0.00010395863221910326</v>
+        <v>-5.6196228945409779e-005</v>
       </c>
       <c r="U23">
-        <v>0.0002509161093790798</v>
+        <v>-5.5385040726977264e-005</v>
       </c>
       <c r="V23">
-        <v>0.00046317685470327814</v>
+        <v>0.00043171961229125828</v>
       </c>
       <c r="W23">
-        <v>0.00077538220137592984</v>
+        <v>0.00066507668324857242</v>
       </c>
       <c r="X23">
-        <v>0.011617979337056251</v>
+        <v>0.0048196125849117805</v>
       </c>
       <c r="Y23">
-        <v>0.0021527424510600804</v>
+        <v>-0.00022391558354033282</v>
       </c>
     </row>
     <row r="24">
@@ -4186,76 +4186,76 @@
         <v>63</v>
       </c>
       <c r="B24" s="52">
-        <v>2.7558802264190057</v>
+        <v>2.7141400232299153</v>
       </c>
       <c r="C24">
-        <v>-0.0010355903812184026</v>
+        <v>-0.0010467990983319257</v>
       </c>
       <c r="D24">
-        <v>-0.11409029022333123</v>
+        <v>-0.11408708249946239</v>
       </c>
       <c r="E24">
-        <v>0.0028413931176680014</v>
+        <v>0.0028415250943395398</v>
       </c>
       <c r="F24">
-        <v>-0.00061097093425310854</v>
+        <v>-0.00060677992294312524</v>
       </c>
       <c r="G24">
-        <v>-0.0017068928893956858</v>
+        <v>-0.0017015524945483489</v>
       </c>
       <c r="H24">
-        <v>-0.0013647071269125017</v>
+        <v>-0.0015327863749833069</v>
       </c>
       <c r="I24">
-        <v>-0.0021257602710622347</v>
+        <v>-0.0023131031216598917</v>
       </c>
       <c r="J24">
-        <v>-0.0020080157220545699</v>
+        <v>-0.0021396886179511935</v>
       </c>
       <c r="K24">
-        <v>-0.00076465093317661537</v>
+        <v>-0.00085443346765786917</v>
       </c>
       <c r="L24">
-        <v>-0.0025277854504054558</v>
+        <v>-0.0026705539023951039</v>
       </c>
       <c r="M24">
-        <v>-0.0018360516625129317</v>
+        <v>-0.0020491136542521368</v>
       </c>
       <c r="N24">
-        <v>-0.0022839752853169274</v>
+        <v>-0.0024006673650027086</v>
       </c>
       <c r="O24">
-        <v>-0.0029928396134509894</v>
+        <v>-0.0031087019318487546</v>
       </c>
       <c r="P24">
-        <v>-0.0020947180758441467</v>
+        <v>-0.0022224268835616713</v>
       </c>
       <c r="Q24">
-        <v>-0.0026831384243376534</v>
+        <v>-0.0028293279057869311</v>
       </c>
       <c r="R24">
-        <v>-0.00083613873693785606</v>
+        <v>-0.00097595339758657141</v>
       </c>
       <c r="S24">
-        <v>-0.00013402273981353609</v>
+        <v>-0.00013352900393857913</v>
       </c>
       <c r="T24">
-        <v>0.00064489286383876538</v>
+        <v>0.00066630802387617502</v>
       </c>
       <c r="U24">
-        <v>0.0023224973979459299</v>
+        <v>0.0023838481364170743</v>
       </c>
       <c r="V24">
-        <v>-4.8579953204957251e-005</v>
+        <v>-0.00013825023746867865</v>
       </c>
       <c r="W24">
-        <v>-0.0022728966306490251</v>
+        <v>-0.0024197667005215464</v>
       </c>
       <c r="X24">
-        <v>0.0021527424510600804</v>
+        <v>-0.00022391558354033282</v>
       </c>
       <c r="Y24">
-        <v>1.1365224196549155</v>
+        <v>1.1365820986201245</v>
       </c>
     </row>
   </sheetData>
@@ -4364,91 +4364,91 @@
         <v>41</v>
       </c>
       <c r="B2" s="57">
-        <v>-0.21715866936676789</v>
+        <v>-0.21742470295789534</v>
       </c>
       <c r="C2">
-        <v>0.001744605176047704</v>
+        <v>0.0017391273308529796</v>
       </c>
       <c r="D2">
-        <v>-3.3527273501583339e-005</v>
+        <v>-3.437219059182325e-005</v>
       </c>
       <c r="E2">
-        <v>1.2966694387038911e-006</v>
+        <v>1.3295585449884713e-006</v>
       </c>
       <c r="F2">
-        <v>-0.00056013654492442896</v>
+        <v>-0.00054043443116396695</v>
       </c>
       <c r="G2">
-        <v>-0.0004478255040073157</v>
+        <v>-0.00042664364171915567</v>
       </c>
       <c r="H2">
-        <v>0.00020376917197370499</v>
+        <v>0.00019464987155914801</v>
       </c>
       <c r="I2">
-        <v>-5.3235335457980832e-005</v>
+        <v>-6.661282820566249e-005</v>
       </c>
       <c r="J2">
-        <v>0.00019587129925520853</v>
+        <v>0.0001913874495823146</v>
       </c>
       <c r="K2">
-        <v>0.0001841268582629523</v>
+        <v>0.00019840438150519338</v>
       </c>
       <c r="L2">
-        <v>0.00027321255975238908</v>
+        <v>0.00028472177252259119</v>
       </c>
       <c r="M2">
-        <v>-0.00014914193097558437</v>
+        <v>-0.00012184995214222654</v>
       </c>
       <c r="N2">
-        <v>-0.0002647249610810595</v>
+        <v>-0.00023369367434231689</v>
       </c>
       <c r="O2">
-        <v>-9.808718506288251e-006</v>
+        <v>1.4295501506872486e-005</v>
       </c>
       <c r="P2">
-        <v>-6.452426763047935e-005</v>
+        <v>-3.5354293973364126e-005</v>
       </c>
       <c r="Q2">
-        <v>0.00012895297864136962</v>
+        <v>0.00016000214546063935</v>
       </c>
       <c r="R2">
-        <v>-9.4142811264912312e-005</v>
+        <v>-6.860220925942735e-005</v>
       </c>
       <c r="S2">
-        <v>0.00055655211327724401</v>
+        <v>0.0005821765835903824</v>
       </c>
       <c r="T2">
-        <v>5.5753981385478816e-005</v>
+        <v>8.691297598797693e-005</v>
       </c>
       <c r="U2">
-        <v>-7.7955191953153237e-005</v>
+        <v>-4.8939286837537243e-005</v>
       </c>
       <c r="V2">
-        <v>-5.9756413666336755e-005</v>
+        <v>-1.9675608440710064e-005</v>
       </c>
       <c r="W2">
-        <v>-0.00030288055986193107</v>
+        <v>-0.00027611176422195796</v>
       </c>
       <c r="X2">
-        <v>6.4169728635986333e-005</v>
+        <v>6.4976732524300694e-005</v>
       </c>
       <c r="Y2">
-        <v>-0.00044296828210544129</v>
+        <v>-0.00047608647764882232</v>
       </c>
       <c r="Z2">
-        <v>-0.00032178015481110244</v>
+        <v>-0.00033434262502253357</v>
       </c>
       <c r="AA2">
-        <v>-0.00034049071355579208</v>
+        <v>-0.00031786032283763607</v>
       </c>
       <c r="AB2">
-        <v>-0.00022427449719754139</v>
+        <v>-0.0001990793614942202</v>
       </c>
       <c r="AC2">
-        <v>-0.00092059851594129848</v>
+        <v>-0.00018264908301718</v>
       </c>
       <c r="AD2">
-        <v>-0.0013847970364222772</v>
+        <v>-0.0014387676109756361</v>
       </c>
     </row>
     <row r="3">
@@ -4456,91 +4456,91 @@
         <v>42</v>
       </c>
       <c r="B3" s="59">
-        <v>-0.39651759994259356</v>
+        <v>-0.39973118845903238</v>
       </c>
       <c r="C3">
-        <v>-3.3527273501583339e-005</v>
+        <v>-3.437219059182325e-005</v>
       </c>
       <c r="D3">
-        <v>0.0021427903673508718</v>
+        <v>0.0021323357115012541</v>
       </c>
       <c r="E3">
-        <v>-4.0029505714518682e-005</v>
+        <v>-3.9808845099808576e-005</v>
       </c>
       <c r="F3">
-        <v>0.00025177391491668435</v>
+        <v>0.00024672138369611317</v>
       </c>
       <c r="G3">
-        <v>0.00022608885687059287</v>
+        <v>0.00023065410929652697</v>
       </c>
       <c r="H3">
-        <v>0.00043606244729480718</v>
+        <v>0.00044077545423759374</v>
       </c>
       <c r="I3">
-        <v>9.7937024018748017e-005</v>
+        <v>9.5998307349689507e-005</v>
       </c>
       <c r="J3">
-        <v>-0.00037143867699328828</v>
+        <v>-0.00036913456358594898</v>
       </c>
       <c r="K3">
-        <v>-0.00018844875983389884</v>
+        <v>-0.00013577032644896715</v>
       </c>
       <c r="L3">
-        <v>0.00020140732256225709</v>
+        <v>0.0002684354805675554</v>
       </c>
       <c r="M3">
-        <v>-1.4868692866879668e-005</v>
+        <v>-1.6205375349302026e-005</v>
       </c>
       <c r="N3">
-        <v>9.234075722103826e-005</v>
+        <v>9.415408627863435e-005</v>
       </c>
       <c r="O3">
-        <v>-9.9682993422930966e-005</v>
+        <v>-0.00011980043958486827</v>
       </c>
       <c r="P3">
-        <v>-0.00020322519838046962</v>
+        <v>-0.0002115628290429647</v>
       </c>
       <c r="Q3">
-        <v>-0.00017894502428724736</v>
+        <v>-0.00025080832820536126</v>
       </c>
       <c r="R3">
-        <v>-2.3881072141691828e-005</v>
+        <v>-1.9528031437242993e-005</v>
       </c>
       <c r="S3">
-        <v>-0.00030585564263751249</v>
+        <v>-0.00029671143525167049</v>
       </c>
       <c r="T3">
-        <v>-0.00025151484442306749</v>
+        <v>-0.00024743765242954754</v>
       </c>
       <c r="U3">
-        <v>-7.7819788718597183e-005</v>
+        <v>-7.5601721556298879e-005</v>
       </c>
       <c r="V3">
-        <v>0.000248807304958059</v>
+        <v>0.00024342748275127217</v>
       </c>
       <c r="W3">
-        <v>0.00018988179196845201</v>
+        <v>0.00019331437682851282</v>
       </c>
       <c r="X3">
-        <v>-5.7972278548507929e-005</v>
+        <v>-5.8824166971039715e-005</v>
       </c>
       <c r="Y3">
-        <v>0.00042539485440859417</v>
+        <v>0.00038841961198819025</v>
       </c>
       <c r="Z3">
-        <v>0.00036498210965349442</v>
+        <v>0.00034550188329664396</v>
       </c>
       <c r="AA3">
-        <v>-0.00041378895058555992</v>
+        <v>-0.00040071099743363772</v>
       </c>
       <c r="AB3">
-        <v>-0.00013596267946565724</v>
+        <v>-0.00012762425749894904</v>
       </c>
       <c r="AC3">
-        <v>0.00030506818082499249</v>
+        <v>0.00025602809545094331</v>
       </c>
       <c r="AD3">
-        <v>-0.026946079142751843</v>
+        <v>-0.026858820714371383</v>
       </c>
     </row>
     <row r="4">
@@ -4548,91 +4548,91 @@
         <v>43</v>
       </c>
       <c r="B4" s="61">
-        <v>0.0057268847725177111</v>
+        <v>0.0057888022055199648</v>
       </c>
       <c r="C4">
-        <v>1.2966694387038911e-006</v>
+        <v>1.3295585449884713e-006</v>
       </c>
       <c r="D4">
-        <v>-4.0029505714518682e-005</v>
+        <v>-3.9808845099808576e-005</v>
       </c>
       <c r="E4">
-        <v>7.5512711357292554e-007</v>
+        <v>7.5053176261962141e-007</v>
       </c>
       <c r="F4">
-        <v>-3.6410312999638156e-006</v>
+        <v>-3.5562412950510696e-006</v>
       </c>
       <c r="G4">
-        <v>-3.2966972108148694e-006</v>
+        <v>-3.3712155714472002e-006</v>
       </c>
       <c r="H4">
-        <v>-7.4030726300223951e-006</v>
+        <v>-7.4735401346243791e-006</v>
       </c>
       <c r="I4">
-        <v>-2.1523458505057683e-006</v>
+        <v>-2.095681905433835e-006</v>
       </c>
       <c r="J4">
-        <v>6.8742981732753471e-006</v>
+        <v>6.836515080407213e-006</v>
       </c>
       <c r="K4">
-        <v>4.0788235386134402e-006</v>
+        <v>3.0548019427742868e-006</v>
       </c>
       <c r="L4">
-        <v>-3.2463760413794476e-006</v>
+        <v>-4.5320119375305708e-006</v>
       </c>
       <c r="M4">
-        <v>-2.1226571421297923e-008</v>
+        <v>-9.1634611202966437e-008</v>
       </c>
       <c r="N4">
-        <v>-2.1691541774024792e-006</v>
+        <v>-2.2856990456732445e-006</v>
       </c>
       <c r="O4">
-        <v>1.5391485307339903e-006</v>
+        <v>1.8219691464452193e-006</v>
       </c>
       <c r="P4">
-        <v>3.6069093899931243e-006</v>
+        <v>3.6835251704600829e-006</v>
       </c>
       <c r="Q4">
-        <v>3.2732016847402052e-006</v>
+        <v>4.6460433463141776e-006</v>
       </c>
       <c r="R4">
-        <v>-1.3402354175103665e-007</v>
+        <v>-3.0017782629682653e-007</v>
       </c>
       <c r="S4">
-        <v>6.4648877400107587e-006</v>
+        <v>6.2137729379616849e-006</v>
       </c>
       <c r="T4">
-        <v>4.8165476837419346e-006</v>
+        <v>4.6418348206948574e-006</v>
       </c>
       <c r="U4">
-        <v>1.6262060839134038e-006</v>
+        <v>1.4848698575775708e-006</v>
       </c>
       <c r="V4">
-        <v>-5.0781623995771517e-006</v>
+        <v>-5.1035854318403023e-006</v>
       </c>
       <c r="W4">
-        <v>-3.4392800377659174e-006</v>
+        <v>-3.6053193943279922e-006</v>
       </c>
       <c r="X4">
-        <v>1.1400259419693429e-006</v>
+        <v>1.1572674605023024e-006</v>
       </c>
       <c r="Y4">
-        <v>-8.7960742900612058e-006</v>
+        <v>-8.0722297137839375e-006</v>
       </c>
       <c r="Z4">
-        <v>-7.6032255453834918e-006</v>
+        <v>-7.235209321050938e-006</v>
       </c>
       <c r="AA4">
-        <v>7.2744751576634716e-006</v>
+        <v>6.9458082233648166e-006</v>
       </c>
       <c r="AB4">
-        <v>1.9352393934263614e-006</v>
+        <v>1.6840575566798061e-006</v>
       </c>
       <c r="AC4">
-        <v>-5.2800947341681998e-006</v>
+        <v>-5.2505789576269153e-006</v>
       </c>
       <c r="AD4">
-        <v>0.00049641157626876067</v>
+        <v>0.00049454712347467983</v>
       </c>
     </row>
     <row r="5">
@@ -4640,91 +4640,91 @@
         <v>76</v>
       </c>
       <c r="B5" s="63">
-        <v>-0.13286656347420675</v>
+        <v>-0.13230295126764779</v>
       </c>
       <c r="C5">
-        <v>-0.00056013654492442896</v>
+        <v>-0.00054043443116396695</v>
       </c>
       <c r="D5">
-        <v>0.00025177391491668435</v>
+        <v>0.00024672138369611317</v>
       </c>
       <c r="E5">
-        <v>-3.6410312999638156e-006</v>
+        <v>-3.5562412950510696e-006</v>
       </c>
       <c r="F5">
-        <v>0.0028364857247036718</v>
+        <v>0.0028117753422945567</v>
       </c>
       <c r="G5">
-        <v>0.0024601684409628704</v>
+        <v>0.0024317930166949057</v>
       </c>
       <c r="H5">
-        <v>-0.0001116664281141115</v>
+        <v>-0.00010381921947602958</v>
       </c>
       <c r="I5">
-        <v>-0.00015558087509684698</v>
+        <v>-0.00013716549331970509</v>
       </c>
       <c r="J5">
-        <v>0.00013319939433749687</v>
+        <v>0.00014705950582071493</v>
       </c>
       <c r="K5">
-        <v>-0.00065483166450535008</v>
+        <v>-0.00065441531492795881</v>
       </c>
       <c r="L5">
-        <v>-0.00094884554453156852</v>
+        <v>-0.0009414231309553267</v>
       </c>
       <c r="M5">
-        <v>-0.00052281977331783132</v>
+        <v>-0.00053987057337635119</v>
       </c>
       <c r="N5">
-        <v>-0.00056206282714286299</v>
+        <v>-0.00058015028956883959</v>
       </c>
       <c r="O5">
-        <v>-0.00067544894813233039</v>
+        <v>-0.00070632518054655107</v>
       </c>
       <c r="P5">
-        <v>-0.00099155645602631111</v>
+        <v>-0.0010128533382708438</v>
       </c>
       <c r="Q5">
-        <v>-0.00074122644032078677</v>
+        <v>-0.00074067731350654009</v>
       </c>
       <c r="R5">
-        <v>-0.00084657510647237477</v>
+        <v>-0.00085492624073873233</v>
       </c>
       <c r="S5">
-        <v>-0.0012392140322610684</v>
+        <v>-0.0012455562694091051</v>
       </c>
       <c r="T5">
-        <v>-0.00078322041686731351</v>
+        <v>-0.00080605828042742923</v>
       </c>
       <c r="U5">
-        <v>-0.00036045509987020843</v>
+        <v>-0.00037858740168326879</v>
       </c>
       <c r="V5">
-        <v>-0.00046574207488261671</v>
+        <v>-0.00051258748280689093</v>
       </c>
       <c r="W5">
-        <v>-0.00028346299435504183</v>
+        <v>-0.00029680556774447494</v>
       </c>
       <c r="X5">
-        <v>-8.1689300042880105e-005</v>
+        <v>-8.2110906797003898e-005</v>
       </c>
       <c r="Y5">
-        <v>0.00029781497400764318</v>
+        <v>0.00033193486707643418</v>
       </c>
       <c r="Z5">
-        <v>0.00041466867353847042</v>
+        <v>0.00040504155709004193</v>
       </c>
       <c r="AA5">
-        <v>0.0005382775568378113</v>
+        <v>0.00052159728177028804</v>
       </c>
       <c r="AB5">
-        <v>-0.00017751568387027079</v>
+        <v>-0.00019345968367365414</v>
       </c>
       <c r="AC5">
-        <v>0.0012465082138351767</v>
+        <v>0.00036290090328815845</v>
       </c>
       <c r="AD5">
-        <v>-0.0032556389145149281</v>
+        <v>-0.0031676229425260903</v>
       </c>
     </row>
     <row r="6">
@@ -4732,91 +4732,91 @@
         <v>77</v>
       </c>
       <c r="B6" s="65">
-        <v>-0.27513927067387778</v>
+        <v>-0.27660615736639171</v>
       </c>
       <c r="C6">
-        <v>-0.0004478255040073157</v>
+        <v>-0.00042664364171915567</v>
       </c>
       <c r="D6">
-        <v>0.00022608885687059287</v>
+        <v>0.00023065410929652697</v>
       </c>
       <c r="E6">
-        <v>-3.2966972108148694e-006</v>
+        <v>-3.3712155714472002e-006</v>
       </c>
       <c r="F6">
-        <v>0.0024601684409628704</v>
+        <v>0.0024317930166949057</v>
       </c>
       <c r="G6">
-        <v>0.0095586650441585527</v>
+        <v>0.0096231817632503776</v>
       </c>
       <c r="H6">
-        <v>-0.00064059522011742937</v>
+        <v>-0.00062767943515373609</v>
       </c>
       <c r="I6">
-        <v>-0.00023100968852949631</v>
+        <v>-0.00020934305266257576</v>
       </c>
       <c r="J6">
-        <v>-0.00021812589380810148</v>
+        <v>-0.00020107601866268886</v>
       </c>
       <c r="K6">
-        <v>-0.00087503511445901239</v>
+        <v>-0.00087424749807960098</v>
       </c>
       <c r="L6">
-        <v>-0.0010551456968386414</v>
+        <v>-0.001026797326460863</v>
       </c>
       <c r="M6">
-        <v>-0.00087877513306407586</v>
+        <v>-0.00096249114512526966</v>
       </c>
       <c r="N6">
-        <v>-0.00037146438768003755</v>
+        <v>-0.00042707558337928136</v>
       </c>
       <c r="O6">
-        <v>-0.0011131117271727174</v>
+        <v>-0.0011969049259907701</v>
       </c>
       <c r="P6">
-        <v>-0.0012823846965279019</v>
+        <v>-0.0013432639610760628</v>
       </c>
       <c r="Q6">
-        <v>-0.001263947426588898</v>
+        <v>-0.0013253220665356226</v>
       </c>
       <c r="R6">
-        <v>-0.0016069528534080068</v>
+        <v>-0.0016564927924880403</v>
       </c>
       <c r="S6">
-        <v>-0.0018163804762692888</v>
+        <v>-0.0018783438318018624</v>
       </c>
       <c r="T6">
-        <v>-0.001084787388648241</v>
+        <v>-0.0011651509990863004</v>
       </c>
       <c r="U6">
-        <v>-0.0010921644123880322</v>
+        <v>-0.0011718772343099742</v>
       </c>
       <c r="V6">
-        <v>-0.00088007641819220052</v>
+        <v>-0.00099347223905786423</v>
       </c>
       <c r="W6">
-        <v>-0.0016839454708573189</v>
+        <v>-0.001778816795663345</v>
       </c>
       <c r="X6">
-        <v>-9.1759218800773737e-005</v>
+        <v>-9.2456415785086466e-005</v>
       </c>
       <c r="Y6">
-        <v>0.00046134185792364563</v>
+        <v>0.00046941345405632391</v>
       </c>
       <c r="Z6">
-        <v>0.00023131736780290595</v>
+        <v>0.0002212952569453498</v>
       </c>
       <c r="AA6">
-        <v>0.00029109246113433358</v>
+        <v>0.00023455848808348785</v>
       </c>
       <c r="AB6">
-        <v>-0.00078016100331416375</v>
+        <v>-0.00084840965801500322</v>
       </c>
       <c r="AC6">
-        <v>0.00096287797038103833</v>
+        <v>-4.6610187418628403e-005</v>
       </c>
       <c r="AD6">
-        <v>-0.002022223997550773</v>
+        <v>-0.0020123779576044706</v>
       </c>
     </row>
     <row r="7">
@@ -4824,91 +4824,91 @@
         <v>78</v>
       </c>
       <c r="B7" s="67">
-        <v>0.18367910229884188</v>
+        <v>0.18213117981889068</v>
       </c>
       <c r="C7">
-        <v>0.00020376917197370499</v>
+        <v>0.00019464987155914801</v>
       </c>
       <c r="D7">
-        <v>0.00043606244729480718</v>
+        <v>0.00044077545423759374</v>
       </c>
       <c r="E7">
-        <v>-7.4030726300223951e-006</v>
+        <v>-7.4735401346243791e-006</v>
       </c>
       <c r="F7">
-        <v>-0.0001116664281141115</v>
+        <v>-0.00010381921947602958</v>
       </c>
       <c r="G7">
-        <v>-0.00064059522011742937</v>
+        <v>-0.00062767943515373609</v>
       </c>
       <c r="H7">
-        <v>0.0021503364012176512</v>
+        <v>0.0021604762703094933</v>
       </c>
       <c r="I7">
-        <v>-0.0001505043788894704</v>
+        <v>-0.00015992983728524283</v>
       </c>
       <c r="J7">
-        <v>3.3367269775409539e-006</v>
+        <v>-2.0972613713714629e-006</v>
       </c>
       <c r="K7">
-        <v>0.00013773457706824153</v>
+        <v>0.00013914969052036211</v>
       </c>
       <c r="L7">
-        <v>0.00015024690091404815</v>
+        <v>0.00015025520099789819</v>
       </c>
       <c r="M7">
-        <v>-0.00076882272320018177</v>
+        <v>-0.00078882085337370002</v>
       </c>
       <c r="N7">
-        <v>-8.6289491455220513e-005</v>
+        <v>-9.1934631037546332e-005</v>
       </c>
       <c r="O7">
-        <v>-0.00037057801362125765</v>
+        <v>-0.00039423593603075957</v>
       </c>
       <c r="P7">
-        <v>-0.00046142683630648784</v>
+        <v>-0.00047772726849802378</v>
       </c>
       <c r="Q7">
-        <v>-0.00054835967203010431</v>
+        <v>-0.00054509294433923556</v>
       </c>
       <c r="R7">
-        <v>-0.00018716058691508328</v>
+        <v>-0.00019792836957004492</v>
       </c>
       <c r="S7">
-        <v>-0.00025938732519574433</v>
+        <v>-0.00027436484315977142</v>
       </c>
       <c r="T7">
-        <v>-0.00033003893803459959</v>
+        <v>-0.00034485827091860306</v>
       </c>
       <c r="U7">
-        <v>-0.00048842047964455654</v>
+        <v>-0.00050527044810335341</v>
       </c>
       <c r="V7">
-        <v>-0.00030990849664889412</v>
+        <v>-0.00032375390226934775</v>
       </c>
       <c r="W7">
-        <v>-0.00068332926587718885</v>
+        <v>-0.00070446898277532486</v>
       </c>
       <c r="X7">
-        <v>-8.7011166735024128e-006</v>
+        <v>-7.9776642754461136e-006</v>
       </c>
       <c r="Y7">
-        <v>-0.0002768966747274588</v>
+        <v>-0.0002871620745060194</v>
       </c>
       <c r="Z7">
-        <v>0.00010984877596511384</v>
+        <v>9.3228366997010685e-005</v>
       </c>
       <c r="AA7">
-        <v>-0.00045279409719744699</v>
+        <v>-0.0004621546032321038</v>
       </c>
       <c r="AB7">
-        <v>-0.00041806808959597881</v>
+        <v>-0.0004324905533191481</v>
       </c>
       <c r="AC7">
-        <v>-0.00082927178701539136</v>
+        <v>-0.00044257238583942667</v>
       </c>
       <c r="AD7">
-        <v>-0.006175967897320664</v>
+        <v>-0.0062372033290646551</v>
       </c>
     </row>
     <row r="8">
@@ -4916,91 +4916,91 @@
         <v>79</v>
       </c>
       <c r="B8" s="69">
-        <v>0.051941252679446083</v>
+        <v>0.049932737645264166</v>
       </c>
       <c r="C8">
-        <v>-5.3235335457980832e-005</v>
+        <v>-6.661282820566249e-005</v>
       </c>
       <c r="D8">
-        <v>9.7937024018748017e-005</v>
+        <v>9.5998307349689507e-005</v>
       </c>
       <c r="E8">
-        <v>-2.1523458505057683e-006</v>
+        <v>-2.095681905433835e-006</v>
       </c>
       <c r="F8">
-        <v>-0.00015558087509684698</v>
+        <v>-0.00013716549331970509</v>
       </c>
       <c r="G8">
-        <v>-0.00023100968852949631</v>
+        <v>-0.00020934305266257576</v>
       </c>
       <c r="H8">
-        <v>-0.0001505043788894704</v>
+        <v>-0.00015992983728524283</v>
       </c>
       <c r="I8">
-        <v>0.0003626510619320177</v>
+        <v>0.00035136485634539223</v>
       </c>
       <c r="J8">
-        <v>-0.00053360557564218283</v>
+        <v>-0.00054508802116344306</v>
       </c>
       <c r="K8">
-        <v>-9.2943219797320326e-005</v>
+        <v>-7.5253762224183137e-005</v>
       </c>
       <c r="L8">
-        <v>-9.1403229417907732e-005</v>
+        <v>-7.5007082049135913e-005</v>
       </c>
       <c r="M8">
-        <v>0.00021372345323283502</v>
+        <v>0.00023641083347411725</v>
       </c>
       <c r="N8">
-        <v>0.00011147108679180647</v>
+        <v>0.00013414906076533999</v>
       </c>
       <c r="O8">
-        <v>7.3634448536536302e-005</v>
+        <v>9.2910893726938244e-005</v>
       </c>
       <c r="P8">
-        <v>9.1260579496445096e-005</v>
+        <v>0.00010934181632256629</v>
       </c>
       <c r="Q8">
-        <v>9.1219024660235817e-005</v>
+        <v>6.9133405975335628e-005</v>
       </c>
       <c r="R8">
-        <v>0.0001963602679162181</v>
+        <v>0.00021628308089945137</v>
       </c>
       <c r="S8">
-        <v>5.8184997973119261e-005</v>
+        <v>7.7213697449518733e-005</v>
       </c>
       <c r="T8">
-        <v>4.7909561327761025e-005</v>
+        <v>7.2889171237782335e-005</v>
       </c>
       <c r="U8">
-        <v>0.00019034303831213161</v>
+        <v>0.00021334973461589551</v>
       </c>
       <c r="V8">
-        <v>3.5500914472902834e-005</v>
+        <v>9.3469124141004872e-005</v>
       </c>
       <c r="W8">
-        <v>0.00025535969374797219</v>
+        <v>0.00027506424775705662</v>
       </c>
       <c r="X8">
-        <v>-9.1607373875157673e-006</v>
+        <v>-8.9866495295515888e-006</v>
       </c>
       <c r="Y8">
-        <v>9.4084096334294846e-005</v>
+        <v>6.8042679064816459e-005</v>
       </c>
       <c r="Z8">
-        <v>6.9516724853600147e-005</v>
+        <v>6.0587076645444949e-005</v>
       </c>
       <c r="AA8">
-        <v>-5.4180356062105174e-005</v>
+        <v>-2.9458846697555819e-005</v>
       </c>
       <c r="AB8">
-        <v>4.1728441694810709e-005</v>
+        <v>6.4315249850045286e-005</v>
       </c>
       <c r="AC8">
-        <v>-0.00077951976627440721</v>
+        <v>-0.00013822516778159814</v>
       </c>
       <c r="AD8">
-        <v>-0.00093089067211116769</v>
+        <v>-0.0009560495568672815</v>
       </c>
     </row>
     <row r="9">
@@ -5008,91 +5008,91 @@
         <v>80</v>
       </c>
       <c r="B9" s="71">
-        <v>-0.26780770657003694</v>
+        <v>-0.26756945748287003</v>
       </c>
       <c r="C9">
-        <v>0.00019587129925520853</v>
+        <v>0.0001913874495823146</v>
       </c>
       <c r="D9">
-        <v>-0.00037143867699328828</v>
+        <v>-0.00036913456358594898</v>
       </c>
       <c r="E9">
-        <v>6.8742981732753471e-006</v>
+        <v>6.836515080407213e-006</v>
       </c>
       <c r="F9">
-        <v>0.00013319939433749687</v>
+        <v>0.00014705950582071493</v>
       </c>
       <c r="G9">
-        <v>-0.00021812589380810148</v>
+        <v>-0.00020107601866268886</v>
       </c>
       <c r="H9">
-        <v>3.3367269775409539e-006</v>
+        <v>-2.0972613713714629e-006</v>
       </c>
       <c r="I9">
-        <v>-0.00053360557564218283</v>
+        <v>-0.00054508802116344306</v>
       </c>
       <c r="J9">
-        <v>0.0033459103522783303</v>
+        <v>0.0033853318460588624</v>
       </c>
       <c r="K9">
-        <v>5.9134644950252892e-005</v>
+        <v>4.7127392802791376e-005</v>
       </c>
       <c r="L9">
-        <v>-1.9955914468079705e-005</v>
+        <v>-4.0315939008480099e-005</v>
       </c>
       <c r="M9">
-        <v>-0.00046274713269495648</v>
+        <v>-0.00046171432079609087</v>
       </c>
       <c r="N9">
-        <v>0.00024500832870281172</v>
+        <v>0.00025553822896362674</v>
       </c>
       <c r="O9">
-        <v>-9.0759942953571714e-005</v>
+        <v>-7.917363076938755e-005</v>
       </c>
       <c r="P9">
-        <v>-0.0001768017622656604</v>
+        <v>-0.00018150766490292723</v>
       </c>
       <c r="Q9">
-        <v>0.00013380935966043948</v>
+        <v>0.0001714304228199895</v>
       </c>
       <c r="R9">
-        <v>-0.00022426407948341774</v>
+        <v>-0.0002272672582829448</v>
       </c>
       <c r="S9">
-        <v>-0.00011117718650630471</v>
+        <v>-0.00011034665067511133</v>
       </c>
       <c r="T9">
-        <v>-0.00011369915076271902</v>
+        <v>-0.00011111481152825784</v>
       </c>
       <c r="U9">
-        <v>-0.00051440485620587485</v>
+        <v>-0.00051543616714001773</v>
       </c>
       <c r="V9">
-        <v>-0.00016970104313837934</v>
+        <v>-0.00016134224293845416</v>
       </c>
       <c r="W9">
-        <v>-0.00050360616746535211</v>
+        <v>-0.00050095224640280293</v>
       </c>
       <c r="X9">
-        <v>3.673166797329866e-005</v>
+        <v>3.7355555689726232e-005</v>
       </c>
       <c r="Y9">
-        <v>4.5520980033952278e-006</v>
+        <v>6.0154933508439583e-007</v>
       </c>
       <c r="Z9">
-        <v>-0.00018817889387134131</v>
+        <v>-0.00018333655285065814</v>
       </c>
       <c r="AA9">
-        <v>-3.3756505129463234e-005</v>
+        <v>-3.5141514432944845e-005</v>
       </c>
       <c r="AB9">
-        <v>-0.00012993645404362018</v>
+        <v>-0.0001305264997695137</v>
       </c>
       <c r="AC9">
-        <v>-0.00040061451013042552</v>
+        <v>-0.00016861853350639796</v>
       </c>
       <c r="AD9">
-        <v>0.0041393820025250475</v>
+        <v>0.0041022116317662796</v>
       </c>
     </row>
     <row r="10">
@@ -5100,91 +5100,91 @@
         <v>44</v>
       </c>
       <c r="B10" s="73">
-        <v>-0.29923487283216887</v>
+        <v>-0.29251467902670192</v>
       </c>
       <c r="C10">
-        <v>0.0001841268582629523</v>
+        <v>0.00019840438150519338</v>
       </c>
       <c r="D10">
-        <v>-0.00018844875983389884</v>
+        <v>-0.00013577032644896715</v>
       </c>
       <c r="E10">
-        <v>4.0788235386134402e-006</v>
+        <v>3.0548019427742868e-006</v>
       </c>
       <c r="F10">
-        <v>-0.00065483166450535008</v>
+        <v>-0.00065441531492795881</v>
       </c>
       <c r="G10">
-        <v>-0.00087503511445901239</v>
+        <v>-0.00087424749807960098</v>
       </c>
       <c r="H10">
-        <v>0.00013773457706824153</v>
+        <v>0.00013914969052036211</v>
       </c>
       <c r="I10">
-        <v>-9.2943219797320326e-005</v>
+        <v>-7.5253762224183137e-005</v>
       </c>
       <c r="J10">
-        <v>5.9134644950252892e-005</v>
+        <v>4.7127392802791376e-005</v>
       </c>
       <c r="K10">
-        <v>0.0039133130343177681</v>
+        <v>0.003802948433798096</v>
       </c>
       <c r="L10">
-        <v>0.0034679562778587025</v>
+        <v>0.0033418894821779115</v>
       </c>
       <c r="M10">
-        <v>-0.00036048080765640447</v>
+        <v>-0.00039826988848292241</v>
       </c>
       <c r="N10">
-        <v>-0.00036040950793239917</v>
+        <v>-0.00041631000965925129</v>
       </c>
       <c r="O10">
-        <v>-0.00075951844167168516</v>
+        <v>-0.0007699896531477568</v>
       </c>
       <c r="P10">
-        <v>-0.00030169586232326948</v>
+        <v>-0.00033849007728787309</v>
       </c>
       <c r="Q10">
-        <v>-0.00050803979778130451</v>
+        <v>-0.00038578045885747709</v>
       </c>
       <c r="R10">
-        <v>-0.00033600654796146523</v>
+        <v>-0.00039348043471889481</v>
       </c>
       <c r="S10">
-        <v>0.00023491068295171261</v>
+        <v>0.00016590060226850308</v>
       </c>
       <c r="T10">
-        <v>-0.00029076106028032457</v>
+        <v>-0.00034863732741485825</v>
       </c>
       <c r="U10">
-        <v>-0.00036031636519535243</v>
+        <v>-0.00042069437730262436</v>
       </c>
       <c r="V10">
-        <v>-0.00024029024359936127</v>
+        <v>-0.00028522632948149615</v>
       </c>
       <c r="W10">
-        <v>-0.00043291584001511885</v>
+        <v>-0.00049894790773069391</v>
       </c>
       <c r="X10">
-        <v>7.6064213868253154e-005</v>
+        <v>7.7384035381430184e-005</v>
       </c>
       <c r="Y10">
-        <v>-0.0010599507660143863</v>
+        <v>-0.00095769501423219512</v>
       </c>
       <c r="Z10">
-        <v>-0.0010256417521587293</v>
+        <v>-0.00097907707533994182</v>
       </c>
       <c r="AA10">
-        <v>-6.1493002479241668e-005</v>
+        <v>-0.00013337994466864809</v>
       </c>
       <c r="AB10">
-        <v>2.4791378281807924e-005</v>
+        <v>-4.5668465427433692e-005</v>
       </c>
       <c r="AC10">
-        <v>-4.9465223970228379e-005</v>
+        <v>-0.00065754759900779147</v>
       </c>
       <c r="AD10">
-        <v>-0.0016242457535629619</v>
+        <v>-0.0021589802621188566</v>
       </c>
     </row>
     <row r="11">
@@ -5192,91 +5192,91 @@
         <v>45</v>
       </c>
       <c r="B11" s="75">
-        <v>-0.3572115251437068</v>
+        <v>-0.35137092657186209</v>
       </c>
       <c r="C11">
-        <v>0.00027321255975238908</v>
+        <v>0.00028472177252259119</v>
       </c>
       <c r="D11">
-        <v>0.00020140732256225709</v>
+        <v>0.0002684354805675554</v>
       </c>
       <c r="E11">
-        <v>-3.2463760413794476e-006</v>
+        <v>-4.5320119375305708e-006</v>
       </c>
       <c r="F11">
-        <v>-0.00094884554453156852</v>
+        <v>-0.0009414231309553267</v>
       </c>
       <c r="G11">
-        <v>-0.0010551456968386414</v>
+        <v>-0.001026797326460863</v>
       </c>
       <c r="H11">
-        <v>0.00015024690091404815</v>
+        <v>0.00015025520099789819</v>
       </c>
       <c r="I11">
-        <v>-9.1403229417907732e-005</v>
+        <v>-7.5007082049135913e-005</v>
       </c>
       <c r="J11">
-        <v>-1.9955914468079705e-005</v>
+        <v>-4.0315939008480099e-005</v>
       </c>
       <c r="K11">
-        <v>0.0034679562778587025</v>
+        <v>0.0033418894821779115</v>
       </c>
       <c r="L11">
-        <v>0.005427551604274038</v>
+        <v>0.0052984206957326363</v>
       </c>
       <c r="M11">
-        <v>-0.00082704151343447499</v>
+        <v>-0.00091171834267591363</v>
       </c>
       <c r="N11">
-        <v>-0.00027459741552781405</v>
+        <v>-0.00036825236592238875</v>
       </c>
       <c r="O11">
-        <v>-0.0008617047656154465</v>
+        <v>-0.00090582666089675701</v>
       </c>
       <c r="P11">
-        <v>-0.00030312860479829521</v>
+        <v>-0.00036345465314200818</v>
       </c>
       <c r="Q11">
-        <v>-0.00075631427482164906</v>
+        <v>-0.00064077923724033703</v>
       </c>
       <c r="R11">
-        <v>-7.941280410501294e-005</v>
+        <v>-0.00016897275317119531</v>
       </c>
       <c r="S11">
-        <v>0.00021799257526608685</v>
+        <v>0.00011150703690077337</v>
       </c>
       <c r="T11">
-        <v>-0.0004751171259604491</v>
+        <v>-0.00057216670764221906</v>
       </c>
       <c r="U11">
-        <v>-0.00065281608983242846</v>
+        <v>-0.0007593125770759692</v>
       </c>
       <c r="V11">
-        <v>-0.00029504910637672825</v>
+        <v>-0.00036869207399091474</v>
       </c>
       <c r="W11">
-        <v>-0.00041651950109381365</v>
+        <v>-0.0005335111358318929</v>
       </c>
       <c r="X11">
-        <v>0.00010142186696377223</v>
+        <v>0.00010324933184171247</v>
       </c>
       <c r="Y11">
-        <v>-0.001032209932942271</v>
+        <v>-0.00093885212478094057</v>
       </c>
       <c r="Z11">
-        <v>-0.00044666980520720654</v>
+        <v>-0.00039351063802412379</v>
       </c>
       <c r="AA11">
-        <v>-0.00063682123442268469</v>
+        <v>-0.00074209015227016592</v>
       </c>
       <c r="AB11">
-        <v>3.8440129129652871e-005</v>
+        <v>-7.37141077118555e-005</v>
       </c>
       <c r="AC11">
-        <v>-0.000731149807846121</v>
+        <v>-0.0012566007749082032</v>
       </c>
       <c r="AD11">
-        <v>-0.0068935888604638659</v>
+        <v>-0.0075681472674728294</v>
       </c>
     </row>
     <row r="12">
@@ -5284,91 +5284,91 @@
         <v>46</v>
       </c>
       <c r="B12" s="77">
-        <v>-0.034474157114101386</v>
+        <v>-0.014982550661407938</v>
       </c>
       <c r="C12">
-        <v>-0.00014914193097558437</v>
+        <v>-0.00012184995214222654</v>
       </c>
       <c r="D12">
-        <v>-1.4868692866879668e-005</v>
+        <v>-1.6205375349302026e-005</v>
       </c>
       <c r="E12">
-        <v>-2.1226571421297923e-008</v>
+        <v>-9.1634611202966437e-008</v>
       </c>
       <c r="F12">
-        <v>-0.00052281977331783132</v>
+        <v>-0.00053987057337635119</v>
       </c>
       <c r="G12">
-        <v>-0.00087877513306407586</v>
+        <v>-0.00096249114512526966</v>
       </c>
       <c r="H12">
-        <v>-0.00076882272320018177</v>
+        <v>-0.00078882085337370002</v>
       </c>
       <c r="I12">
-        <v>0.00021372345323283502</v>
+        <v>0.00023641083347411725</v>
       </c>
       <c r="J12">
-        <v>-0.00046274713269495648</v>
+        <v>-0.00046171432079609087</v>
       </c>
       <c r="K12">
-        <v>-0.00036048080765640447</v>
+        <v>-0.00039826988848292241</v>
       </c>
       <c r="L12">
-        <v>-0.00082704151343447499</v>
+        <v>-0.00091171834267591363</v>
       </c>
       <c r="M12">
-        <v>0.012169757925551491</v>
+        <v>0.012575810147575335</v>
       </c>
       <c r="N12">
-        <v>0.0042253171625875321</v>
+        <v>0.0045350130728454476</v>
       </c>
       <c r="O12">
-        <v>0.004312865773555042</v>
+        <v>0.0046904251713879687</v>
       </c>
       <c r="P12">
-        <v>0.0042793501458941192</v>
+        <v>0.0045882049803929667</v>
       </c>
       <c r="Q12">
-        <v>0.0042072019961639524</v>
+        <v>0.0046534600545807894</v>
       </c>
       <c r="R12">
-        <v>0.004154509096823634</v>
+        <v>0.0044348988767802314</v>
       </c>
       <c r="S12">
-        <v>0.0042071856482081898</v>
+        <v>0.0045230537608742559</v>
       </c>
       <c r="T12">
-        <v>0.0043501356815151904</v>
+        <v>0.0047084949893931687</v>
       </c>
       <c r="U12">
-        <v>0.0044282720502237544</v>
+        <v>0.0048146355667414821</v>
       </c>
       <c r="V12">
-        <v>0.0044191319293576514</v>
+        <v>0.0047593489821810718</v>
       </c>
       <c r="W12">
-        <v>0.0044527280323268421</v>
+        <v>0.0048594057673663083</v>
       </c>
       <c r="X12">
-        <v>-2.6173596611608229e-005</v>
+        <v>-2.7296910969367382e-005</v>
       </c>
       <c r="Y12">
-        <v>-0.00055021652696677107</v>
+        <v>-0.00042789889936725419</v>
       </c>
       <c r="Z12">
-        <v>8.0644674639837426e-005</v>
+        <v>9.4161069373627985e-005</v>
       </c>
       <c r="AA12">
-        <v>0.0015130080778286263</v>
+        <v>0.0016779255556667555</v>
       </c>
       <c r="AB12">
-        <v>0.0030864910508118801</v>
+        <v>0.003356192975299304</v>
       </c>
       <c r="AC12">
-        <v>0.0033274646089603123</v>
+        <v>0.0030666609388244983</v>
       </c>
       <c r="AD12">
-        <v>-0.002527988945701293</v>
+        <v>-0.0028055517791006949</v>
       </c>
     </row>
     <row r="13">
@@ -5376,91 +5376,91 @@
         <v>47</v>
       </c>
       <c r="B13" s="79">
-        <v>-0.09949714041070773</v>
+        <v>-0.082965144650010703</v>
       </c>
       <c r="C13">
-        <v>-0.0002647249610810595</v>
+        <v>-0.00023369367434231689</v>
       </c>
       <c r="D13">
-        <v>9.234075722103826e-005</v>
+        <v>9.415408627863435e-005</v>
       </c>
       <c r="E13">
-        <v>-2.1691541774024792e-006</v>
+        <v>-2.2856990456732445e-006</v>
       </c>
       <c r="F13">
-        <v>-0.00056206282714286299</v>
+        <v>-0.00058015028956883959</v>
       </c>
       <c r="G13">
-        <v>-0.00037146438768003755</v>
+        <v>-0.00042707558337928136</v>
       </c>
       <c r="H13">
-        <v>-8.6289491455220513e-005</v>
+        <v>-9.1934631037546332e-005</v>
       </c>
       <c r="I13">
-        <v>0.00011147108679180647</v>
+        <v>0.00013414906076533999</v>
       </c>
       <c r="J13">
-        <v>0.00024500832870281172</v>
+        <v>0.00025553822896362674</v>
       </c>
       <c r="K13">
-        <v>-0.00036040950793239917</v>
+        <v>-0.00041631000965925129</v>
       </c>
       <c r="L13">
-        <v>-0.00027459741552781405</v>
+        <v>-0.00036825236592238875</v>
       </c>
       <c r="M13">
-        <v>0.0042253171625875321</v>
+        <v>0.0045350130728454476</v>
       </c>
       <c r="N13">
-        <v>0.0073649117743509974</v>
+        <v>0.0076054265346772549</v>
       </c>
       <c r="O13">
-        <v>0.0041282458943980322</v>
+        <v>0.0044224389548158955</v>
       </c>
       <c r="P13">
-        <v>0.0040775223851324989</v>
+        <v>0.0043165821841610131</v>
       </c>
       <c r="Q13">
-        <v>0.0040220874885596248</v>
+        <v>0.0043905322776606973</v>
       </c>
       <c r="R13">
-        <v>0.0039921357618860056</v>
+        <v>0.0042081781869454399</v>
       </c>
       <c r="S13">
-        <v>0.0041143739752187896</v>
+        <v>0.0043575544818940416</v>
       </c>
       <c r="T13">
-        <v>0.0042127744566387206</v>
+        <v>0.0044866887969909289</v>
       </c>
       <c r="U13">
-        <v>0.0042141080723935593</v>
+        <v>0.0045105089881673577</v>
       </c>
       <c r="V13">
-        <v>0.0042943043592783975</v>
+        <v>0.0045291799378279858</v>
       </c>
       <c r="W13">
-        <v>0.0041614164523188502</v>
+        <v>0.0044745512719364527</v>
       </c>
       <c r="X13">
-        <v>4.5567323935269307e-005</v>
+        <v>4.4701602354527739e-005</v>
       </c>
       <c r="Y13">
-        <v>-0.00068446884740063125</v>
+        <v>-0.00058029005612368417</v>
       </c>
       <c r="Z13">
-        <v>0.00034508168083520886</v>
+        <v>0.00036163713090229979</v>
       </c>
       <c r="AA13">
-        <v>0.00097807242301378716</v>
+        <v>0.0010846299012199591</v>
       </c>
       <c r="AB13">
-        <v>0.0030660498330441492</v>
+        <v>0.003255423572251039</v>
       </c>
       <c r="AC13">
-        <v>0.0028775755304505371</v>
+        <v>0.0023906816936546636</v>
       </c>
       <c r="AD13">
-        <v>-0.0051001186682699167</v>
+        <v>-0.0053261825802646632</v>
       </c>
     </row>
     <row r="14">
@@ -5468,91 +5468,91 @@
         <v>48</v>
       </c>
       <c r="B14" s="81">
-        <v>-0.12113241614383058</v>
+        <v>-0.1041807206918906</v>
       </c>
       <c r="C14">
-        <v>-9.808718506288251e-006</v>
+        <v>1.4295501506872486e-005</v>
       </c>
       <c r="D14">
-        <v>-9.9682993422930966e-005</v>
+        <v>-0.00011980043958486827</v>
       </c>
       <c r="E14">
-        <v>1.5391485307339903e-006</v>
+        <v>1.8219691464452193e-006</v>
       </c>
       <c r="F14">
-        <v>-0.00067544894813233039</v>
+        <v>-0.00070632518054655107</v>
       </c>
       <c r="G14">
-        <v>-0.0011131117271727174</v>
+        <v>-0.0011969049259907701</v>
       </c>
       <c r="H14">
-        <v>-0.00037057801362125765</v>
+        <v>-0.00039423593603075957</v>
       </c>
       <c r="I14">
-        <v>7.3634448536536302e-005</v>
+        <v>9.2910893726938244e-005</v>
       </c>
       <c r="J14">
-        <v>-9.0759942953571714e-005</v>
+        <v>-7.917363076938755e-005</v>
       </c>
       <c r="K14">
-        <v>-0.00075951844167168516</v>
+        <v>-0.0007699896531477568</v>
       </c>
       <c r="L14">
-        <v>-0.0008617047656154465</v>
+        <v>-0.00090582666089675701</v>
       </c>
       <c r="M14">
-        <v>0.004312865773555042</v>
+        <v>0.0046904251713879687</v>
       </c>
       <c r="N14">
-        <v>0.0041282458943980322</v>
+        <v>0.0044224389548158955</v>
       </c>
       <c r="O14">
-        <v>0.0077028033229510021</v>
+        <v>0.0080442038385633175</v>
       </c>
       <c r="P14">
-        <v>0.0041595229145452283</v>
+        <v>0.0044520036531653659</v>
       </c>
       <c r="Q14">
-        <v>0.0040972918000303496</v>
+        <v>0.0045022143036793274</v>
       </c>
       <c r="R14">
-        <v>0.0040267585665095876</v>
+        <v>0.0042972103391391223</v>
       </c>
       <c r="S14">
-        <v>0.0041438542434949297</v>
+        <v>0.0044476507259823723</v>
       </c>
       <c r="T14">
-        <v>0.0042265028574685441</v>
+        <v>0.0045671959469540174</v>
       </c>
       <c r="U14">
-        <v>0.0042843707910139349</v>
+        <v>0.0046515206507577109</v>
       </c>
       <c r="V14">
-        <v>0.0043317842468419444</v>
+        <v>0.004613674083160671</v>
       </c>
       <c r="W14">
-        <v>0.0043091500198555524</v>
+        <v>0.0046977356782586036</v>
       </c>
       <c r="X14">
-        <v>3.0487396917418036e-005</v>
+        <v>2.8108409458646889e-005</v>
       </c>
       <c r="Y14">
-        <v>-0.00014111157268094604</v>
+        <v>-2.1160591212731651e-005</v>
       </c>
       <c r="Z14">
-        <v>0.00075071251600452096</v>
+        <v>0.00073622848621853322</v>
       </c>
       <c r="AA14">
-        <v>0.00096782346345637097</v>
+        <v>0.0011231685314784146</v>
       </c>
       <c r="AB14">
-        <v>0.0028869079334501507</v>
+        <v>0.0031443989857716046</v>
       </c>
       <c r="AC14">
-        <v>0.0030908922112620257</v>
+        <v>0.0029913734302788137</v>
       </c>
       <c r="AD14">
-        <v>-0.0019807408575671119</v>
+        <v>-0.0019888358961703922</v>
       </c>
     </row>
     <row r="15">
@@ -5560,91 +5560,91 @@
         <v>49</v>
       </c>
       <c r="B15" s="83">
-        <v>-0.22747381140400053</v>
+        <v>-0.21265226081933869</v>
       </c>
       <c r="C15">
-        <v>-6.452426763047935e-005</v>
+        <v>-3.5354293973364126e-005</v>
       </c>
       <c r="D15">
-        <v>-0.00020322519838046962</v>
+        <v>-0.0002115628290429647</v>
       </c>
       <c r="E15">
-        <v>3.6069093899931243e-006</v>
+        <v>3.6835251704600829e-006</v>
       </c>
       <c r="F15">
-        <v>-0.00099155645602631111</v>
+        <v>-0.0010128533382708438</v>
       </c>
       <c r="G15">
-        <v>-0.0012823846965279019</v>
+        <v>-0.0013432639610760628</v>
       </c>
       <c r="H15">
-        <v>-0.00046142683630648784</v>
+        <v>-0.00047772726849802378</v>
       </c>
       <c r="I15">
-        <v>9.1260579496445096e-005</v>
+        <v>0.00010934181632256629</v>
       </c>
       <c r="J15">
-        <v>-0.0001768017622656604</v>
+        <v>-0.00018150766490292723</v>
       </c>
       <c r="K15">
-        <v>-0.00030169586232326948</v>
+        <v>-0.00033849007728787309</v>
       </c>
       <c r="L15">
-        <v>-0.00030312860479829521</v>
+        <v>-0.00036345465314200818</v>
       </c>
       <c r="M15">
-        <v>0.0042793501458941192</v>
+        <v>0.0045882049803929667</v>
       </c>
       <c r="N15">
-        <v>0.0040775223851324989</v>
+        <v>0.0043165821841610131</v>
       </c>
       <c r="O15">
-        <v>0.0041595229145452283</v>
+        <v>0.0044520036531653659</v>
       </c>
       <c r="P15">
-        <v>0.0092705529411186184</v>
+        <v>0.0095138692415450837</v>
       </c>
       <c r="Q15">
-        <v>0.0040634702647367269</v>
+        <v>0.0044086711328022408</v>
       </c>
       <c r="R15">
-        <v>0.0040203104407566456</v>
+        <v>0.0042397972569410353</v>
       </c>
       <c r="S15">
-        <v>0.0041527283263022999</v>
+        <v>0.0043989484434733914</v>
       </c>
       <c r="T15">
-        <v>0.0042242024184902787</v>
+        <v>0.0045009948594165478</v>
       </c>
       <c r="U15">
-        <v>0.0042735254891132883</v>
+        <v>0.0045726214624139047</v>
       </c>
       <c r="V15">
-        <v>0.0042759293755272312</v>
+        <v>0.00450802285105034</v>
       </c>
       <c r="W15">
-        <v>0.0042781950188496998</v>
+        <v>0.0045935003068158006</v>
       </c>
       <c r="X15">
-        <v>2.010138043315895e-005</v>
+        <v>1.9353977542898898e-005</v>
       </c>
       <c r="Y15">
-        <v>-0.00066274084255088538</v>
+        <v>-0.00056536816762100834</v>
       </c>
       <c r="Z15">
-        <v>-9.1078226737989574e-005</v>
+        <v>-7.2904262456958014e-005</v>
       </c>
       <c r="AA15">
-        <v>0.001145147547885363</v>
+        <v>0.0012610586789822535</v>
       </c>
       <c r="AB15">
-        <v>0.0027156095167048108</v>
+        <v>0.0029130535634169447</v>
       </c>
       <c r="AC15">
-        <v>0.0026184310347745093</v>
+        <v>0.0023993898952658424</v>
       </c>
       <c r="AD15">
-        <v>-0.00061088671844520149</v>
+        <v>-0.00072268150820662411</v>
       </c>
     </row>
     <row r="16">
@@ -5652,91 +5652,91 @@
         <v>50</v>
       </c>
       <c r="B16" s="85">
-        <v>-0.10638240175814619</v>
+        <v>-0.09862677657341555</v>
       </c>
       <c r="C16">
-        <v>0.00012895297864136962</v>
+        <v>0.00016000214546063935</v>
       </c>
       <c r="D16">
-        <v>-0.00017894502428724736</v>
+        <v>-0.00025080832820536126</v>
       </c>
       <c r="E16">
-        <v>3.2732016847402052e-006</v>
+        <v>4.6460433463141776e-006</v>
       </c>
       <c r="F16">
-        <v>-0.00074122644032078677</v>
+        <v>-0.00074067731350654009</v>
       </c>
       <c r="G16">
-        <v>-0.001263947426588898</v>
+        <v>-0.0013253220665356226</v>
       </c>
       <c r="H16">
-        <v>-0.00054835967203010431</v>
+        <v>-0.00054509294433923556</v>
       </c>
       <c r="I16">
-        <v>9.1219024660235817e-005</v>
+        <v>6.9133405975335628e-005</v>
       </c>
       <c r="J16">
-        <v>0.00013380935966043948</v>
+        <v>0.0001714304228199895</v>
       </c>
       <c r="K16">
-        <v>-0.00050803979778130451</v>
+        <v>-0.00038578045885747709</v>
       </c>
       <c r="L16">
-        <v>-0.00075631427482164906</v>
+        <v>-0.00064077923724033703</v>
       </c>
       <c r="M16">
-        <v>0.0042072019961639524</v>
+        <v>0.0046534600545807894</v>
       </c>
       <c r="N16">
-        <v>0.0040220874885596248</v>
+        <v>0.0043905322776606973</v>
       </c>
       <c r="O16">
-        <v>0.0040972918000303496</v>
+        <v>0.0045022143036793274</v>
       </c>
       <c r="P16">
-        <v>0.0040634702647367269</v>
+        <v>0.0044086711328022408</v>
       </c>
       <c r="Q16">
-        <v>0.0093099242681106819</v>
+        <v>0.0095417611881530341</v>
       </c>
       <c r="R16">
-        <v>0.0039412299365273878</v>
+        <v>0.0042910118320903246</v>
       </c>
       <c r="S16">
-        <v>0.0040231583809077166</v>
+        <v>0.0044144150404542551</v>
       </c>
       <c r="T16">
-        <v>0.0041064913081218521</v>
+        <v>0.0045379028693302726</v>
       </c>
       <c r="U16">
-        <v>0.0041521592806043964</v>
+        <v>0.0046080970335882045</v>
       </c>
       <c r="V16">
-        <v>0.0041918443359133572</v>
+        <v>0.0045053938694727055</v>
       </c>
       <c r="W16">
-        <v>0.0041987047307523052</v>
+        <v>0.0046820510233839333</v>
       </c>
       <c r="X16">
-        <v>4.1881822060358033e-005</v>
+        <v>3.2859137385277571e-005</v>
       </c>
       <c r="Y16">
-        <v>-5.3478462916410206e-005</v>
+        <v>-6.7596738570274446e-005</v>
       </c>
       <c r="Z16">
-        <v>-0.00029825262597322696</v>
+        <v>-0.00027606992554081965</v>
       </c>
       <c r="AA16">
-        <v>0.00047956674769879335</v>
+        <v>0.00074269452899958666</v>
       </c>
       <c r="AB16">
-        <v>0.0027192047524042763</v>
+        <v>0.0030752207612426384</v>
       </c>
       <c r="AC16">
-        <v>0.0027508966878814481</v>
+        <v>0.0039166079477502402</v>
       </c>
       <c r="AD16">
-        <v>-0.0013033284632634292</v>
+        <v>-0.00084296130571874951</v>
       </c>
     </row>
     <row r="17">
@@ -5744,91 +5744,91 @@
         <v>51</v>
       </c>
       <c r="B17" s="87">
-        <v>-0.1264483039806793</v>
+        <v>-0.11116471479288244</v>
       </c>
       <c r="C17">
-        <v>-9.4142811264912312e-005</v>
+        <v>-6.860220925942735e-005</v>
       </c>
       <c r="D17">
-        <v>-2.3881072141691828e-005</v>
+        <v>-1.9528031437242993e-005</v>
       </c>
       <c r="E17">
-        <v>-1.3402354175103665e-007</v>
+        <v>-3.0017782629682653e-007</v>
       </c>
       <c r="F17">
-        <v>-0.00084657510647237477</v>
+        <v>-0.00085492624073873233</v>
       </c>
       <c r="G17">
-        <v>-0.0016069528534080068</v>
+        <v>-0.0016564927924880403</v>
       </c>
       <c r="H17">
-        <v>-0.00018716058691508328</v>
+        <v>-0.00019792836957004492</v>
       </c>
       <c r="I17">
-        <v>0.0001963602679162181</v>
+        <v>0.00021628308089945137</v>
       </c>
       <c r="J17">
-        <v>-0.00022426407948341774</v>
+        <v>-0.0002272672582829448</v>
       </c>
       <c r="K17">
-        <v>-0.00033600654796146523</v>
+        <v>-0.00039348043471889481</v>
       </c>
       <c r="L17">
-        <v>-7.941280410501294e-005</v>
+        <v>-0.00016897275317119531</v>
       </c>
       <c r="M17">
-        <v>0.004154509096823634</v>
+        <v>0.0044348988767802314</v>
       </c>
       <c r="N17">
-        <v>0.0039921357618860056</v>
+        <v>0.0042081781869454399</v>
       </c>
       <c r="O17">
-        <v>0.0040267585665095876</v>
+        <v>0.0042972103391391223</v>
       </c>
       <c r="P17">
-        <v>0.0040203104407566456</v>
+        <v>0.0042397972569410353</v>
       </c>
       <c r="Q17">
-        <v>0.0039412299365273878</v>
+        <v>0.0042910118320903246</v>
       </c>
       <c r="R17">
-        <v>0.0079604465103370031</v>
+        <v>0.0081658317359612036</v>
       </c>
       <c r="S17">
-        <v>0.0040487130545941337</v>
+        <v>0.0042676722618835141</v>
       </c>
       <c r="T17">
-        <v>0.0041313667866062186</v>
+        <v>0.0043801400896612006</v>
       </c>
       <c r="U17">
-        <v>0.0041572156336784748</v>
+        <v>0.0044269753919717629</v>
       </c>
       <c r="V17">
-        <v>0.0041965661692203162</v>
+        <v>0.0044062571336844717</v>
       </c>
       <c r="W17">
-        <v>0.0041152328301060975</v>
+        <v>0.0044005652462512992</v>
       </c>
       <c r="X17">
-        <v>6.355929796396766e-006</v>
+        <v>5.0345562074083708e-006</v>
       </c>
       <c r="Y17">
-        <v>-0.0004272348586474824</v>
+        <v>-0.00031891859737965622</v>
       </c>
       <c r="Z17">
-        <v>0.00062771686507581464</v>
+        <v>0.00065734568355558728</v>
       </c>
       <c r="AA17">
-        <v>0.00095984775203105006</v>
+        <v>0.0010562586534860526</v>
       </c>
       <c r="AB17">
-        <v>0.0026527782052546832</v>
+        <v>0.0028242397581575837</v>
       </c>
       <c r="AC17">
-        <v>0.0023052377225684017</v>
+        <v>0.0020217654522131359</v>
       </c>
       <c r="AD17">
-        <v>-0.0026557403313212215</v>
+        <v>-0.0028785844740984046</v>
       </c>
     </row>
     <row r="18">
@@ -5836,91 +5836,91 @@
         <v>52</v>
       </c>
       <c r="B18" s="89">
-        <v>-0.13817586520434658</v>
+        <v>-0.12131934594358938</v>
       </c>
       <c r="C18">
-        <v>0.00055655211327724401</v>
+        <v>0.0005821765835903824</v>
       </c>
       <c r="D18">
-        <v>-0.00030585564263751249</v>
+        <v>-0.00029671143525167049</v>
       </c>
       <c r="E18">
-        <v>6.4648877400107587e-006</v>
+        <v>6.2137729379616849e-006</v>
       </c>
       <c r="F18">
-        <v>-0.0012392140322610684</v>
+        <v>-0.0012455562694091051</v>
       </c>
       <c r="G18">
-        <v>-0.0018163804762692888</v>
+        <v>-0.0018783438318018624</v>
       </c>
       <c r="H18">
-        <v>-0.00025938732519574433</v>
+        <v>-0.00027436484315977142</v>
       </c>
       <c r="I18">
-        <v>5.8184997973119261e-005</v>
+        <v>7.7213697449518733e-005</v>
       </c>
       <c r="J18">
-        <v>-0.00011117718650630471</v>
+        <v>-0.00011034665067511133</v>
       </c>
       <c r="K18">
-        <v>0.00023491068295171261</v>
+        <v>0.00016590060226850308</v>
       </c>
       <c r="L18">
-        <v>0.00021799257526608685</v>
+        <v>0.00011150703690077337</v>
       </c>
       <c r="M18">
-        <v>0.0042071856482081898</v>
+        <v>0.0045230537608742559</v>
       </c>
       <c r="N18">
-        <v>0.0041143739752187896</v>
+        <v>0.0043575544818940416</v>
       </c>
       <c r="O18">
-        <v>0.0041438542434949297</v>
+        <v>0.0044476507259823723</v>
       </c>
       <c r="P18">
-        <v>0.0041527283263022999</v>
+        <v>0.0043989484434733914</v>
       </c>
       <c r="Q18">
-        <v>0.0040231583809077166</v>
+        <v>0.0044144150404542551</v>
       </c>
       <c r="R18">
-        <v>0.0040487130545941337</v>
+        <v>0.0042676722618835141</v>
       </c>
       <c r="S18">
-        <v>0.0083292554531262924</v>
+        <v>0.0085851973349125102</v>
       </c>
       <c r="T18">
-        <v>0.0041904714814142941</v>
+        <v>0.0044711451965680563</v>
       </c>
       <c r="U18">
-        <v>0.0042583813321429385</v>
+        <v>0.0045616017801356715</v>
       </c>
       <c r="V18">
-        <v>0.0043211582266946547</v>
+        <v>0.0045719031414063506</v>
       </c>
       <c r="W18">
-        <v>0.0043659898165358197</v>
+        <v>0.0046852363621794658</v>
       </c>
       <c r="X18">
-        <v>0.00015343273042017319</v>
+        <v>0.00015333317193805626</v>
       </c>
       <c r="Y18">
-        <v>-0.0014597399892493563</v>
+        <v>-0.0013525316336007139</v>
       </c>
       <c r="Z18">
-        <v>-0.0010075853278498639</v>
+        <v>-0.00098891864941602495</v>
       </c>
       <c r="AA18">
-        <v>0.00097930767718454759</v>
+        <v>0.001086506850925221</v>
       </c>
       <c r="AB18">
-        <v>0.0028610336380212285</v>
+        <v>0.0030551922122021352</v>
       </c>
       <c r="AC18">
-        <v>0.0023461178135706466</v>
+        <v>0.0022014605088905574</v>
       </c>
       <c r="AD18">
-        <v>-0.0025192134344144438</v>
+        <v>-0.0028490219925102183</v>
       </c>
     </row>
     <row r="19">
@@ -5928,91 +5928,91 @@
         <v>53</v>
       </c>
       <c r="B19" s="91">
-        <v>-0.22925153009659657</v>
+        <v>-0.21014007673817306</v>
       </c>
       <c r="C19">
-        <v>5.5753981385478816e-005</v>
+        <v>8.691297598797693e-005</v>
       </c>
       <c r="D19">
-        <v>-0.00025151484442306749</v>
+        <v>-0.00024743765242954754</v>
       </c>
       <c r="E19">
-        <v>4.8165476837419346e-006</v>
+        <v>4.6418348206948574e-006</v>
       </c>
       <c r="F19">
-        <v>-0.00078322041686731351</v>
+        <v>-0.00080605828042742923</v>
       </c>
       <c r="G19">
-        <v>-0.001084787388648241</v>
+        <v>-0.0011651509990863004</v>
       </c>
       <c r="H19">
-        <v>-0.00033003893803459959</v>
+        <v>-0.00034485827091860306</v>
       </c>
       <c r="I19">
-        <v>4.7909561327761025e-005</v>
+        <v>7.2889171237782335e-005</v>
       </c>
       <c r="J19">
-        <v>-0.00011369915076271902</v>
+        <v>-0.00011111481152825784</v>
       </c>
       <c r="K19">
-        <v>-0.00029076106028032457</v>
+        <v>-0.00034863732741485825</v>
       </c>
       <c r="L19">
-        <v>-0.0004751171259604491</v>
+        <v>-0.00057216670764221906</v>
       </c>
       <c r="M19">
-        <v>0.0043501356815151904</v>
+        <v>0.0047084949893931687</v>
       </c>
       <c r="N19">
-        <v>0.0042127744566387206</v>
+        <v>0.0044866887969909289</v>
       </c>
       <c r="O19">
-        <v>0.0042265028574685441</v>
+        <v>0.0045671959469540174</v>
       </c>
       <c r="P19">
-        <v>0.0042242024184902787</v>
+        <v>0.0045009948594165478</v>
       </c>
       <c r="Q19">
-        <v>0.0041064913081218521</v>
+        <v>0.0045379028693302726</v>
       </c>
       <c r="R19">
-        <v>0.0041313667866062186</v>
+        <v>0.0043801400896612006</v>
       </c>
       <c r="S19">
-        <v>0.0041904714814142941</v>
+        <v>0.0044711451965680563</v>
       </c>
       <c r="T19">
-        <v>0.0094391594243519172</v>
+        <v>0.0097587328821904847</v>
       </c>
       <c r="U19">
-        <v>0.0043467658994803746</v>
+        <v>0.0046899283544248943</v>
       </c>
       <c r="V19">
-        <v>0.0044067994500638719</v>
+        <v>0.0046869726060344919</v>
       </c>
       <c r="W19">
-        <v>0.0044188554879140834</v>
+        <v>0.0047801113727514999</v>
       </c>
       <c r="X19">
-        <v>3.3295008276435336e-005</v>
+        <v>3.283157873832282e-005</v>
       </c>
       <c r="Y19">
-        <v>-0.00049766859003566024</v>
+        <v>-0.00037509487849990484</v>
       </c>
       <c r="Z19">
-        <v>-0.0002273304122262401</v>
+        <v>-0.00020850470866470372</v>
       </c>
       <c r="AA19">
-        <v>0.0013958774696231687</v>
+        <v>0.0015292086424286075</v>
       </c>
       <c r="AB19">
-        <v>0.0030758052373109457</v>
+        <v>0.003306310070333527</v>
       </c>
       <c r="AC19">
-        <v>0.0030089220953264675</v>
+        <v>0.0026838909949487514</v>
       </c>
       <c r="AD19">
-        <v>-0.00069735223262202845</v>
+        <v>-0.0009916339603318787</v>
       </c>
     </row>
     <row r="20">
@@ -6020,91 +6020,91 @@
         <v>54</v>
       </c>
       <c r="B20" s="93">
-        <v>-0.069259985535321353</v>
+        <v>-0.049320294269175953</v>
       </c>
       <c r="C20">
-        <v>-7.7955191953153237e-005</v>
+        <v>-4.8939286837537243e-005</v>
       </c>
       <c r="D20">
-        <v>-7.7819788718597183e-005</v>
+        <v>-7.5601721556298879e-005</v>
       </c>
       <c r="E20">
-        <v>1.6262060839134038e-006</v>
+        <v>1.4848698575775708e-006</v>
       </c>
       <c r="F20">
-        <v>-0.00036045509987020843</v>
+        <v>-0.00037858740168326879</v>
       </c>
       <c r="G20">
-        <v>-0.0010921644123880322</v>
+        <v>-0.0011718772343099742</v>
       </c>
       <c r="H20">
-        <v>-0.00048842047964455654</v>
+        <v>-0.00050527044810335341</v>
       </c>
       <c r="I20">
-        <v>0.00019034303831213161</v>
+        <v>0.00021334973461589551</v>
       </c>
       <c r="J20">
-        <v>-0.00051440485620587485</v>
+        <v>-0.00051543616714001773</v>
       </c>
       <c r="K20">
-        <v>-0.00036031636519535243</v>
+        <v>-0.00042069437730262436</v>
       </c>
       <c r="L20">
-        <v>-0.00065281608983242846</v>
+        <v>-0.0007593125770759692</v>
       </c>
       <c r="M20">
-        <v>0.0044282720502237544</v>
+        <v>0.0048146355667414821</v>
       </c>
       <c r="N20">
-        <v>0.0042141080723935593</v>
+        <v>0.0045105089881673577</v>
       </c>
       <c r="O20">
-        <v>0.0042843707910139349</v>
+        <v>0.0046515206507577109</v>
       </c>
       <c r="P20">
-        <v>0.0042735254891132883</v>
+        <v>0.0045726214624139047</v>
       </c>
       <c r="Q20">
-        <v>0.0041521592806043964</v>
+        <v>0.0046080970335882045</v>
       </c>
       <c r="R20">
-        <v>0.0041572156336784748</v>
+        <v>0.0044269753919717629</v>
       </c>
       <c r="S20">
-        <v>0.0042583813321429385</v>
+        <v>0.0045616017801356715</v>
       </c>
       <c r="T20">
-        <v>0.0043467658994803746</v>
+        <v>0.0046899283544248943</v>
       </c>
       <c r="U20">
-        <v>0.0092376620444230926</v>
+        <v>0.0096093742769252574</v>
       </c>
       <c r="V20">
-        <v>0.0044551384305109056</v>
+        <v>0.0047619230329576543</v>
       </c>
       <c r="W20">
-        <v>0.0044420655284151817</v>
+        <v>0.0048328794868023293</v>
       </c>
       <c r="X20">
-        <v>4.6314002076712924e-005</v>
+        <v>4.5556102532413097e-005</v>
       </c>
       <c r="Y20">
-        <v>-0.00028236338577864925</v>
+        <v>-0.00015083614139536948</v>
       </c>
       <c r="Z20">
-        <v>-0.00017095149913492558</v>
+        <v>-0.00015387311947324457</v>
       </c>
       <c r="AA20">
-        <v>0.0014822179586252613</v>
+        <v>0.0016337331712749611</v>
       </c>
       <c r="AB20">
-        <v>0.0031138369584921798</v>
+        <v>0.0033676653441762974</v>
       </c>
       <c r="AC20">
-        <v>0.0030772339772108222</v>
+        <v>0.002855259889195232</v>
       </c>
       <c r="AD20">
-        <v>-0.0034153796845287012</v>
+        <v>-0.0037060621689632292</v>
       </c>
     </row>
     <row r="21">
@@ -6112,91 +6112,91 @@
         <v>55</v>
       </c>
       <c r="B21" s="95">
-        <v>0.11992500578387273</v>
+        <v>0.13713938201820183</v>
       </c>
       <c r="C21">
-        <v>-5.9756413666336755e-005</v>
+        <v>-1.9675608440710064e-005</v>
       </c>
       <c r="D21">
-        <v>0.000248807304958059</v>
+        <v>0.00024342748275127217</v>
       </c>
       <c r="E21">
-        <v>-5.0781623995771517e-006</v>
+        <v>-5.1035854318403023e-006</v>
       </c>
       <c r="F21">
-        <v>-0.00046574207488261671</v>
+        <v>-0.00051258748280689093</v>
       </c>
       <c r="G21">
-        <v>-0.00088007641819220052</v>
+        <v>-0.00099347223905786423</v>
       </c>
       <c r="H21">
-        <v>-0.00030990849664889412</v>
+        <v>-0.00032375390226934775</v>
       </c>
       <c r="I21">
-        <v>3.5500914472902834e-005</v>
+        <v>9.3469124141004872e-005</v>
       </c>
       <c r="J21">
-        <v>-0.00016970104313837934</v>
+        <v>-0.00016134224293845416</v>
       </c>
       <c r="K21">
-        <v>-0.00024029024359936127</v>
+        <v>-0.00028522632948149615</v>
       </c>
       <c r="L21">
-        <v>-0.00029504910637672825</v>
+        <v>-0.00036869207399091474</v>
       </c>
       <c r="M21">
-        <v>0.0044191319293576514</v>
+        <v>0.0047593489821810718</v>
       </c>
       <c r="N21">
-        <v>0.0042943043592783975</v>
+        <v>0.0045291799378279858</v>
       </c>
       <c r="O21">
-        <v>0.0043317842468419444</v>
+        <v>0.004613674083160671</v>
       </c>
       <c r="P21">
-        <v>0.0042759293755272312</v>
+        <v>0.00450802285105034</v>
       </c>
       <c r="Q21">
-        <v>0.0041918443359133572</v>
+        <v>0.0045053938694727055</v>
       </c>
       <c r="R21">
-        <v>0.0041965661692203162</v>
+        <v>0.0044062571336844717</v>
       </c>
       <c r="S21">
-        <v>0.0043211582266946547</v>
+        <v>0.0045719031414063506</v>
       </c>
       <c r="T21">
-        <v>0.0044067994500638719</v>
+        <v>0.0046869726060344919</v>
       </c>
       <c r="U21">
-        <v>0.0044551384305109056</v>
+        <v>0.0047619230329576543</v>
       </c>
       <c r="V21">
-        <v>0.0079626034165820366</v>
+        <v>0.0082170520857840507</v>
       </c>
       <c r="W21">
-        <v>0.004421895597168525</v>
+        <v>0.0047519188096458538</v>
       </c>
       <c r="X21">
-        <v>3.669724397911407e-005</v>
+        <v>3.5095413329925315e-005</v>
       </c>
       <c r="Y21">
-        <v>-0.00055569899083928397</v>
+        <v>-0.00046146838436498324</v>
       </c>
       <c r="Z21">
-        <v>0.00032978150107721392</v>
+        <v>0.0003368504222852702</v>
       </c>
       <c r="AA21">
-        <v>0.0015281375007457636</v>
+        <v>0.0016421560899143911</v>
       </c>
       <c r="AB21">
-        <v>0.0032914455179091271</v>
+        <v>0.0034934701405673159</v>
       </c>
       <c r="AC21">
-        <v>0.0054041965207372901</v>
+        <v>0.0034646183333371565</v>
       </c>
       <c r="AD21">
-        <v>-0.0072603510784798424</v>
+        <v>-0.0073779384077685122</v>
       </c>
     </row>
     <row r="22">
@@ -6204,91 +6204,91 @@
         <v>56</v>
       </c>
       <c r="B22" s="97">
-        <v>-0.029807129343957305</v>
+        <v>-0.0094509771707949157</v>
       </c>
       <c r="C22">
-        <v>-0.00030288055986193107</v>
+        <v>-0.00027611176422195796</v>
       </c>
       <c r="D22">
-        <v>0.00018988179196845201</v>
+        <v>0.00019331437682851282</v>
       </c>
       <c r="E22">
-        <v>-3.4392800377659174e-006</v>
+        <v>-3.6053193943279922e-006</v>
       </c>
       <c r="F22">
-        <v>-0.00028346299435504183</v>
+        <v>-0.00029680556774447494</v>
       </c>
       <c r="G22">
-        <v>-0.0016839454708573189</v>
+        <v>-0.001778816795663345</v>
       </c>
       <c r="H22">
-        <v>-0.00068332926587718885</v>
+        <v>-0.00070446898277532486</v>
       </c>
       <c r="I22">
-        <v>0.00025535969374797219</v>
+        <v>0.00027506424775705662</v>
       </c>
       <c r="J22">
-        <v>-0.00050360616746535211</v>
+        <v>-0.00050095224640280293</v>
       </c>
       <c r="K22">
-        <v>-0.00043291584001511885</v>
+        <v>-0.00049894790773069391</v>
       </c>
       <c r="L22">
-        <v>-0.00041651950109381365</v>
+        <v>-0.0005335111358318929</v>
       </c>
       <c r="M22">
-        <v>0.0044527280323268421</v>
+        <v>0.0048594057673663083</v>
       </c>
       <c r="N22">
-        <v>0.0041614164523188502</v>
+        <v>0.0044745512719364527</v>
       </c>
       <c r="O22">
-        <v>0.0043091500198555524</v>
+        <v>0.0046977356782586036</v>
       </c>
       <c r="P22">
-        <v>0.0042781950188496998</v>
+        <v>0.0045935003068158006</v>
       </c>
       <c r="Q22">
-        <v>0.0041987047307523052</v>
+        <v>0.0046820510233839333</v>
       </c>
       <c r="R22">
-        <v>0.0041152328301060975</v>
+        <v>0.0044005652462512992</v>
       </c>
       <c r="S22">
-        <v>0.0043659898165358197</v>
+        <v>0.0046852363621794658</v>
       </c>
       <c r="T22">
-        <v>0.0044188554879140834</v>
+        <v>0.0047801113727514999</v>
       </c>
       <c r="U22">
-        <v>0.0044420655284151817</v>
+        <v>0.0048328794868023293</v>
       </c>
       <c r="V22">
-        <v>0.004421895597168525</v>
+        <v>0.0047519188096458538</v>
       </c>
       <c r="W22">
-        <v>0.012862219267448795</v>
+        <v>0.013282058893478154</v>
       </c>
       <c r="X22">
-        <v>2.1747010336498076e-005</v>
+        <v>2.0736112911637775e-005</v>
       </c>
       <c r="Y22">
-        <v>-0.00063035031378928113</v>
+        <v>-0.00049108703151904006</v>
       </c>
       <c r="Z22">
-        <v>-0.00027078005173173086</v>
+        <v>-0.00025247646252193857</v>
       </c>
       <c r="AA22">
-        <v>0.0014535113279800303</v>
+        <v>0.0016166636909249119</v>
       </c>
       <c r="AB22">
-        <v>0.0030256621107212444</v>
+        <v>0.0032933939247188956</v>
       </c>
       <c r="AC22">
-        <v>0.002916835247580264</v>
+        <v>0.0028702346510884238</v>
       </c>
       <c r="AD22">
-        <v>-0.0063533337540501783</v>
+        <v>-0.0066681468687801318</v>
       </c>
     </row>
     <row r="23">
@@ -6296,91 +6296,91 @@
         <v>57</v>
       </c>
       <c r="B23" s="99">
-        <v>0.0078387639495990959</v>
+        <v>0.0075402048969391566</v>
       </c>
       <c r="C23">
-        <v>6.4169728635986333e-005</v>
+        <v>6.4976732524300694e-005</v>
       </c>
       <c r="D23">
-        <v>-5.7972278548507929e-005</v>
+        <v>-5.8824166971039715e-005</v>
       </c>
       <c r="E23">
-        <v>1.1400259419693429e-006</v>
+        <v>1.1572674605023024e-006</v>
       </c>
       <c r="F23">
-        <v>-8.1689300042880105e-005</v>
+        <v>-8.2110906797003898e-005</v>
       </c>
       <c r="G23">
-        <v>-9.1759218800773737e-005</v>
+        <v>-9.2456415785086466e-005</v>
       </c>
       <c r="H23">
-        <v>-8.7011166735024128e-006</v>
+        <v>-7.9776642754461136e-006</v>
       </c>
       <c r="I23">
-        <v>-9.1607373875157673e-006</v>
+        <v>-8.9866495295515888e-006</v>
       </c>
       <c r="J23">
-        <v>3.673166797329866e-005</v>
+        <v>3.7355555689726232e-005</v>
       </c>
       <c r="K23">
-        <v>7.6064213868253154e-005</v>
+        <v>7.7384035381430184e-005</v>
       </c>
       <c r="L23">
-        <v>0.00010142186696377223</v>
+        <v>0.00010324933184171247</v>
       </c>
       <c r="M23">
-        <v>-2.6173596611608229e-005</v>
+        <v>-2.7296910969367382e-005</v>
       </c>
       <c r="N23">
-        <v>4.5567323935269307e-005</v>
+        <v>4.4701602354527739e-005</v>
       </c>
       <c r="O23">
-        <v>3.0487396917418036e-005</v>
+        <v>2.8108409458646889e-005</v>
       </c>
       <c r="P23">
-        <v>2.010138043315895e-005</v>
+        <v>1.9353977542898898e-005</v>
       </c>
       <c r="Q23">
-        <v>4.1881822060358033e-005</v>
+        <v>3.2859137385277571e-005</v>
       </c>
       <c r="R23">
-        <v>6.355929796396766e-006</v>
+        <v>5.0345562074083708e-006</v>
       </c>
       <c r="S23">
-        <v>0.00015343273042017319</v>
+        <v>0.00015333317193805626</v>
       </c>
       <c r="T23">
-        <v>3.3295008276435336e-005</v>
+        <v>3.283157873832282e-005</v>
       </c>
       <c r="U23">
-        <v>4.6314002076712924e-005</v>
+        <v>4.5556102532413097e-005</v>
       </c>
       <c r="V23">
-        <v>3.669724397911407e-005</v>
+        <v>3.5095413329925315e-005</v>
       </c>
       <c r="W23">
-        <v>2.1747010336498076e-005</v>
+        <v>2.0736112911637775e-005</v>
       </c>
       <c r="X23">
-        <v>5.4544724700216258e-005</v>
+        <v>5.4392626808117282e-005</v>
       </c>
       <c r="Y23">
-        <v>-0.00026314844169013346</v>
+        <v>-0.00026492903606329559</v>
       </c>
       <c r="Z23">
-        <v>-0.000314806560146291</v>
+        <v>-0.00031504004147039336</v>
       </c>
       <c r="AA23">
-        <v>-2.8686563503874519e-005</v>
+        <v>-2.8788281952270203e-005</v>
       </c>
       <c r="AB23">
-        <v>3.5545574641035384e-006</v>
+        <v>2.9234245933820995e-006</v>
       </c>
       <c r="AC23">
-        <v>2.9203764942810156e-005</v>
+        <v>1.2526582314423326e-005</v>
       </c>
       <c r="AD23">
-        <v>-0.00018792368212190757</v>
+        <v>-0.00017571635609555259</v>
       </c>
     </row>
     <row r="24">
@@ -6388,91 +6388,91 @@
         <v>58</v>
       </c>
       <c r="B24" s="101">
-        <v>-0.093410023756403684</v>
+        <v>-0.093323941404581445</v>
       </c>
       <c r="C24">
-        <v>-0.00044296828210544129</v>
+        <v>-0.00047608647764882232</v>
       </c>
       <c r="D24">
-        <v>0.00042539485440859417</v>
+        <v>0.00038841961198819025</v>
       </c>
       <c r="E24">
-        <v>-8.7960742900612058e-006</v>
+        <v>-8.0722297137839375e-006</v>
       </c>
       <c r="F24">
-        <v>0.00029781497400764318</v>
+        <v>0.00033193486707643418</v>
       </c>
       <c r="G24">
-        <v>0.00046134185792364563</v>
+        <v>0.00046941345405632391</v>
       </c>
       <c r="H24">
-        <v>-0.0002768966747274588</v>
+        <v>-0.0002871620745060194</v>
       </c>
       <c r="I24">
-        <v>9.4084096334294846e-005</v>
+        <v>6.8042679064816459e-005</v>
       </c>
       <c r="J24">
-        <v>4.5520980033952278e-006</v>
+        <v>6.0154933508439583e-007</v>
       </c>
       <c r="K24">
-        <v>-0.0010599507660143863</v>
+        <v>-0.00095769501423219512</v>
       </c>
       <c r="L24">
-        <v>-0.001032209932942271</v>
+        <v>-0.00093885212478094057</v>
       </c>
       <c r="M24">
-        <v>-0.00055021652696677107</v>
+        <v>-0.00042789889936725419</v>
       </c>
       <c r="N24">
-        <v>-0.00068446884740063125</v>
+        <v>-0.00058029005612368417</v>
       </c>
       <c r="O24">
-        <v>-0.00014111157268094604</v>
+        <v>-2.1160591212731651e-005</v>
       </c>
       <c r="P24">
-        <v>-0.00066274084255088538</v>
+        <v>-0.00056536816762100834</v>
       </c>
       <c r="Q24">
-        <v>-5.3478462916410206e-005</v>
+        <v>-6.7596738570274446e-005</v>
       </c>
       <c r="R24">
-        <v>-0.0004272348586474824</v>
+        <v>-0.00031891859737965622</v>
       </c>
       <c r="S24">
-        <v>-0.0014597399892493563</v>
+        <v>-0.0013525316336007139</v>
       </c>
       <c r="T24">
-        <v>-0.00049766859003566024</v>
+        <v>-0.00037509487849990484</v>
       </c>
       <c r="U24">
-        <v>-0.00028236338577864925</v>
+        <v>-0.00015083614139536948</v>
       </c>
       <c r="V24">
-        <v>-0.00055569899083928397</v>
+        <v>-0.00046146838436498324</v>
       </c>
       <c r="W24">
-        <v>-0.00063035031378928113</v>
+        <v>-0.00049108703151904006</v>
       </c>
       <c r="X24">
-        <v>-0.00026314844169013346</v>
+        <v>-0.00026492903606329559</v>
       </c>
       <c r="Y24">
-        <v>0.0076029981420700065</v>
+        <v>0.0075377645000785243</v>
       </c>
       <c r="Z24">
-        <v>0.00192836852049882</v>
+        <v>0.00192643591010339</v>
       </c>
       <c r="AA24">
-        <v>0.00044153304496702254</v>
+        <v>0.00056799707638894898</v>
       </c>
       <c r="AB24">
-        <v>-0.00041708798327447401</v>
+        <v>-0.00028604066662445637</v>
       </c>
       <c r="AC24">
-        <v>-0.00052419528462550771</v>
+        <v>0.00083742458525234466</v>
       </c>
       <c r="AD24">
-        <v>5.7186844924045962e-005</v>
+        <v>0.00032530918479361376</v>
       </c>
     </row>
     <row r="25">
@@ -6480,91 +6480,91 @@
         <v>59</v>
       </c>
       <c r="B25" s="103">
-        <v>0.028494722741707525</v>
+        <v>0.026771064458444696</v>
       </c>
       <c r="C25">
-        <v>-0.00032178015481110244</v>
+        <v>-0.00033434262502253357</v>
       </c>
       <c r="D25">
-        <v>0.00036498210965349442</v>
+        <v>0.00034550188329664396</v>
       </c>
       <c r="E25">
-        <v>-7.6032255453834918e-006</v>
+        <v>-7.235209321050938e-006</v>
       </c>
       <c r="F25">
-        <v>0.00041466867353847042</v>
+        <v>0.00040504155709004193</v>
       </c>
       <c r="G25">
-        <v>0.00023131736780290595</v>
+        <v>0.0002212952569453498</v>
       </c>
       <c r="H25">
-        <v>0.00010984877596511384</v>
+        <v>9.3228366997010685e-005</v>
       </c>
       <c r="I25">
-        <v>6.9516724853600147e-005</v>
+        <v>6.0587076645444949e-005</v>
       </c>
       <c r="J25">
-        <v>-0.00018817889387134131</v>
+        <v>-0.00018333655285065814</v>
       </c>
       <c r="K25">
-        <v>-0.0010256417521587293</v>
+        <v>-0.00097907707533994182</v>
       </c>
       <c r="L25">
-        <v>-0.00044666980520720654</v>
+        <v>-0.00039351063802412379</v>
       </c>
       <c r="M25">
-        <v>8.0644674639837426e-005</v>
+        <v>9.4161069373627985e-005</v>
       </c>
       <c r="N25">
-        <v>0.00034508168083520886</v>
+        <v>0.00036163713090229979</v>
       </c>
       <c r="O25">
-        <v>0.00075071251600452096</v>
+        <v>0.00073622848621853322</v>
       </c>
       <c r="P25">
-        <v>-9.1078226737989574e-005</v>
+        <v>-7.2904262456958014e-005</v>
       </c>
       <c r="Q25">
-        <v>-0.00029825262597322696</v>
+        <v>-0.00027606992554081965</v>
       </c>
       <c r="R25">
-        <v>0.00062771686507581464</v>
+        <v>0.00065734568355558728</v>
       </c>
       <c r="S25">
-        <v>-0.0010075853278498639</v>
+        <v>-0.00098891864941602495</v>
       </c>
       <c r="T25">
-        <v>-0.0002273304122262401</v>
+        <v>-0.00020850470866470372</v>
       </c>
       <c r="U25">
-        <v>-0.00017095149913492558</v>
+        <v>-0.00015387311947324457</v>
       </c>
       <c r="V25">
-        <v>0.00032978150107721392</v>
+        <v>0.0003368504222852702</v>
       </c>
       <c r="W25">
-        <v>-0.00027078005173173086</v>
+        <v>-0.00025247646252193857</v>
       </c>
       <c r="X25">
-        <v>-0.000314806560146291</v>
+        <v>-0.00031504004147039336</v>
       </c>
       <c r="Y25">
-        <v>0.00192836852049882</v>
+        <v>0.00192643591010339</v>
       </c>
       <c r="Z25">
-        <v>0.008394766061667263</v>
+        <v>0.0083969864365740741</v>
       </c>
       <c r="AA25">
-        <v>1.4451266667382581e-005</v>
+        <v>3.2185723906719838e-005</v>
       </c>
       <c r="AB25">
-        <v>2.3696143870506788e-006</v>
+        <v>2.4086856601600835e-005</v>
       </c>
       <c r="AC25">
-        <v>-0.00059739373050705154</v>
+        <v>-8.7592947962987239e-005</v>
       </c>
       <c r="AD25">
-        <v>0.00069465425075839696</v>
+        <v>0.00090846738452928996</v>
       </c>
     </row>
     <row r="26">
@@ -6572,91 +6572,91 @@
         <v>60</v>
       </c>
       <c r="B26" s="105">
-        <v>-0.075000511026766525</v>
+        <v>-0.060847765375106506</v>
       </c>
       <c r="C26">
-        <v>-0.00034049071355579208</v>
+        <v>-0.00031786032283763607</v>
       </c>
       <c r="D26">
-        <v>-0.00041378895058555992</v>
+        <v>-0.00040071099743363772</v>
       </c>
       <c r="E26">
-        <v>7.2744751576634716e-006</v>
+        <v>6.9458082233648166e-006</v>
       </c>
       <c r="F26">
-        <v>0.0005382775568378113</v>
+        <v>0.00052159728177028804</v>
       </c>
       <c r="G26">
-        <v>0.00029109246113433358</v>
+        <v>0.00023455848808348785</v>
       </c>
       <c r="H26">
-        <v>-0.00045279409719744699</v>
+        <v>-0.0004621546032321038</v>
       </c>
       <c r="I26">
-        <v>-5.4180356062105174e-005</v>
+        <v>-2.9458846697555819e-005</v>
       </c>
       <c r="J26">
-        <v>-3.3756505129463234e-005</v>
+        <v>-3.5141514432944845e-005</v>
       </c>
       <c r="K26">
-        <v>-6.1493002479241668e-005</v>
+        <v>-0.00013337994466864809</v>
       </c>
       <c r="L26">
-        <v>-0.00063682123442268469</v>
+        <v>-0.00074209015227016592</v>
       </c>
       <c r="M26">
-        <v>0.0015130080778286263</v>
+        <v>0.0016779255556667555</v>
       </c>
       <c r="N26">
-        <v>0.00097807242301378716</v>
+        <v>0.0010846299012199591</v>
       </c>
       <c r="O26">
-        <v>0.00096782346345637097</v>
+        <v>0.0011231685314784146</v>
       </c>
       <c r="P26">
-        <v>0.001145147547885363</v>
+        <v>0.0012610586789822535</v>
       </c>
       <c r="Q26">
-        <v>0.00047956674769879335</v>
+        <v>0.00074269452899958666</v>
       </c>
       <c r="R26">
-        <v>0.00095984775203105006</v>
+        <v>0.0010562586534860526</v>
       </c>
       <c r="S26">
-        <v>0.00097930767718454759</v>
+        <v>0.001086506850925221</v>
       </c>
       <c r="T26">
-        <v>0.0013958774696231687</v>
+        <v>0.0015292086424286075</v>
       </c>
       <c r="U26">
-        <v>0.0014822179586252613</v>
+        <v>0.0016337331712749611</v>
       </c>
       <c r="V26">
-        <v>0.0015281375007457636</v>
+        <v>0.0016421560899143911</v>
       </c>
       <c r="W26">
-        <v>0.0014535113279800303</v>
+        <v>0.0016166636909249119</v>
       </c>
       <c r="X26">
-        <v>-2.8686563503874519e-005</v>
+        <v>-2.8788281952270203e-005</v>
       </c>
       <c r="Y26">
-        <v>0.00044153304496702254</v>
+        <v>0.00056799707638894898</v>
       </c>
       <c r="Z26">
-        <v>1.4451266667382581e-005</v>
+        <v>3.2185723906719838e-005</v>
       </c>
       <c r="AA26">
-        <v>0.0051242057673113331</v>
+        <v>0.0051873605716980095</v>
       </c>
       <c r="AB26">
-        <v>0.0013581488178651575</v>
+        <v>0.0014626929577455493</v>
       </c>
       <c r="AC26">
-        <v>0.0022069723625364793</v>
+        <v>0.0015508460408581199</v>
       </c>
       <c r="AD26">
-        <v>0.0046302482849825532</v>
+        <v>0.0044105267956745364</v>
       </c>
     </row>
     <row r="27">
@@ -6664,91 +6664,91 @@
         <v>61</v>
       </c>
       <c r="B27" s="107">
-        <v>0.2469463784254449</v>
+        <v>0.26419359667474529</v>
       </c>
       <c r="C27">
-        <v>-0.00022427449719754139</v>
+        <v>-0.0001990793614942202</v>
       </c>
       <c r="D27">
-        <v>-0.00013596267946565724</v>
+        <v>-0.00012762425749894904</v>
       </c>
       <c r="E27">
-        <v>1.9352393934263614e-006</v>
+        <v>1.6840575566798061e-006</v>
       </c>
       <c r="F27">
-        <v>-0.00017751568387027079</v>
+        <v>-0.00019345968367365414</v>
       </c>
       <c r="G27">
-        <v>-0.00078016100331416375</v>
+        <v>-0.00084840965801500322</v>
       </c>
       <c r="H27">
-        <v>-0.00041806808959597881</v>
+        <v>-0.0004324905533191481</v>
       </c>
       <c r="I27">
-        <v>4.1728441694810709e-005</v>
+        <v>6.4315249850045286e-005</v>
       </c>
       <c r="J27">
-        <v>-0.00012993645404362018</v>
+        <v>-0.0001305264997695137</v>
       </c>
       <c r="K27">
-        <v>2.4791378281807924e-005</v>
+        <v>-4.5668465427433692e-005</v>
       </c>
       <c r="L27">
-        <v>3.8440129129652871e-005</v>
+        <v>-7.37141077118555e-005</v>
       </c>
       <c r="M27">
-        <v>0.0030864910508118801</v>
+        <v>0.003356192975299304</v>
       </c>
       <c r="N27">
-        <v>0.0030660498330441492</v>
+        <v>0.003255423572251039</v>
       </c>
       <c r="O27">
-        <v>0.0028869079334501507</v>
+        <v>0.0031443989857716046</v>
       </c>
       <c r="P27">
-        <v>0.0027156095167048108</v>
+        <v>0.0029130535634169447</v>
       </c>
       <c r="Q27">
-        <v>0.0027192047524042763</v>
+        <v>0.0030752207612426384</v>
       </c>
       <c r="R27">
-        <v>0.0026527782052546832</v>
+        <v>0.0028242397581575837</v>
       </c>
       <c r="S27">
-        <v>0.0028610336380212285</v>
+        <v>0.0030551922122021352</v>
       </c>
       <c r="T27">
-        <v>0.0030758052373109457</v>
+        <v>0.003306310070333527</v>
       </c>
       <c r="U27">
-        <v>0.0031138369584921798</v>
+        <v>0.0033676653441762974</v>
       </c>
       <c r="V27">
-        <v>0.0032914455179091271</v>
+        <v>0.0034934701405673159</v>
       </c>
       <c r="W27">
-        <v>0.0030256621107212444</v>
+        <v>0.0032933939247188956</v>
       </c>
       <c r="X27">
-        <v>3.5545574641035384e-006</v>
+        <v>2.9234245933820995e-006</v>
       </c>
       <c r="Y27">
-        <v>-0.00041708798327447401</v>
+        <v>-0.00028604066662445637</v>
       </c>
       <c r="Z27">
-        <v>2.3696143870506788e-006</v>
+        <v>2.4086856601600835e-005</v>
       </c>
       <c r="AA27">
-        <v>0.0013581488178651575</v>
+        <v>0.0014626929577455493</v>
       </c>
       <c r="AB27">
-        <v>0.0076796507881353388</v>
+        <v>0.0078311106243768372</v>
       </c>
       <c r="AC27">
-        <v>0.0025485306135856365</v>
+        <v>0.0021830770150559446</v>
       </c>
       <c r="AD27">
-        <v>-0.00068701088292852223</v>
+        <v>-0.00093338449295081861</v>
       </c>
     </row>
     <row r="28">
@@ -6756,91 +6756,91 @@
         <v>62</v>
       </c>
       <c r="B28" s="109">
-        <v>0.041263603127537997</v>
+        <v>0.17504802825073135</v>
       </c>
       <c r="C28">
-        <v>-0.00092059851594129848</v>
+        <v>-0.00018264908301718</v>
       </c>
       <c r="D28">
-        <v>0.00030506818082499249</v>
+        <v>0.00025602809545094331</v>
       </c>
       <c r="E28">
-        <v>-5.2800947341681998e-006</v>
+        <v>-5.2505789576269153e-006</v>
       </c>
       <c r="F28">
-        <v>0.0012465082138351767</v>
+        <v>0.00036290090328815845</v>
       </c>
       <c r="G28">
-        <v>0.00096287797038103833</v>
+        <v>-4.6610187418628403e-005</v>
       </c>
       <c r="H28">
-        <v>-0.00082927178701539136</v>
+        <v>-0.00044257238583942667</v>
       </c>
       <c r="I28">
-        <v>-0.00077951976627440721</v>
+        <v>-0.00013822516778159814</v>
       </c>
       <c r="J28">
-        <v>-0.00040061451013042552</v>
+        <v>-0.00016861853350639796</v>
       </c>
       <c r="K28">
-        <v>-4.9465223970228379e-005</v>
+        <v>-0.00065754759900779147</v>
       </c>
       <c r="L28">
-        <v>-0.000731149807846121</v>
+        <v>-0.0012566007749082032</v>
       </c>
       <c r="M28">
-        <v>0.0033274646089603123</v>
+        <v>0.0030666609388244983</v>
       </c>
       <c r="N28">
-        <v>0.0028775755304505371</v>
+        <v>0.0023906816936546636</v>
       </c>
       <c r="O28">
-        <v>0.0030908922112620257</v>
+        <v>0.0029913734302788137</v>
       </c>
       <c r="P28">
-        <v>0.0026184310347745093</v>
+        <v>0.0023993898952658424</v>
       </c>
       <c r="Q28">
-        <v>0.0027508966878814481</v>
+        <v>0.0039166079477502402</v>
       </c>
       <c r="R28">
-        <v>0.0023052377225684017</v>
+        <v>0.0020217654522131359</v>
       </c>
       <c r="S28">
-        <v>0.0023461178135706466</v>
+        <v>0.0022014605088905574</v>
       </c>
       <c r="T28">
-        <v>0.0030089220953264675</v>
+        <v>0.0026838909949487514</v>
       </c>
       <c r="U28">
-        <v>0.0030772339772108222</v>
+        <v>0.002855259889195232</v>
       </c>
       <c r="V28">
-        <v>0.0054041965207372901</v>
+        <v>0.0034646183333371565</v>
       </c>
       <c r="W28">
-        <v>0.002916835247580264</v>
+        <v>0.0028702346510884238</v>
       </c>
       <c r="X28">
-        <v>2.9203764942810156e-005</v>
+        <v>1.2526582314423326e-005</v>
       </c>
       <c r="Y28">
-        <v>-0.00052419528462550771</v>
+        <v>0.00083742458525234466</v>
       </c>
       <c r="Z28">
-        <v>-0.00059739373050705154</v>
+        <v>-8.7592947962987239e-005</v>
       </c>
       <c r="AA28">
-        <v>0.0022069723625364793</v>
+        <v>0.0015508460408581199</v>
       </c>
       <c r="AB28">
-        <v>0.0025485306135856365</v>
+        <v>0.0021830770150559446</v>
       </c>
       <c r="AC28">
-        <v>0.036783649993338524</v>
+        <v>0.012129475375903078</v>
       </c>
       <c r="AD28">
-        <v>-0.0074314039103062111</v>
+        <v>-0.0054727146642710419</v>
       </c>
     </row>
     <row r="29">
@@ -6848,91 +6848,91 @@
         <v>63</v>
       </c>
       <c r="B29" s="111">
-        <v>4.6098797559175377</v>
+        <v>4.6294891005078336</v>
       </c>
       <c r="C29">
-        <v>-0.0013847970364222772</v>
+        <v>-0.0014387676109756361</v>
       </c>
       <c r="D29">
-        <v>-0.026946079142751843</v>
+        <v>-0.026858820714371383</v>
       </c>
       <c r="E29">
-        <v>0.00049641157626876067</v>
+        <v>0.00049454712347467983</v>
       </c>
       <c r="F29">
-        <v>-0.0032556389145149281</v>
+        <v>-0.0031676229425260903</v>
       </c>
       <c r="G29">
-        <v>-0.002022223997550773</v>
+        <v>-0.0020123779576044706</v>
       </c>
       <c r="H29">
-        <v>-0.006175967897320664</v>
+        <v>-0.0062372033290646551</v>
       </c>
       <c r="I29">
-        <v>-0.00093089067211116769</v>
+        <v>-0.0009560495568672815</v>
       </c>
       <c r="J29">
-        <v>0.0041393820025250475</v>
+        <v>0.0041022116317662796</v>
       </c>
       <c r="K29">
-        <v>-0.0016242457535629619</v>
+        <v>-0.0021589802621188566</v>
       </c>
       <c r="L29">
-        <v>-0.0068935888604638659</v>
+        <v>-0.0075681472674728294</v>
       </c>
       <c r="M29">
-        <v>-0.002527988945701293</v>
+        <v>-0.0028055517791006949</v>
       </c>
       <c r="N29">
-        <v>-0.0051001186682699167</v>
+        <v>-0.0053261825802646632</v>
       </c>
       <c r="O29">
-        <v>-0.0019807408575671119</v>
+        <v>-0.0019888358961703922</v>
       </c>
       <c r="P29">
-        <v>-0.00061088671844520149</v>
+        <v>-0.00072268150820662411</v>
       </c>
       <c r="Q29">
-        <v>-0.0013033284632634292</v>
+        <v>-0.00084296130571874951</v>
       </c>
       <c r="R29">
-        <v>-0.0026557403313212215</v>
+        <v>-0.0028785844740984046</v>
       </c>
       <c r="S29">
-        <v>-0.0025192134344144438</v>
+        <v>-0.0028490219925102183</v>
       </c>
       <c r="T29">
-        <v>-0.00069735223262202845</v>
+        <v>-0.0009916339603318787</v>
       </c>
       <c r="U29">
-        <v>-0.0034153796845287012</v>
+        <v>-0.0037060621689632292</v>
       </c>
       <c r="V29">
-        <v>-0.0072603510784798424</v>
+        <v>-0.0073779384077685122</v>
       </c>
       <c r="W29">
-        <v>-0.0063533337540501783</v>
+        <v>-0.0066681468687801318</v>
       </c>
       <c r="X29">
-        <v>-0.00018792368212190757</v>
+        <v>-0.00017571635609555259</v>
       </c>
       <c r="Y29">
-        <v>5.7186844924045962e-005</v>
+        <v>0.00032530918479361376</v>
       </c>
       <c r="Z29">
-        <v>0.00069465425075839696</v>
+        <v>0.00090846738452928996</v>
       </c>
       <c r="AA29">
-        <v>0.0046302482849825532</v>
+        <v>0.0044105267956745364</v>
       </c>
       <c r="AB29">
-        <v>-0.00068701088292852223</v>
+        <v>-0.00093338449295081861</v>
       </c>
       <c r="AC29">
-        <v>-0.0074314039103062111</v>
+        <v>-0.0054727146642710419</v>
       </c>
       <c r="AD29">
-        <v>0.36568023671214261</v>
+        <v>0.36527429771111442</v>
       </c>
     </row>
   </sheetData>
@@ -6974,7 +6974,7 @@
         <v>85</v>
       </c>
       <c r="C3">
-        <v>-0.23785360307364919</v>
+        <v>-0.23480801490802339</v>
       </c>
     </row>
     <row r="4">
@@ -6985,7 +6985,7 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>1.5901415283540126</v>
+        <v>1.6101315656341801</v>
       </c>
     </row>
     <row r="5">
@@ -6996,7 +6996,7 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>-0.028065130654565694</v>
+        <v>-0.028594550571658713</v>
       </c>
     </row>
     <row r="6">
@@ -7018,7 +7018,7 @@
         <v>87</v>
       </c>
       <c r="C7">
-        <v>-0.1591520996977123</v>
+        <v>-0.16642872553051377</v>
       </c>
     </row>
     <row r="8">
@@ -7040,7 +7040,7 @@
         <v>89</v>
       </c>
       <c r="C9">
-        <v>-1.2702598307148392</v>
+        <v>-1.281862961196319</v>
       </c>
     </row>
     <row r="10">
@@ -7062,7 +7062,7 @@
         <v>91</v>
       </c>
       <c r="C11">
-        <v>-0.42637741228277481</v>
+        <v>-0.3853563420191613</v>
       </c>
     </row>
     <row r="12">
@@ -7084,7 +7084,7 @@
         <v>93</v>
       </c>
       <c r="C13">
-        <v>-0.20249546535842691</v>
+        <v>-0.12242073983301567</v>
       </c>
     </row>
     <row r="14">
@@ -7106,7 +7106,7 @@
         <v>95</v>
       </c>
       <c r="C15">
-        <v>-0.21596794938438812</v>
+        <v>-0.178735591877868</v>
       </c>
     </row>
     <row r="16">
@@ -7128,7 +7128,7 @@
         <v>97</v>
       </c>
       <c r="C17">
-        <v>-0.1587680698610916</v>
+        <v>-0.12014072966666636</v>
       </c>
     </row>
     <row r="18">
@@ -7150,7 +7150,7 @@
         <v>99</v>
       </c>
       <c r="C19">
-        <v>-0.27067698873958973</v>
+        <v>-0.21744199190824959</v>
       </c>
     </row>
     <row r="20">
@@ -7172,7 +7172,7 @@
         <v>101</v>
       </c>
       <c r="C21">
-        <v>0.11910564542282348</v>
+        <v>0.1714699624440045</v>
       </c>
     </row>
     <row r="22">
@@ -7194,7 +7194,7 @@
         <v>103</v>
       </c>
       <c r="C23">
-        <v>0.24762267817997061</v>
+        <v>0.28639811284172306</v>
       </c>
     </row>
     <row r="24">
@@ -7216,7 +7216,7 @@
         <v>105</v>
       </c>
       <c r="C25">
-        <v>-0.12951159737455664</v>
+        <v>-0.092036890602620033</v>
       </c>
     </row>
     <row r="26">
@@ -7238,7 +7238,7 @@
         <v>107</v>
       </c>
       <c r="C27">
-        <v>-0.50536476666537855</v>
+        <v>-0.45876162849996499</v>
       </c>
     </row>
     <row r="28">
@@ -7260,7 +7260,7 @@
         <v>109</v>
       </c>
       <c r="C29">
-        <v>0.74701043401792411</v>
+        <v>0.77710142531810378</v>
       </c>
     </row>
     <row r="30">
@@ -7282,7 +7282,7 @@
         <v>111</v>
       </c>
       <c r="C31">
-        <v>-0.78292107573527381</v>
+        <v>-0.73964734270429722</v>
       </c>
     </row>
     <row r="32">
@@ -7293,7 +7293,7 @@
         <v>57</v>
       </c>
       <c r="C32">
-        <v>-0.057496078032922469</v>
+        <v>-0.055770931748341399</v>
       </c>
     </row>
     <row r="33">
@@ -7304,7 +7304,7 @@
         <v>58</v>
       </c>
       <c r="C33">
-        <v>-0.32741713755744806</v>
+        <v>-0.34099814027199005</v>
       </c>
     </row>
     <row r="34">
@@ -7315,7 +7315,7 @@
         <v>59</v>
       </c>
       <c r="C34">
-        <v>-0.047058936946074735</v>
+        <v>-0.052307869785393174</v>
       </c>
     </row>
     <row r="35">
@@ -7337,7 +7337,7 @@
         <v>113</v>
       </c>
       <c r="C36">
-        <v>0.64927933970608531</v>
+        <v>0.6583366502225062</v>
       </c>
     </row>
     <row r="37">
@@ -7359,7 +7359,7 @@
         <v>115</v>
       </c>
       <c r="C38">
-        <v>-1.1075335686445367</v>
+        <v>-1.0781815590043224</v>
       </c>
     </row>
     <row r="39">
@@ -7381,7 +7381,7 @@
         <v>117</v>
       </c>
       <c r="C40">
-        <v>-0.81295773521112213</v>
+        <v>-0.37962537663809914</v>
       </c>
     </row>
     <row r="41">
@@ -7392,7 +7392,7 @@
         <v>118</v>
       </c>
       <c r="C41">
-        <v>-14.918085530521617</v>
+        <v>-15.168198039446652</v>
       </c>
     </row>
     <row r="42">
@@ -7414,7 +7414,7 @@
         <v>85</v>
       </c>
       <c r="C43">
-        <v>-0.23785360307364919</v>
+        <v>-0.23480801490802339</v>
       </c>
     </row>
     <row r="44">
@@ -7425,7 +7425,7 @@
         <v>42</v>
       </c>
       <c r="C44">
-        <v>8.8240210278873601</v>
+        <v>8.8040577253831938</v>
       </c>
     </row>
     <row r="45">
@@ -7436,7 +7436,7 @@
         <v>43</v>
       </c>
       <c r="C45">
-        <v>-0.18088968169257946</v>
+        <v>-0.18044622342089697</v>
       </c>
     </row>
     <row r="46">
@@ -7458,7 +7458,7 @@
         <v>87</v>
       </c>
       <c r="C47">
-        <v>-0.1591520996977123</v>
+        <v>-0.16642872553051377</v>
       </c>
     </row>
     <row r="48">
@@ -7480,7 +7480,7 @@
         <v>89</v>
       </c>
       <c r="C49">
-        <v>-0.36859288968029846</v>
+        <v>-0.38073209252714729</v>
       </c>
     </row>
     <row r="50">
@@ -7502,7 +7502,7 @@
         <v>91</v>
       </c>
       <c r="C51">
-        <v>-0.42637741228277481</v>
+        <v>-0.3853563420191613</v>
       </c>
     </row>
     <row r="52">
@@ -7524,7 +7524,7 @@
         <v>93</v>
       </c>
       <c r="C53">
-        <v>-0.20249546535842691</v>
+        <v>-0.12242073983301567</v>
       </c>
     </row>
     <row r="54">
@@ -7546,7 +7546,7 @@
         <v>95</v>
       </c>
       <c r="C55">
-        <v>-0.21596794938438812</v>
+        <v>-0.178735591877868</v>
       </c>
     </row>
     <row r="56">
@@ -7568,7 +7568,7 @@
         <v>97</v>
       </c>
       <c r="C57">
-        <v>-0.1587680698610916</v>
+        <v>-0.12014072966666636</v>
       </c>
     </row>
     <row r="58">
@@ -7590,7 +7590,7 @@
         <v>99</v>
       </c>
       <c r="C59">
-        <v>-0.27067698873958973</v>
+        <v>-0.21744199190824959</v>
       </c>
     </row>
     <row r="60">
@@ -7612,7 +7612,7 @@
         <v>101</v>
       </c>
       <c r="C61">
-        <v>0.11910564542282348</v>
+        <v>0.1714699624440045</v>
       </c>
     </row>
     <row r="62">
@@ -7634,7 +7634,7 @@
         <v>103</v>
       </c>
       <c r="C63">
-        <v>0.24762267817997061</v>
+        <v>0.28639811284172306</v>
       </c>
     </row>
     <row r="64">
@@ -7656,7 +7656,7 @@
         <v>105</v>
       </c>
       <c r="C65">
-        <v>-0.12951159737455664</v>
+        <v>-0.092036890602620033</v>
       </c>
     </row>
     <row r="66">
@@ -7678,7 +7678,7 @@
         <v>107</v>
       </c>
       <c r="C67">
-        <v>-0.50536476666537855</v>
+        <v>-0.45876162849996499</v>
       </c>
     </row>
     <row r="68">
@@ -7700,7 +7700,7 @@
         <v>109</v>
       </c>
       <c r="C69">
-        <v>-0.48168257165260159</v>
+        <v>-0.43919223043408767</v>
       </c>
     </row>
     <row r="70">
@@ -7722,7 +7722,7 @@
         <v>111</v>
       </c>
       <c r="C71">
-        <v>-0.78292107573527381</v>
+        <v>-0.73964734270429722</v>
       </c>
     </row>
     <row r="72">
@@ -7733,7 +7733,7 @@
         <v>57</v>
       </c>
       <c r="C72">
-        <v>0.054867534863794483</v>
+        <v>0.055375566550119271</v>
       </c>
     </row>
     <row r="73">
@@ -7744,7 +7744,7 @@
         <v>58</v>
       </c>
       <c r="C73">
-        <v>-0.32741713755744806</v>
+        <v>-0.34099814027199005</v>
       </c>
     </row>
     <row r="74">
@@ -7755,7 +7755,7 @@
         <v>59</v>
       </c>
       <c r="C74">
-        <v>-0.047058936946074735</v>
+        <v>-0.052307869785393174</v>
       </c>
     </row>
     <row r="75">
@@ -7777,7 +7777,7 @@
         <v>113</v>
       </c>
       <c r="C76">
-        <v>-0.17457932899162343</v>
+        <v>-0.16501786126126664</v>
       </c>
     </row>
     <row r="77">
@@ -7799,7 +7799,7 @@
         <v>115</v>
       </c>
       <c r="C78">
-        <v>-1.1075335686445367</v>
+        <v>-1.0781815590043224</v>
       </c>
     </row>
     <row r="79">
@@ -7821,7 +7821,7 @@
         <v>117</v>
       </c>
       <c r="C80">
-        <v>-0.81295773521112213</v>
+        <v>-0.37962537663809914</v>
       </c>
     </row>
     <row r="81">
@@ -7832,7 +7832,7 @@
         <v>118</v>
       </c>
       <c r="C81">
-        <v>-105.95478992301595</v>
+        <v>-105.77487952399589</v>
       </c>
     </row>
   </sheetData>
@@ -7929,76 +7929,76 @@
         <v>121</v>
       </c>
       <c r="B2">
-        <v>-0.23785360307364919</v>
+        <v>-0.23480801490802339</v>
       </c>
       <c r="C2">
-        <v>0.011616632641414009</v>
+        <v>0.011600194766253737</v>
       </c>
       <c r="D2">
-        <v>0.0055064974450513915</v>
+        <v>0.0050055860381973405</v>
       </c>
       <c r="E2">
-        <v>-0.00013231952349082975</v>
+        <v>-0.00011957584110140236</v>
       </c>
       <c r="F2">
-        <v>0.00096879204985659282</v>
+        <v>0.0010022687388788476</v>
       </c>
       <c r="G2">
-        <v>0.0015209414461064595</v>
+        <v>0.0016293962721757468</v>
       </c>
       <c r="H2">
-        <v>0.0002769460158475761</v>
+        <v>-8.8717751448658382e-005</v>
       </c>
       <c r="I2">
-        <v>0.00073527837626894386</v>
+        <v>0.00012285930966221667</v>
       </c>
       <c r="J2">
-        <v>-0.0010128109284132548</v>
+        <v>-0.0014166606794765722</v>
       </c>
       <c r="K2">
-        <v>-0.00020316866227121399</v>
+        <v>-0.00059542029173049018</v>
       </c>
       <c r="L2">
-        <v>0.0010734176620697128</v>
+        <v>0.00048753383370077731</v>
       </c>
       <c r="M2">
-        <v>-0.0011863819372699208</v>
+        <v>-0.0016537061051955311</v>
       </c>
       <c r="N2">
-        <v>-0.0015764955372397568</v>
+        <v>-0.0019518039540231619</v>
       </c>
       <c r="O2">
-        <v>-0.00066943176298618384</v>
+        <v>-0.0010214076944866099</v>
       </c>
       <c r="P2">
-        <v>0.00026525917372310253</v>
+        <v>0.00025339546330360697</v>
       </c>
       <c r="Q2">
-        <v>-0.0015493619379225319</v>
+        <v>-0.0016265236491419229</v>
       </c>
       <c r="R2">
-        <v>-0.067072731632742216</v>
+        <v>-0.061653181327328083</v>
       </c>
       <c r="S2">
-        <v>-0.0021723445121804852</v>
+        <v>-0.0021479696872344031</v>
       </c>
       <c r="T2">
-        <v>2.9912850119951391e-005</v>
+        <v>2.9590155677698295e-005</v>
       </c>
       <c r="U2">
-        <v>0.0033195195714538633</v>
+        <v>0.0033523580722680277</v>
       </c>
       <c r="V2">
-        <v>-0.00035725022737280844</v>
+        <v>-0.00073223705583846455</v>
       </c>
       <c r="W2">
-        <v>0.00010480757327048515</v>
+        <v>0.00010134049971374737</v>
       </c>
       <c r="X2">
-        <v>-0.0011087782332625095</v>
+        <v>-0.0011658801186762392</v>
       </c>
       <c r="Y2">
-        <v>0.024732974339711937</v>
+        <v>0.024774009099340716</v>
       </c>
     </row>
     <row r="3">
@@ -8006,76 +8006,76 @@
         <v>122</v>
       </c>
       <c r="B3">
-        <v>1.5901415283540126</v>
+        <v>1.6101315656341801</v>
       </c>
       <c r="C3">
-        <v>0.0055064974450513915</v>
+        <v>0.0050055860381973405</v>
       </c>
       <c r="D3">
-        <v>1.0085565001054837</v>
+        <v>1.0103522831490463</v>
       </c>
       <c r="E3">
-        <v>-0.025457445407800709</v>
+        <v>-0.025481874008355457</v>
       </c>
       <c r="F3">
-        <v>-0.0043193432568506065</v>
+        <v>-0.0051853881561403801</v>
       </c>
       <c r="G3">
-        <v>-0.029394003081649155</v>
+        <v>-0.032578123215155644</v>
       </c>
       <c r="H3">
-        <v>-0.013679290943683484</v>
+        <v>-0.0071968018052798784</v>
       </c>
       <c r="I3">
-        <v>0.002204521592456001</v>
+        <v>0.01209714092611258</v>
       </c>
       <c r="J3">
-        <v>0.0062659603033340333</v>
+        <v>0.01177673378451739</v>
       </c>
       <c r="K3">
-        <v>-0.0030351305523411763</v>
+        <v>0.0035594906903665623</v>
       </c>
       <c r="L3">
-        <v>-0.0091949362808869169</v>
+        <v>-0.0020873564687597474</v>
       </c>
       <c r="M3">
-        <v>-0.00022649960103674155</v>
+        <v>0.0085612633445623573</v>
       </c>
       <c r="N3">
-        <v>0.0024623046509099954</v>
+        <v>0.0081687621655946487</v>
       </c>
       <c r="O3">
-        <v>-0.052896460845679637</v>
+        <v>-0.050113873309320427</v>
       </c>
       <c r="P3">
-        <v>-0.0017461394088366679</v>
+        <v>-0.0016709817877310833</v>
       </c>
       <c r="Q3">
-        <v>-0.018352104469186201</v>
+        <v>-0.016065328430331222</v>
       </c>
       <c r="R3">
-        <v>-9.8130732386500199</v>
+        <v>-9.8434658703243247</v>
       </c>
       <c r="S3">
-        <v>-0.0053756718422006845</v>
+        <v>-0.0069745789592231579</v>
       </c>
       <c r="T3">
-        <v>5.5729989433851461e-005</v>
+        <v>9.288503751423376e-005</v>
       </c>
       <c r="U3">
-        <v>-0.0014954922560221203</v>
+        <v>-0.0025978041191392514</v>
       </c>
       <c r="V3">
-        <v>-0.0028276095273021915</v>
+        <v>0.0030527382646219204</v>
       </c>
       <c r="W3">
-        <v>0.0011679829375999609</v>
+        <v>0.0011978923805470907</v>
       </c>
       <c r="X3">
-        <v>-0.0041545232945605932</v>
+        <v>-0.0030309269420318551</v>
       </c>
       <c r="Y3">
-        <v>0.07649619665720328</v>
+        <v>0.08845858048279176</v>
       </c>
     </row>
     <row r="4">
@@ -8083,76 +8083,76 @@
         <v>123</v>
       </c>
       <c r="B4">
-        <v>-0.028065130654565694</v>
+        <v>-0.028594550571658713</v>
       </c>
       <c r="C4">
-        <v>-0.00013231952349082975</v>
+        <v>-0.00011957584110140236</v>
       </c>
       <c r="D4">
-        <v>-0.025457445407800709</v>
+        <v>-0.025481874008355457</v>
       </c>
       <c r="E4">
-        <v>0.00064497833997567309</v>
+        <v>0.00064504679194207185</v>
       </c>
       <c r="F4">
-        <v>0.00011792451045356111</v>
+        <v>0.0001386158500339072</v>
       </c>
       <c r="G4">
-        <v>0.00078028925920869984</v>
+        <v>0.00085822688684960907</v>
       </c>
       <c r="H4">
-        <v>0.00030355172121452836</v>
+        <v>0.00014587861338733707</v>
       </c>
       <c r="I4">
-        <v>-7.8828250259784478e-005</v>
+        <v>-0.00031833445427680902</v>
       </c>
       <c r="J4">
-        <v>-0.00018070821664923172</v>
+        <v>-0.00031379892751168676</v>
       </c>
       <c r="K4">
-        <v>5.656716074288265e-005</v>
+        <v>-0.0001032435624626111</v>
       </c>
       <c r="L4">
-        <v>0.00019996332053127437</v>
+        <v>2.9928944102143044e-005</v>
       </c>
       <c r="M4">
-        <v>-8.1106328057707714e-006</v>
+        <v>-0.00022190466296702441</v>
       </c>
       <c r="N4">
-        <v>-7.3260790072397791e-005</v>
+        <v>-0.00021141589478900714</v>
       </c>
       <c r="O4">
-        <v>0.00129998868479327</v>
+        <v>0.0012339145070637686</v>
       </c>
       <c r="P4">
-        <v>4.4138726323535228e-005</v>
+        <v>4.2405001270426701e-005</v>
       </c>
       <c r="Q4">
-        <v>0.00036800309077190084</v>
+        <v>0.00031135717916891853</v>
       </c>
       <c r="R4">
-        <v>0.2469000750380746</v>
+        <v>0.24746153844676486</v>
       </c>
       <c r="S4">
-        <v>0.00016325164573825508</v>
+        <v>0.0002020355750934036</v>
       </c>
       <c r="T4">
-        <v>-1.8853098154217488e-006</v>
+        <v>-2.7915235999184802e-006</v>
       </c>
       <c r="U4">
-        <v>5.3986813111875914e-005</v>
+        <v>8.0483989365072678e-005</v>
       </c>
       <c r="V4">
-        <v>4.3977759216249116e-005</v>
+        <v>-9.8061596233026257e-005</v>
       </c>
       <c r="W4">
-        <v>-2.8980675775335976e-005</v>
+        <v>-2.967949052247506e-005</v>
       </c>
       <c r="X4">
-        <v>8.8586617717276685e-005</v>
+        <v>6.125105545367205e-005</v>
       </c>
       <c r="Y4">
-        <v>-0.0022888856122253052</v>
+        <v>-0.002577557211566996</v>
       </c>
     </row>
     <row r="5">
@@ -8160,76 +8160,76 @@
         <v>124</v>
       </c>
       <c r="B5">
-        <v>-0.1591520996977123</v>
+        <v>-0.16642872553051377</v>
       </c>
       <c r="C5">
-        <v>0.00096879204985659282</v>
+        <v>0.0010022687388788476</v>
       </c>
       <c r="D5">
-        <v>-0.0043193432568506065</v>
+        <v>-0.0051853881561403801</v>
       </c>
       <c r="E5">
-        <v>0.00011792451045356111</v>
+        <v>0.0001386158500339072</v>
       </c>
       <c r="F5">
-        <v>0.022997011101271649</v>
+        <v>0.023080527231599122</v>
       </c>
       <c r="G5">
-        <v>0.019593725352441735</v>
+        <v>0.019807784312091396</v>
       </c>
       <c r="H5">
-        <v>-0.0039939750508961609</v>
+        <v>-0.0036482692376902399</v>
       </c>
       <c r="I5">
-        <v>-0.0027312370734353282</v>
+        <v>-0.0027171126110038975</v>
       </c>
       <c r="J5">
-        <v>-0.002456541760120879</v>
+        <v>-0.0021754371868854677</v>
       </c>
       <c r="K5">
-        <v>-0.0026591811956800347</v>
+        <v>-0.0024427342623351833</v>
       </c>
       <c r="L5">
-        <v>-0.0018878052988861947</v>
+        <v>-0.0016674131671266922</v>
       </c>
       <c r="M5">
-        <v>-0.0039419527922578169</v>
+        <v>-0.003760374077736774</v>
       </c>
       <c r="N5">
-        <v>-0.0025105356060551188</v>
+        <v>-0.0021617289336707916</v>
       </c>
       <c r="O5">
-        <v>-0.0088385237557335808</v>
+        <v>-0.0086199259316448555</v>
       </c>
       <c r="P5">
-        <v>0.00023950373411577388</v>
+        <v>0.0002321184502152127</v>
       </c>
       <c r="Q5">
-        <v>-0.0011291593329799928</v>
+        <v>-0.00096024117423127581</v>
       </c>
       <c r="R5">
-        <v>0.017927623939530436</v>
+        <v>0.026421095413848843</v>
       </c>
       <c r="S5">
-        <v>-0.0039632207248863072</v>
+        <v>-0.0037908075296283344</v>
       </c>
       <c r="T5">
-        <v>8.0000970881053714e-005</v>
+        <v>7.5322762958819232e-005</v>
       </c>
       <c r="U5">
-        <v>0.018512791175171919</v>
+        <v>0.018516024929112217</v>
       </c>
       <c r="V5">
-        <v>-0.0022484505412503283</v>
+        <v>-0.0019025985775990538</v>
       </c>
       <c r="W5">
-        <v>-1.9443095666656004e-005</v>
+        <v>-2.3992212417232617e-005</v>
       </c>
       <c r="X5">
-        <v>0.00011521200843341017</v>
+        <v>0.00038409323747300161</v>
       </c>
       <c r="Y5">
-        <v>0.031522895658933014</v>
+        <v>0.029603221311972683</v>
       </c>
     </row>
     <row r="6">
@@ -8237,76 +8237,76 @@
         <v>125</v>
       </c>
       <c r="B6">
-        <v>-1.2702598307148392</v>
+        <v>-1.281862961196319</v>
       </c>
       <c r="C6">
-        <v>0.0015209414461064595</v>
+        <v>0.0016293962721757468</v>
       </c>
       <c r="D6">
-        <v>-0.029394003081649155</v>
+        <v>-0.032578123215155644</v>
       </c>
       <c r="E6">
-        <v>0.00078028925920869984</v>
+        <v>0.00085822688684960907</v>
       </c>
       <c r="F6">
-        <v>0.019593725352441735</v>
+        <v>0.019807784312091396</v>
       </c>
       <c r="G6">
-        <v>0.052786647045697105</v>
+        <v>0.053455231368507362</v>
       </c>
       <c r="H6">
-        <v>-0.0048052776588599772</v>
+        <v>-0.0042048317137711715</v>
       </c>
       <c r="I6">
-        <v>-0.0042345711138580978</v>
+        <v>-0.0035999041327304838</v>
       </c>
       <c r="J6">
-        <v>-0.0019005835757315379</v>
+        <v>-0.001168736333851228</v>
       </c>
       <c r="K6">
-        <v>-0.0046566422053659021</v>
+        <v>-0.0042183003688922114</v>
       </c>
       <c r="L6">
-        <v>0.00030980780668507686</v>
+        <v>8.5699678498040582e-005</v>
       </c>
       <c r="M6">
-        <v>-0.0042559827417372924</v>
+        <v>-0.00419245465145848</v>
       </c>
       <c r="N6">
-        <v>-0.0033315713805505895</v>
+        <v>-0.0027373275853670095</v>
       </c>
       <c r="O6">
-        <v>-0.013881156556067236</v>
+        <v>-0.013154312529508244</v>
       </c>
       <c r="P6">
-        <v>8.2795999871123163e-005</v>
+        <v>2.5931568473829892e-005</v>
       </c>
       <c r="Q6">
-        <v>-0.012687099278331244</v>
+        <v>-0.012379642323366812</v>
       </c>
       <c r="R6">
-        <v>0.24469957461451369</v>
+        <v>0.27643551668800465</v>
       </c>
       <c r="S6">
-        <v>-0.0043930309503979331</v>
+        <v>-0.0043955746350505948</v>
       </c>
       <c r="T6">
-        <v>9.0725994229884344e-005</v>
+        <v>8.9900913539709987e-005</v>
       </c>
       <c r="U6">
-        <v>0.016880002092697272</v>
+        <v>0.017011674573388348</v>
       </c>
       <c r="V6">
-        <v>-0.0027740734688043792</v>
+        <v>-0.0021052664239159455</v>
       </c>
       <c r="W6">
-        <v>-0.0001657032621199118</v>
+        <v>-0.00018134841572720644</v>
       </c>
       <c r="X6">
-        <v>-0.00043251249552319834</v>
+        <v>0.00010246945497852794</v>
       </c>
       <c r="Y6">
-        <v>0.040626484403742058</v>
+        <v>0.040302395968057014</v>
       </c>
     </row>
     <row r="7">
@@ -8314,76 +8314,76 @@
         <v>126</v>
       </c>
       <c r="B7">
-        <v>-0.42637741228277481</v>
+        <v>-0.3853563420191613</v>
       </c>
       <c r="C7">
-        <v>0.0002769460158475761</v>
+        <v>-8.8717751448658382e-005</v>
       </c>
       <c r="D7">
-        <v>-0.013679290943683484</v>
+        <v>-0.0071968018052798784</v>
       </c>
       <c r="E7">
-        <v>0.00030355172121452836</v>
+        <v>0.00014587861338733707</v>
       </c>
       <c r="F7">
-        <v>-0.0039939750508961609</v>
+        <v>-0.0036482692376902399</v>
       </c>
       <c r="G7">
-        <v>-0.0048052776588599772</v>
+        <v>-0.0042048317137711715</v>
       </c>
       <c r="H7">
-        <v>0.086189807785035225</v>
+        <v>0.089708680185646913</v>
       </c>
       <c r="I7">
-        <v>0.03402118205024382</v>
+        <v>0.037278422890968763</v>
       </c>
       <c r="J7">
-        <v>0.034342729672846198</v>
+        <v>0.037363213025633488</v>
       </c>
       <c r="K7">
-        <v>0.035002447848571761</v>
+        <v>0.038155447561434304</v>
       </c>
       <c r="L7">
-        <v>0.033791697907112693</v>
+        <v>0.03659850847509076</v>
       </c>
       <c r="M7">
-        <v>0.034643039014791654</v>
+        <v>0.037396439877842975</v>
       </c>
       <c r="N7">
-        <v>0.034200499569412408</v>
+        <v>0.037221430235005008</v>
       </c>
       <c r="O7">
-        <v>0.036613140979260946</v>
+        <v>0.04059312930411825</v>
       </c>
       <c r="P7">
-        <v>-0.00010688040858591004</v>
+        <v>-0.00019655588422281314</v>
       </c>
       <c r="Q7">
-        <v>0.013724888147351086</v>
+        <v>0.015742117213027578</v>
       </c>
       <c r="R7">
-        <v>0.11658808281077201</v>
+        <v>0.048757591469960296</v>
       </c>
       <c r="S7">
-        <v>0.025343245015255332</v>
+        <v>0.027851611571655773</v>
       </c>
       <c r="T7">
-        <v>-0.00056733673457738285</v>
+        <v>-0.00062280729808751828</v>
       </c>
       <c r="U7">
-        <v>-0.011962193423956404</v>
+        <v>-0.011726568370736094</v>
       </c>
       <c r="V7">
-        <v>0.03450133792492948</v>
+        <v>0.037729354320394391</v>
       </c>
       <c r="W7">
-        <v>-0.00049062748545745352</v>
+        <v>-0.00044537857244799056</v>
       </c>
       <c r="X7">
-        <v>0.01454310686640483</v>
+        <v>0.016121074389093219</v>
       </c>
       <c r="Y7">
-        <v>-0.30442195008988482</v>
+        <v>-0.33665197905406075</v>
       </c>
     </row>
     <row r="8">
@@ -8391,76 +8391,76 @@
         <v>127</v>
       </c>
       <c r="B8">
-        <v>-0.20249546535842691</v>
+        <v>-0.12242073983301567</v>
       </c>
       <c r="C8">
-        <v>0.00073527837626894386</v>
+        <v>0.00012285930966221667</v>
       </c>
       <c r="D8">
-        <v>0.002204521592456001</v>
+        <v>0.01209714092611258</v>
       </c>
       <c r="E8">
-        <v>-7.8828250259784478e-005</v>
+        <v>-0.00031833445427680902</v>
       </c>
       <c r="F8">
-        <v>-0.0027312370734353282</v>
+        <v>-0.0027171126110038975</v>
       </c>
       <c r="G8">
-        <v>-0.0042345711138580978</v>
+        <v>-0.0035999041327304838</v>
       </c>
       <c r="H8">
-        <v>0.03402118205024382</v>
+        <v>0.037278422890968763</v>
       </c>
       <c r="I8">
-        <v>0.060527331115196571</v>
+        <v>0.062950552485918826</v>
       </c>
       <c r="J8">
-        <v>0.032422310956843337</v>
+        <v>0.035110813978553368</v>
       </c>
       <c r="K8">
-        <v>0.032416340657893193</v>
+        <v>0.035276306226947808</v>
       </c>
       <c r="L8">
-        <v>0.03182131335026632</v>
+        <v>0.034408704893676437</v>
       </c>
       <c r="M8">
-        <v>0.032273093362116097</v>
+        <v>0.034785312732684287</v>
       </c>
       <c r="N8">
-        <v>0.03202128439098488</v>
+        <v>0.034680657116886823</v>
       </c>
       <c r="O8">
-        <v>0.032605208706014001</v>
+        <v>0.036409223999904428</v>
       </c>
       <c r="P8">
-        <v>0.0010244427523525188</v>
+        <v>0.00080955696019207029</v>
       </c>
       <c r="Q8">
-        <v>0.0081222268648945602</v>
+        <v>0.010282544292566444</v>
       </c>
       <c r="R8">
-        <v>-0.059870244551011406</v>
+        <v>-0.15982575715901284</v>
       </c>
       <c r="S8">
-        <v>0.018295044762799396</v>
+        <v>0.021396976728628194</v>
       </c>
       <c r="T8">
-        <v>-0.00041528945465330519</v>
+        <v>-0.00048205370469504779</v>
       </c>
       <c r="U8">
-        <v>-0.010198393913999355</v>
+        <v>-0.010110711546489289</v>
       </c>
       <c r="V8">
-        <v>0.033041541897449948</v>
+        <v>0.035814895253189073</v>
       </c>
       <c r="W8">
-        <v>-0.00019913699048554925</v>
+        <v>-9.0662794942340423e-005</v>
       </c>
       <c r="X8">
-        <v>0.010794361798935927</v>
+        <v>0.012150033359423617</v>
       </c>
       <c r="Y8">
-        <v>-0.22758677465104993</v>
+        <v>-0.26732370303095609</v>
       </c>
     </row>
     <row r="9">
@@ -8468,76 +8468,76 @@
         <v>128</v>
       </c>
       <c r="B9">
-        <v>-0.21596794938438812</v>
+        <v>-0.178735591877868</v>
       </c>
       <c r="C9">
-        <v>-0.0010128109284132548</v>
+        <v>-0.0014166606794765722</v>
       </c>
       <c r="D9">
-        <v>0.0062659603033340333</v>
+        <v>0.01177673378451739</v>
       </c>
       <c r="E9">
-        <v>-0.00018070821664923172</v>
+        <v>-0.00031379892751168676</v>
       </c>
       <c r="F9">
-        <v>-0.002456541760120879</v>
+        <v>-0.0021754371868854677</v>
       </c>
       <c r="G9">
-        <v>-0.0019005835757315379</v>
+        <v>-0.001168736333851228</v>
       </c>
       <c r="H9">
-        <v>0.034342729672846198</v>
+        <v>0.037363213025633488</v>
       </c>
       <c r="I9">
-        <v>0.032422310956843337</v>
+        <v>0.035110813978553368</v>
       </c>
       <c r="J9">
-        <v>0.061938465013951748</v>
+        <v>0.064637380662935534</v>
       </c>
       <c r="K9">
-        <v>0.033024638915246582</v>
+        <v>0.03569923119796601</v>
       </c>
       <c r="L9">
-        <v>0.03204611818454161</v>
+        <v>0.034512943252256477</v>
       </c>
       <c r="M9">
-        <v>0.033001997536372937</v>
+        <v>0.035364101035781227</v>
       </c>
       <c r="N9">
-        <v>0.032495847160949387</v>
+        <v>0.035049741295243894</v>
       </c>
       <c r="O9">
-        <v>0.034663391495461798</v>
+        <v>0.038129942432039432</v>
       </c>
       <c r="P9">
-        <v>0.00015635146654439515</v>
+        <v>9.6009065509437889e-005</v>
       </c>
       <c r="Q9">
-        <v>0.0075019305829390204</v>
+        <v>0.0091654872440610734</v>
       </c>
       <c r="R9">
-        <v>-0.088297088709374139</v>
+        <v>-0.14656272537621404</v>
       </c>
       <c r="S9">
-        <v>0.024202043702766907</v>
+        <v>0.026287512873777008</v>
       </c>
       <c r="T9">
-        <v>-0.00052865368694297128</v>
+        <v>-0.00057439260828632817</v>
       </c>
       <c r="U9">
-        <v>-0.010838627257470944</v>
+        <v>-0.010577870784374603</v>
       </c>
       <c r="V9">
-        <v>0.032142782782399973</v>
+        <v>0.034867133312834891</v>
       </c>
       <c r="W9">
-        <v>-0.00024788203587096716</v>
+        <v>-0.00019626035076312815</v>
       </c>
       <c r="X9">
-        <v>0.010615858932583887</v>
+        <v>0.011898253088559733</v>
       </c>
       <c r="Y9">
-        <v>-0.29984310319552049</v>
+        <v>-0.3270005656427894</v>
       </c>
     </row>
     <row r="10">
@@ -8545,76 +8545,76 @@
         <v>129</v>
       </c>
       <c r="B10">
-        <v>-0.1587680698610916</v>
+        <v>-0.12014072966666636</v>
       </c>
       <c r="C10">
-        <v>-0.00020316866227121399</v>
+        <v>-0.00059542029173049018</v>
       </c>
       <c r="D10">
-        <v>-0.0030351305523411763</v>
+        <v>0.0035594906903665623</v>
       </c>
       <c r="E10">
-        <v>5.656716074288265e-005</v>
+        <v>-0.0001032435624626111</v>
       </c>
       <c r="F10">
-        <v>-0.0026591811956800347</v>
+        <v>-0.0024427342623351833</v>
       </c>
       <c r="G10">
-        <v>-0.0046566422053659021</v>
+        <v>-0.0042183003688922114</v>
       </c>
       <c r="H10">
-        <v>0.035002447848571761</v>
+        <v>0.038155447561434304</v>
       </c>
       <c r="I10">
-        <v>0.032416340657893193</v>
+        <v>0.035276306226947808</v>
       </c>
       <c r="J10">
-        <v>0.033024638915246582</v>
+        <v>0.03569923119796601</v>
       </c>
       <c r="K10">
-        <v>0.067104494618674682</v>
+        <v>0.069685344964392923</v>
       </c>
       <c r="L10">
-        <v>0.032186857773636113</v>
+        <v>0.034740746517458017</v>
       </c>
       <c r="M10">
-        <v>0.033287091394124425</v>
+        <v>0.035815710343329386</v>
       </c>
       <c r="N10">
-        <v>0.032768720983518282</v>
+        <v>0.03544302503196587</v>
       </c>
       <c r="O10">
-        <v>0.033849778179795259</v>
+        <v>0.037412665967184643</v>
       </c>
       <c r="P10">
-        <v>-0.00029669082041846098</v>
+        <v>-0.00038909235821529549</v>
       </c>
       <c r="Q10">
-        <v>0.013107080925647448</v>
+        <v>0.014958086345313135</v>
       </c>
       <c r="R10">
-        <v>0.011061011486085574</v>
+        <v>-0.057553562089717958</v>
       </c>
       <c r="S10">
-        <v>0.024445562842894824</v>
+        <v>0.026471737283380519</v>
       </c>
       <c r="T10">
-        <v>-0.00053212764160620954</v>
+        <v>-0.00057677497640197116</v>
       </c>
       <c r="U10">
-        <v>-0.012131069420982993</v>
+        <v>-0.011938635405631262</v>
       </c>
       <c r="V10">
-        <v>0.032959878803592788</v>
+        <v>0.035779577436945778</v>
       </c>
       <c r="W10">
-        <v>-1.2222456203655093e-005</v>
+        <v>4.0034442430125322e-005</v>
       </c>
       <c r="X10">
-        <v>0.012924704928631259</v>
+        <v>0.014251483715287292</v>
       </c>
       <c r="Y10">
-        <v>-0.30787287650249034</v>
+        <v>-0.33431064175664543</v>
       </c>
     </row>
     <row r="11">
@@ -8622,76 +8622,76 @@
         <v>130</v>
       </c>
       <c r="B11">
-        <v>-0.27067698873958973</v>
+        <v>-0.21744199190824959</v>
       </c>
       <c r="C11">
-        <v>0.0010734176620697128</v>
+        <v>0.00048753383370077731</v>
       </c>
       <c r="D11">
-        <v>-0.0091949362808869169</v>
+        <v>-0.0020873564687597474</v>
       </c>
       <c r="E11">
-        <v>0.00019996332053127437</v>
+        <v>2.9928944102143044e-005</v>
       </c>
       <c r="F11">
-        <v>-0.0018878052988861947</v>
+        <v>-0.0016674131671266922</v>
       </c>
       <c r="G11">
-        <v>0.00030980780668507686</v>
+        <v>8.5699678498040582e-005</v>
       </c>
       <c r="H11">
-        <v>0.033791697907112693</v>
+        <v>0.03659850847509076</v>
       </c>
       <c r="I11">
-        <v>0.03182131335026632</v>
+        <v>0.034408704893676437</v>
       </c>
       <c r="J11">
-        <v>0.03204611818454161</v>
+        <v>0.034512943252256477</v>
       </c>
       <c r="K11">
-        <v>0.032186857773636113</v>
+        <v>0.034740746517458017</v>
       </c>
       <c r="L11">
-        <v>0.067977433100060672</v>
+        <v>0.06987488689392822</v>
       </c>
       <c r="M11">
-        <v>0.031767046597000068</v>
+        <v>0.034115287110640935</v>
       </c>
       <c r="N11">
-        <v>0.031515408234868487</v>
+        <v>0.033955899218326133</v>
       </c>
       <c r="O11">
-        <v>0.032848219288978082</v>
+        <v>0.0362984855311137</v>
       </c>
       <c r="P11">
-        <v>0.00040506177665122555</v>
+        <v>0.00031270877718056592</v>
       </c>
       <c r="Q11">
-        <v>0.0038130292959741748</v>
+        <v>0.005931414815880472</v>
       </c>
       <c r="R11">
-        <v>0.061960654130356743</v>
+        <v>-0.012116581849915126</v>
       </c>
       <c r="S11">
-        <v>0.030308378665653279</v>
+        <v>0.031652489217684147</v>
       </c>
       <c r="T11">
-        <v>-0.00068866092105616321</v>
+        <v>-0.00071712400867475338</v>
       </c>
       <c r="U11">
-        <v>-0.0093549279849892402</v>
+        <v>-0.0089546294075116759</v>
       </c>
       <c r="V11">
-        <v>0.032320973386020246</v>
+        <v>0.03478560706395839</v>
       </c>
       <c r="W11">
-        <v>-0.00020811961724100456</v>
+        <v>-0.00015294463312843652</v>
       </c>
       <c r="X11">
-        <v>0.01034789896317604</v>
+        <v>0.011385704159522961</v>
       </c>
       <c r="Y11">
-        <v>-0.35857870759930888</v>
+        <v>-0.37749481175084565</v>
       </c>
     </row>
     <row r="12">
@@ -8699,76 +8699,76 @@
         <v>131</v>
       </c>
       <c r="B12">
-        <v>0.11910564542282348</v>
+        <v>0.1714699624440045</v>
       </c>
       <c r="C12">
-        <v>-0.0011863819372699208</v>
+        <v>-0.0016537061051955311</v>
       </c>
       <c r="D12">
-        <v>-0.00022649960103674155</v>
+        <v>0.0085612633445623573</v>
       </c>
       <c r="E12">
-        <v>-8.1106328057707714e-006</v>
+        <v>-0.00022190466296702441</v>
       </c>
       <c r="F12">
-        <v>-0.0039419527922578169</v>
+        <v>-0.003760374077736774</v>
       </c>
       <c r="G12">
-        <v>-0.0042559827417372924</v>
+        <v>-0.00419245465145848</v>
       </c>
       <c r="H12">
-        <v>0.034643039014791654</v>
+        <v>0.037396439877842975</v>
       </c>
       <c r="I12">
-        <v>0.032273093362116097</v>
+        <v>0.034785312732684287</v>
       </c>
       <c r="J12">
-        <v>0.033001997536372937</v>
+        <v>0.035364101035781227</v>
       </c>
       <c r="K12">
-        <v>0.033287091394124425</v>
+        <v>0.035815710343329386</v>
       </c>
       <c r="L12">
-        <v>0.031767046597000068</v>
+        <v>0.034115287110640935</v>
       </c>
       <c r="M12">
-        <v>0.075181512350129279</v>
+        <v>0.0774707047310845</v>
       </c>
       <c r="N12">
-        <v>0.032156686415003834</v>
+        <v>0.03451793409518826</v>
       </c>
       <c r="O12">
-        <v>0.032764390417559693</v>
+        <v>0.035959846740752519</v>
       </c>
       <c r="P12">
-        <v>-0.00022164430588631059</v>
+        <v>-0.00034128859449310462</v>
       </c>
       <c r="Q12">
-        <v>0.01093895202392052</v>
+        <v>0.012477715620751267</v>
       </c>
       <c r="R12">
-        <v>-0.018792616257869897</v>
+        <v>-0.10829269145338025</v>
       </c>
       <c r="S12">
-        <v>0.0024055358601282675</v>
+        <v>0.0047330737128514627</v>
       </c>
       <c r="T12">
-        <v>-5.2908483174344883e-005</v>
+        <v>-0.00010307525183994278</v>
       </c>
       <c r="U12">
-        <v>-0.014301508269201998</v>
+        <v>-0.014131278880868414</v>
       </c>
       <c r="V12">
-        <v>0.03283982377016216</v>
+        <v>0.035239103490789986</v>
       </c>
       <c r="W12">
-        <v>-0.0003489904910296104</v>
+        <v>-0.00029541989996949649</v>
       </c>
       <c r="X12">
-        <v>0.013540596040239088</v>
+        <v>0.014553713465593719</v>
       </c>
       <c r="Y12">
-        <v>-0.050034961869197758</v>
+        <v>-0.079891486281387758</v>
       </c>
     </row>
     <row r="13">
@@ -8776,76 +8776,76 @@
         <v>132</v>
       </c>
       <c r="B13">
-        <v>0.24762267817997061</v>
+        <v>0.28639811284172306</v>
       </c>
       <c r="C13">
-        <v>-0.0015764955372397568</v>
+        <v>-0.0019518039540231619</v>
       </c>
       <c r="D13">
-        <v>0.0024623046509099954</v>
+        <v>0.0081687621655946487</v>
       </c>
       <c r="E13">
-        <v>-7.3260790072397791e-005</v>
+        <v>-0.00021141589478900714</v>
       </c>
       <c r="F13">
-        <v>-0.0025105356060551188</v>
+        <v>-0.0021617289336707916</v>
       </c>
       <c r="G13">
-        <v>-0.0033315713805505895</v>
+        <v>-0.0027373275853670095</v>
       </c>
       <c r="H13">
-        <v>0.034200499569412408</v>
+        <v>0.037221430235005008</v>
       </c>
       <c r="I13">
-        <v>0.03202128439098488</v>
+        <v>0.034680657116886823</v>
       </c>
       <c r="J13">
-        <v>0.032495847160949387</v>
+        <v>0.035049741295243894</v>
       </c>
       <c r="K13">
-        <v>0.032768720983518282</v>
+        <v>0.03544302503196587</v>
       </c>
       <c r="L13">
-        <v>0.031515408234868487</v>
+        <v>0.033955899218326133</v>
       </c>
       <c r="M13">
-        <v>0.032156686415003834</v>
+        <v>0.03451793409518826</v>
       </c>
       <c r="N13">
-        <v>0.056766425710812515</v>
+        <v>0.059151982905769354</v>
       </c>
       <c r="O13">
-        <v>0.032847977798675411</v>
+        <v>0.036243735092450921</v>
       </c>
       <c r="P13">
-        <v>0.00022747184788025833</v>
+        <v>0.00012429513221842107</v>
       </c>
       <c r="Q13">
-        <v>0.0088897148624506664</v>
+        <v>0.01080783058147204</v>
       </c>
       <c r="R13">
-        <v>-0.053476465793885763</v>
+        <v>-0.11295246001545697</v>
       </c>
       <c r="S13">
-        <v>0.0092139717919766245</v>
+        <v>0.011248661722093475</v>
       </c>
       <c r="T13">
-        <v>-0.00020350156256729486</v>
+        <v>-0.00024811490074779169</v>
       </c>
       <c r="U13">
-        <v>-0.0099240319987185903</v>
+        <v>-0.0096068176260550951</v>
       </c>
       <c r="V13">
-        <v>0.032806796201812025</v>
+        <v>0.035516343931734522</v>
       </c>
       <c r="W13">
-        <v>2.6074250663096733e-005</v>
+        <v>8.1343278260058113e-005</v>
       </c>
       <c r="X13">
-        <v>0.011879991294211613</v>
+        <v>0.013193402409202463</v>
       </c>
       <c r="Y13">
-        <v>-0.13308490512355586</v>
+        <v>-0.15979253657577508</v>
       </c>
     </row>
     <row r="14">
@@ -8853,76 +8853,76 @@
         <v>133</v>
       </c>
       <c r="B14">
-        <v>0.74701043401792411</v>
+        <v>0.77710142531810378</v>
       </c>
       <c r="C14">
-        <v>-0.00066943176298618384</v>
+        <v>-0.0010214076944866099</v>
       </c>
       <c r="D14">
-        <v>-0.052896460845679637</v>
+        <v>-0.050113873309320427</v>
       </c>
       <c r="E14">
-        <v>0.00129998868479327</v>
+        <v>0.0012339145070637686</v>
       </c>
       <c r="F14">
-        <v>-0.0088385237557335808</v>
+        <v>-0.0086199259316448555</v>
       </c>
       <c r="G14">
-        <v>-0.013881156556067236</v>
+        <v>-0.013154312529508244</v>
       </c>
       <c r="H14">
-        <v>0.036613140979260946</v>
+        <v>0.04059312930411825</v>
       </c>
       <c r="I14">
-        <v>0.032605208706014001</v>
+        <v>0.036409223999904428</v>
       </c>
       <c r="J14">
-        <v>0.034663391495461798</v>
+        <v>0.038129942432039432</v>
       </c>
       <c r="K14">
-        <v>0.033849778179795259</v>
+        <v>0.037412665967184643</v>
       </c>
       <c r="L14">
-        <v>0.032848219288978082</v>
+        <v>0.0362984855311137</v>
       </c>
       <c r="M14">
-        <v>0.032764390417559693</v>
+        <v>0.035959846740752519</v>
       </c>
       <c r="N14">
-        <v>0.032847977798675411</v>
+        <v>0.036243735092450921</v>
       </c>
       <c r="O14">
-        <v>0.21696556137690037</v>
+        <v>0.22037153682665378</v>
       </c>
       <c r="P14">
-        <v>0.0025034302782909489</v>
+        <v>0.0023592092961577269</v>
       </c>
       <c r="Q14">
-        <v>0.01870362085365989</v>
+        <v>0.020937104095120968</v>
       </c>
       <c r="R14">
-        <v>0.45818662124816201</v>
+        <v>0.42757430754859782</v>
       </c>
       <c r="S14">
-        <v>0.017527047739228765</v>
+        <v>0.019726489098207924</v>
       </c>
       <c r="T14">
-        <v>-0.00039314748309713027</v>
+        <v>-0.00044167153187022715</v>
       </c>
       <c r="U14">
-        <v>-0.015591268285219364</v>
+        <v>-0.015516258815562546</v>
       </c>
       <c r="V14">
-        <v>0.032046281910435306</v>
+        <v>0.035651497109209604</v>
       </c>
       <c r="W14">
-        <v>-1.9795718969220432e-005</v>
+        <v>2.2033756845692967e-005</v>
       </c>
       <c r="X14">
-        <v>0.012668443547665482</v>
+        <v>0.014301010019637208</v>
       </c>
       <c r="Y14">
-        <v>-0.21686520544625632</v>
+        <v>-0.24588801049600584</v>
       </c>
     </row>
     <row r="15">
@@ -8930,76 +8930,76 @@
         <v>134</v>
       </c>
       <c r="B15">
-        <v>-0.057496078032922469</v>
+        <v>-0.055770931748341399</v>
       </c>
       <c r="C15">
-        <v>0.00026525917372310253</v>
+        <v>0.00025339546330360697</v>
       </c>
       <c r="D15">
-        <v>-0.0017461394088366679</v>
+        <v>-0.0016709817877310833</v>
       </c>
       <c r="E15">
-        <v>4.4138726323535228e-005</v>
+        <v>4.2405001270426701e-005</v>
       </c>
       <c r="F15">
-        <v>0.00023950373411577388</v>
+        <v>0.0002321184502152127</v>
       </c>
       <c r="G15">
-        <v>8.2795999871123163e-005</v>
+        <v>2.5931568473829892e-005</v>
       </c>
       <c r="H15">
-        <v>-0.00010688040858591004</v>
+        <v>-0.00019655588422281314</v>
       </c>
       <c r="I15">
-        <v>0.0010244427523525188</v>
+        <v>0.00080955696019207029</v>
       </c>
       <c r="J15">
-        <v>0.00015635146654439515</v>
+        <v>9.6009065509437889e-005</v>
       </c>
       <c r="K15">
-        <v>-0.00029669082041846098</v>
+        <v>-0.00038909235821529549</v>
       </c>
       <c r="L15">
-        <v>0.00040506177665122555</v>
+        <v>0.00031270877718056592</v>
       </c>
       <c r="M15">
-        <v>-0.00022164430588631059</v>
+        <v>-0.00034128859449310462</v>
       </c>
       <c r="N15">
-        <v>0.00022747184788025833</v>
+        <v>0.00012429513221842107</v>
       </c>
       <c r="O15">
-        <v>0.0025034302782909489</v>
+        <v>0.0023592092961577269</v>
       </c>
       <c r="P15">
-        <v>0.00086201421028237791</v>
+        <v>0.00085631072148977406</v>
       </c>
       <c r="Q15">
-        <v>-0.00068704121904124412</v>
+        <v>-0.00069112660645502479</v>
       </c>
       <c r="R15">
-        <v>0.0029399655054350711</v>
+        <v>0.0023874332498862345</v>
       </c>
       <c r="S15">
-        <v>0.0004216385643480685</v>
+        <v>0.00043779727632878686</v>
       </c>
       <c r="T15">
-        <v>-9.7557914157508224e-006</v>
+        <v>-1.0019389218519231e-005</v>
       </c>
       <c r="U15">
-        <v>-0.00013697028930906708</v>
+        <v>-0.0001469280205691802</v>
       </c>
       <c r="V15">
-        <v>0.00038421132656732654</v>
+        <v>0.00027120307094364053</v>
       </c>
       <c r="W15">
-        <v>0.0001073898381658414</v>
+        <v>0.00010694134910629394</v>
       </c>
       <c r="X15">
-        <v>0.00016211328558497903</v>
+        <v>0.00012158231909279024</v>
       </c>
       <c r="Y15">
-        <v>-0.0066518892006353289</v>
+        <v>-0.0067380919546416868</v>
       </c>
     </row>
     <row r="16">
@@ -9007,76 +9007,76 @@
         <v>135</v>
       </c>
       <c r="B16">
-        <v>0.64927933970608531</v>
+        <v>0.6583366502225062</v>
       </c>
       <c r="C16">
-        <v>-0.0015493619379225319</v>
+        <v>-0.0016265236491419229</v>
       </c>
       <c r="D16">
-        <v>-0.018352104469186201</v>
+        <v>-0.016065328430331222</v>
       </c>
       <c r="E16">
-        <v>0.00036800309077190084</v>
+        <v>0.00031135717916891853</v>
       </c>
       <c r="F16">
-        <v>-0.0011291593329799928</v>
+        <v>-0.00096024117423127581</v>
       </c>
       <c r="G16">
-        <v>-0.012687099278331244</v>
+        <v>-0.012379642323366812</v>
       </c>
       <c r="H16">
-        <v>0.013724888147351086</v>
+        <v>0.015742117213027578</v>
       </c>
       <c r="I16">
-        <v>0.0081222268648945602</v>
+        <v>0.010282544292566444</v>
       </c>
       <c r="J16">
-        <v>0.0075019305829390204</v>
+        <v>0.0091654872440610734</v>
       </c>
       <c r="K16">
-        <v>0.013107080925647448</v>
+        <v>0.014958086345313135</v>
       </c>
       <c r="L16">
-        <v>0.0038130292959741748</v>
+        <v>0.005931414815880472</v>
       </c>
       <c r="M16">
-        <v>0.01093895202392052</v>
+        <v>0.012477715620751267</v>
       </c>
       <c r="N16">
-        <v>0.0088897148624506664</v>
+        <v>0.01080783058147204</v>
       </c>
       <c r="O16">
-        <v>0.01870362085365989</v>
+        <v>0.020937104095120968</v>
       </c>
       <c r="P16">
-        <v>-0.00068704121904124412</v>
+        <v>-0.00069112660645502479</v>
       </c>
       <c r="Q16">
-        <v>0.11380944691232392</v>
+        <v>0.11460400651292926</v>
       </c>
       <c r="R16">
-        <v>0.20896656617942305</v>
+        <v>0.18414668705229537</v>
       </c>
       <c r="S16">
-        <v>0.0020452459505115273</v>
+        <v>0.0033834955202176622</v>
       </c>
       <c r="T16">
-        <v>-5.0231260278373399e-005</v>
+        <v>-8.034866936091046e-005</v>
       </c>
       <c r="U16">
-        <v>-0.003268305613875231</v>
+        <v>-0.0031736795833913144</v>
       </c>
       <c r="V16">
-        <v>0.0099264511826259328</v>
+        <v>0.011811184389089421</v>
       </c>
       <c r="W16">
-        <v>7.0011269185320807e-005</v>
+        <v>7.9269950659934701e-005</v>
       </c>
       <c r="X16">
-        <v>0.0071875922766534463</v>
+        <v>0.0079680888567978218</v>
       </c>
       <c r="Y16">
-        <v>-0.029827105296814704</v>
+        <v>-0.046786919553689334</v>
       </c>
     </row>
     <row r="17">
@@ -9084,76 +9084,76 @@
         <v>136</v>
       </c>
       <c r="B17">
-        <v>-14.918085530521617</v>
+        <v>-15.168198039446652</v>
       </c>
       <c r="C17">
-        <v>-0.067072731632742216</v>
+        <v>-0.061653181327328083</v>
       </c>
       <c r="D17">
-        <v>-9.8130732386500199</v>
+        <v>-9.8434658703243247</v>
       </c>
       <c r="E17">
-        <v>0.2469000750380746</v>
+        <v>0.24746153844676486</v>
       </c>
       <c r="F17">
-        <v>0.017927623939530436</v>
+        <v>0.026421095413848843</v>
       </c>
       <c r="G17">
-        <v>0.24469957461451369</v>
+        <v>0.27643551668800465</v>
       </c>
       <c r="H17">
-        <v>0.11658808281077201</v>
+        <v>0.048757591469960296</v>
       </c>
       <c r="I17">
-        <v>-0.059870244551011406</v>
+        <v>-0.15982575715901284</v>
       </c>
       <c r="J17">
-        <v>-0.088297088709374139</v>
+        <v>-0.14656272537621404</v>
       </c>
       <c r="K17">
-        <v>0.011061011486085574</v>
+        <v>-0.057553562089717958</v>
       </c>
       <c r="L17">
-        <v>0.061960654130356743</v>
+        <v>-0.012116581849915126</v>
       </c>
       <c r="M17">
-        <v>-0.018792616257869897</v>
+        <v>-0.10829269145338025</v>
       </c>
       <c r="N17">
-        <v>-0.053476465793885763</v>
+        <v>-0.11295246001545697</v>
       </c>
       <c r="O17">
-        <v>0.45818662124816201</v>
+        <v>0.42757430754859782</v>
       </c>
       <c r="P17">
-        <v>0.0029399655054350711</v>
+        <v>0.0023874332498862345</v>
       </c>
       <c r="Q17">
-        <v>0.20896656617942305</v>
+        <v>0.18414668705229537</v>
       </c>
       <c r="R17">
-        <v>96.035944657221066</v>
+        <v>96.460251899654111</v>
       </c>
       <c r="S17">
-        <v>0.025160473611944678</v>
+        <v>0.038553544441519039</v>
       </c>
       <c r="T17">
-        <v>5.1019890994033999e-005</v>
+        <v>-0.00026268848278208738</v>
       </c>
       <c r="U17">
-        <v>0.0032478103691141111</v>
+        <v>0.014214999057012435</v>
       </c>
       <c r="V17">
-        <v>0.001635877137705688</v>
+        <v>-0.059753856202672873</v>
       </c>
       <c r="W17">
-        <v>-0.012925219306456161</v>
+        <v>-0.013269077682751323</v>
       </c>
       <c r="X17">
-        <v>0.031357918407832919</v>
+        <v>0.018837338960273842</v>
       </c>
       <c r="Y17">
-        <v>-0.36516224868337366</v>
+        <v>-0.45273249912037317</v>
       </c>
     </row>
     <row r="18">
@@ -9161,76 +9161,76 @@
         <v>137</v>
       </c>
       <c r="B18">
-        <v>8.8240210278873601</v>
+        <v>8.8040577253831938</v>
       </c>
       <c r="C18">
-        <v>-0.0021723445121804852</v>
+        <v>-0.0021479696872344031</v>
       </c>
       <c r="D18">
-        <v>-0.0053756718422006845</v>
+        <v>-0.0069745789592231579</v>
       </c>
       <c r="E18">
-        <v>0.00016325164573825508</v>
+        <v>0.0002020355750934036</v>
       </c>
       <c r="F18">
-        <v>-0.0039632207248863072</v>
+        <v>-0.0037908075296283344</v>
       </c>
       <c r="G18">
-        <v>-0.0043930309503979331</v>
+        <v>-0.0043955746350505948</v>
       </c>
       <c r="H18">
-        <v>0.025343245015255332</v>
+        <v>0.027851611571655773</v>
       </c>
       <c r="I18">
-        <v>0.018295044762799396</v>
+        <v>0.021396976728628194</v>
       </c>
       <c r="J18">
-        <v>0.024202043702766907</v>
+        <v>0.026287512873777008</v>
       </c>
       <c r="K18">
-        <v>0.024445562842894824</v>
+        <v>0.026471737283380519</v>
       </c>
       <c r="L18">
-        <v>0.030308378665653279</v>
+        <v>0.031652489217684147</v>
       </c>
       <c r="M18">
-        <v>0.0024055358601282675</v>
+        <v>0.0047330737128514627</v>
       </c>
       <c r="N18">
-        <v>0.0092139717919766245</v>
+        <v>0.011248661722093475</v>
       </c>
       <c r="O18">
-        <v>0.017527047739228765</v>
+        <v>0.019726489098207924</v>
       </c>
       <c r="P18">
-        <v>0.0004216385643480685</v>
+        <v>0.00043779727632878686</v>
       </c>
       <c r="Q18">
-        <v>0.0020452459505115273</v>
+        <v>0.0033834955202176622</v>
       </c>
       <c r="R18">
-        <v>0.025160473611944678</v>
+        <v>0.038553544441519039</v>
       </c>
       <c r="S18">
-        <v>0.60773432545245942</v>
+        <v>0.60446071763330522</v>
       </c>
       <c r="T18">
-        <v>-0.013709090028296983</v>
+        <v>-0.013633043517223775</v>
       </c>
       <c r="U18">
-        <v>-0.0092400807157559939</v>
+        <v>-0.0097206512344520934</v>
       </c>
       <c r="V18">
-        <v>0.030252960912053872</v>
+        <v>0.032436071038740355</v>
       </c>
       <c r="W18">
-        <v>-0.00010576026182667481</v>
+        <v>-0.00015400052114487861</v>
       </c>
       <c r="X18">
-        <v>0.0070014699385234636</v>
+        <v>0.0081120713351028328</v>
       </c>
       <c r="Y18">
-        <v>-6.7111948568140321</v>
+        <v>-6.6777651451385935</v>
       </c>
     </row>
     <row r="19">
@@ -9238,76 +9238,76 @@
         <v>138</v>
       </c>
       <c r="B19">
-        <v>-0.18088968169257946</v>
+        <v>-0.18044622342089697</v>
       </c>
       <c r="C19">
-        <v>2.9912850119951391e-005</v>
+        <v>2.9590155677698295e-005</v>
       </c>
       <c r="D19">
-        <v>5.5729989433851461e-005</v>
+        <v>9.288503751423376e-005</v>
       </c>
       <c r="E19">
-        <v>-1.8853098154217488e-006</v>
+        <v>-2.7915235999184802e-006</v>
       </c>
       <c r="F19">
-        <v>8.0000970881053714e-005</v>
+        <v>7.5322762958819232e-005</v>
       </c>
       <c r="G19">
-        <v>9.0725994229884344e-005</v>
+        <v>8.9900913539709987e-005</v>
       </c>
       <c r="H19">
-        <v>-0.00056733673457738285</v>
+        <v>-0.00062280729808751828</v>
       </c>
       <c r="I19">
-        <v>-0.00041528945465330519</v>
+        <v>-0.00048205370469504779</v>
       </c>
       <c r="J19">
-        <v>-0.00052865368694297128</v>
+        <v>-0.00057439260828632817</v>
       </c>
       <c r="K19">
-        <v>-0.00053212764160620954</v>
+        <v>-0.00057677497640197116</v>
       </c>
       <c r="L19">
-        <v>-0.00068866092105616321</v>
+        <v>-0.00071712400867475338</v>
       </c>
       <c r="M19">
-        <v>-5.2908483174344883e-005</v>
+        <v>-0.00010307525183994278</v>
       </c>
       <c r="N19">
-        <v>-0.00020350156256729486</v>
+        <v>-0.00024811490074779169</v>
       </c>
       <c r="O19">
-        <v>-0.00039314748309713027</v>
+        <v>-0.00044167153187022715</v>
       </c>
       <c r="P19">
-        <v>-9.7557914157508224e-006</v>
+        <v>-1.0019389218519231e-005</v>
       </c>
       <c r="Q19">
-        <v>-5.0231260278373399e-005</v>
+        <v>-8.034866936091046e-005</v>
       </c>
       <c r="R19">
-        <v>5.1019890994033999e-005</v>
+        <v>-0.00026268848278208738</v>
       </c>
       <c r="S19">
-        <v>-0.013709090028296983</v>
+        <v>-0.013633043517223775</v>
       </c>
       <c r="T19">
-        <v>0.00031036415151676055</v>
+        <v>0.00030859299048630138</v>
       </c>
       <c r="U19">
-        <v>0.0001908918422132283</v>
+        <v>0.00020038925701834631</v>
       </c>
       <c r="V19">
-        <v>-0.00070714040080213647</v>
+        <v>-0.00075452978980487806</v>
       </c>
       <c r="W19">
-        <v>1.321692517463279e-006</v>
+        <v>2.4118359807592414e-006</v>
       </c>
       <c r="X19">
-        <v>-0.00019105575061935387</v>
+        <v>-0.00021563409452170224</v>
       </c>
       <c r="Y19">
-        <v>0.1509240414534947</v>
+        <v>0.15014770985655335</v>
       </c>
     </row>
     <row r="20">
@@ -9315,76 +9315,76 @@
         <v>139</v>
       </c>
       <c r="B20">
-        <v>-0.36859288968029846</v>
+        <v>-0.38073209252714729</v>
       </c>
       <c r="C20">
-        <v>0.0033195195714538633</v>
+        <v>0.0033523580722680277</v>
       </c>
       <c r="D20">
-        <v>-0.0014954922560221203</v>
+        <v>-0.0025978041191392514</v>
       </c>
       <c r="E20">
-        <v>5.3986813111875914e-005</v>
+        <v>8.0483989365072678e-005</v>
       </c>
       <c r="F20">
-        <v>0.018512791175171919</v>
+        <v>0.018516024929112217</v>
       </c>
       <c r="G20">
-        <v>0.016880002092697272</v>
+        <v>0.017011674573388348</v>
       </c>
       <c r="H20">
-        <v>-0.011962193423956404</v>
+        <v>-0.011726568370736094</v>
       </c>
       <c r="I20">
-        <v>-0.010198393913999355</v>
+        <v>-0.010110711546489289</v>
       </c>
       <c r="J20">
-        <v>-0.010838627257470944</v>
+        <v>-0.010577870784374603</v>
       </c>
       <c r="K20">
-        <v>-0.012131069420982993</v>
+        <v>-0.011938635405631262</v>
       </c>
       <c r="L20">
-        <v>-0.0093549279849892402</v>
+        <v>-0.0089546294075116759</v>
       </c>
       <c r="M20">
-        <v>-0.014301508269201998</v>
+        <v>-0.014131278880868414</v>
       </c>
       <c r="N20">
-        <v>-0.0099240319987185903</v>
+        <v>-0.0096068176260550951</v>
       </c>
       <c r="O20">
-        <v>-0.015591268285219364</v>
+        <v>-0.015516258815562546</v>
       </c>
       <c r="P20">
-        <v>-0.00013697028930906708</v>
+        <v>-0.0001469280205691802</v>
       </c>
       <c r="Q20">
-        <v>-0.003268305613875231</v>
+        <v>-0.0031736795833913144</v>
       </c>
       <c r="R20">
-        <v>0.0032478103691141111</v>
+        <v>0.014214999057012435</v>
       </c>
       <c r="S20">
-        <v>-0.0092400807157559939</v>
+        <v>-0.0097206512344520934</v>
       </c>
       <c r="T20">
-        <v>0.0001908918422132283</v>
+        <v>0.00020038925701834631</v>
       </c>
       <c r="U20">
-        <v>0.046643365933994506</v>
+        <v>0.046752788246883982</v>
       </c>
       <c r="V20">
-        <v>-0.0083360041510639124</v>
+        <v>-0.0080496865271320259</v>
       </c>
       <c r="W20">
-        <v>0.00025449230058852346</v>
+        <v>0.00026055022703139527</v>
       </c>
       <c r="X20">
-        <v>-0.012652953579177624</v>
+        <v>-0.012511365122693172</v>
       </c>
       <c r="Y20">
-        <v>0.094777318271895838</v>
+        <v>0.10026280869634341</v>
       </c>
     </row>
     <row r="21">
@@ -9392,76 +9392,76 @@
         <v>140</v>
       </c>
       <c r="B21">
-        <v>-0.48168257165260159</v>
+        <v>-0.43919223043408767</v>
       </c>
       <c r="C21">
-        <v>-0.00035725022737280844</v>
+        <v>-0.00073223705583846455</v>
       </c>
       <c r="D21">
-        <v>-0.0028276095273021915</v>
+        <v>0.0030527382646219204</v>
       </c>
       <c r="E21">
-        <v>4.3977759216249116e-005</v>
+        <v>-9.8061596233026257e-005</v>
       </c>
       <c r="F21">
-        <v>-0.0022484505412503283</v>
+        <v>-0.0019025985775990538</v>
       </c>
       <c r="G21">
-        <v>-0.0027740734688043792</v>
+        <v>-0.0021052664239159455</v>
       </c>
       <c r="H21">
-        <v>0.03450133792492948</v>
+        <v>0.037729354320394391</v>
       </c>
       <c r="I21">
-        <v>0.033041541897449948</v>
+        <v>0.035814895253189073</v>
       </c>
       <c r="J21">
-        <v>0.032142782782399973</v>
+        <v>0.034867133312834891</v>
       </c>
       <c r="K21">
-        <v>0.032959878803592788</v>
+        <v>0.035779577436945778</v>
       </c>
       <c r="L21">
-        <v>0.032320973386020246</v>
+        <v>0.03478560706395839</v>
       </c>
       <c r="M21">
-        <v>0.03283982377016216</v>
+        <v>0.035239103490789986</v>
       </c>
       <c r="N21">
-        <v>0.032806796201812025</v>
+        <v>0.035516343931734522</v>
       </c>
       <c r="O21">
-        <v>0.032046281910435306</v>
+        <v>0.035651497109209604</v>
       </c>
       <c r="P21">
-        <v>0.00038421132656732654</v>
+        <v>0.00027120307094364053</v>
       </c>
       <c r="Q21">
-        <v>0.0099264511826259328</v>
+        <v>0.011811184389089421</v>
       </c>
       <c r="R21">
-        <v>0.001635877137705688</v>
+        <v>-0.059753856202672873</v>
       </c>
       <c r="S21">
-        <v>0.030252960912053872</v>
+        <v>0.032436071038740355</v>
       </c>
       <c r="T21">
-        <v>-0.00070714040080213647</v>
+        <v>-0.00075452978980487806</v>
       </c>
       <c r="U21">
-        <v>-0.0083360041510639124</v>
+        <v>-0.0080496865271320259</v>
       </c>
       <c r="V21">
-        <v>0.071933491308600828</v>
+        <v>0.074609418614566686</v>
       </c>
       <c r="W21">
-        <v>1.6075309401846047e-005</v>
+        <v>6.0055488597692138e-005</v>
       </c>
       <c r="X21">
-        <v>0.016388442631660262</v>
+        <v>0.017790699499587115</v>
       </c>
       <c r="Y21">
-        <v>-0.35534416664755697</v>
+        <v>-0.38394023251196063</v>
       </c>
     </row>
     <row r="22">
@@ -9469,76 +9469,76 @@
         <v>141</v>
       </c>
       <c r="B22">
-        <v>0.054867534863794483</v>
+        <v>0.055375566550119271</v>
       </c>
       <c r="C22">
-        <v>0.00010480757327048515</v>
+        <v>0.00010134049971374737</v>
       </c>
       <c r="D22">
-        <v>0.0011679829375999609</v>
+        <v>0.0011978923805470907</v>
       </c>
       <c r="E22">
-        <v>-2.8980675775335976e-005</v>
+        <v>-2.967949052247506e-005</v>
       </c>
       <c r="F22">
-        <v>-1.9443095666656004e-005</v>
+        <v>-2.3992212417232617e-005</v>
       </c>
       <c r="G22">
-        <v>-0.0001657032621199118</v>
+        <v>-0.00018134841572720644</v>
       </c>
       <c r="H22">
-        <v>-0.00049062748545745352</v>
+        <v>-0.00044537857244799056</v>
       </c>
       <c r="I22">
-        <v>-0.00019913699048554925</v>
+        <v>-9.0662794942340423e-005</v>
       </c>
       <c r="J22">
-        <v>-0.00024788203587096716</v>
+        <v>-0.00019626035076312815</v>
       </c>
       <c r="K22">
-        <v>-1.2222456203655093e-005</v>
+        <v>4.0034442430125322e-005</v>
       </c>
       <c r="L22">
-        <v>-0.00020811961724100456</v>
+        <v>-0.00015294463312843652</v>
       </c>
       <c r="M22">
-        <v>-0.0003489904910296104</v>
+        <v>-0.00029541989996949649</v>
       </c>
       <c r="N22">
-        <v>2.6074250663096733e-005</v>
+        <v>8.1343278260058113e-005</v>
       </c>
       <c r="O22">
-        <v>-1.9795718969220432e-005</v>
+        <v>2.2033756845692967e-005</v>
       </c>
       <c r="P22">
-        <v>0.0001073898381658414</v>
+        <v>0.00010694134910629394</v>
       </c>
       <c r="Q22">
-        <v>7.0011269185320807e-005</v>
+        <v>7.9269950659934701e-005</v>
       </c>
       <c r="R22">
-        <v>-0.012925219306456161</v>
+        <v>-0.013269077682751323</v>
       </c>
       <c r="S22">
-        <v>-0.00010576026182667481</v>
+        <v>-0.00015400052114487861</v>
       </c>
       <c r="T22">
-        <v>1.321692517463279e-006</v>
+        <v>2.4118359807592414e-006</v>
       </c>
       <c r="U22">
-        <v>0.00025449230058852346</v>
+        <v>0.00026055022703139527</v>
       </c>
       <c r="V22">
-        <v>1.6075309401846047e-005</v>
+        <v>6.0055488597692138e-005</v>
       </c>
       <c r="W22">
-        <v>0.0004373366336180637</v>
+        <v>0.00043673634492668266</v>
       </c>
       <c r="X22">
-        <v>-0.00035953465563758058</v>
+        <v>-0.00036368389521511564</v>
       </c>
       <c r="Y22">
-        <v>-0.004946185645548884</v>
+        <v>-0.0044431365666540434</v>
       </c>
     </row>
     <row r="23">
@@ -9546,76 +9546,76 @@
         <v>142</v>
       </c>
       <c r="B23">
-        <v>-0.17457932899162343</v>
+        <v>-0.16501786126126664</v>
       </c>
       <c r="C23">
-        <v>-0.0011087782332625095</v>
+        <v>-0.0011658801186762392</v>
       </c>
       <c r="D23">
-        <v>-0.0041545232945605932</v>
+        <v>-0.0030309269420318551</v>
       </c>
       <c r="E23">
-        <v>8.8586617717276685e-005</v>
+        <v>6.125105545367205e-005</v>
       </c>
       <c r="F23">
-        <v>0.00011521200843341017</v>
+        <v>0.00038409323747300161</v>
       </c>
       <c r="G23">
-        <v>-0.00043251249552319834</v>
+        <v>0.00010246945497852794</v>
       </c>
       <c r="H23">
-        <v>0.01454310686640483</v>
+        <v>0.016121074389093219</v>
       </c>
       <c r="I23">
-        <v>0.010794361798935927</v>
+        <v>0.012150033359423617</v>
       </c>
       <c r="J23">
-        <v>0.010615858932583887</v>
+        <v>0.011898253088559733</v>
       </c>
       <c r="K23">
-        <v>0.012924704928631259</v>
+        <v>0.014251483715287292</v>
       </c>
       <c r="L23">
-        <v>0.01034789896317604</v>
+        <v>0.011385704159522961</v>
       </c>
       <c r="M23">
-        <v>0.013540596040239088</v>
+        <v>0.014553713465593719</v>
       </c>
       <c r="N23">
-        <v>0.011879991294211613</v>
+        <v>0.013193402409202463</v>
       </c>
       <c r="O23">
-        <v>0.012668443547665482</v>
+        <v>0.014301010019637208</v>
       </c>
       <c r="P23">
-        <v>0.00016211328558497903</v>
+        <v>0.00012158231909279024</v>
       </c>
       <c r="Q23">
-        <v>0.0071875922766534463</v>
+        <v>0.0079680888567978218</v>
       </c>
       <c r="R23">
-        <v>0.031357918407832919</v>
+        <v>0.018837338960273842</v>
       </c>
       <c r="S23">
-        <v>0.0070014699385234636</v>
+        <v>0.0081120713351028328</v>
       </c>
       <c r="T23">
-        <v>-0.00019105575061935387</v>
+        <v>-0.00021563409452170224</v>
       </c>
       <c r="U23">
-        <v>-0.012652953579177624</v>
+        <v>-0.012511365122693172</v>
       </c>
       <c r="V23">
-        <v>0.016388442631660262</v>
+        <v>0.017790699499587115</v>
       </c>
       <c r="W23">
-        <v>-0.00035953465563758058</v>
+        <v>-0.00036368389521511564</v>
       </c>
       <c r="X23">
-        <v>0.034943514619875451</v>
+        <v>0.035658780426996162</v>
       </c>
       <c r="Y23">
-        <v>-0.071672496962146837</v>
+        <v>-0.085751391876631472</v>
       </c>
     </row>
     <row r="24">
@@ -9623,76 +9623,76 @@
         <v>143</v>
       </c>
       <c r="B24">
-        <v>-105.95478992301595</v>
+        <v>-105.77487952399589</v>
       </c>
       <c r="C24">
-        <v>0.024732974339711937</v>
+        <v>0.024774009099340716</v>
       </c>
       <c r="D24">
-        <v>0.07649619665720328</v>
+        <v>0.08845858048279176</v>
       </c>
       <c r="E24">
-        <v>-0.0022888856122253052</v>
+        <v>-0.002577557211566996</v>
       </c>
       <c r="F24">
-        <v>0.031522895658933014</v>
+        <v>0.029603221311972683</v>
       </c>
       <c r="G24">
-        <v>0.040626484403742058</v>
+        <v>0.040302395968057014</v>
       </c>
       <c r="H24">
-        <v>-0.30442195008988482</v>
+        <v>-0.33665197905406075</v>
       </c>
       <c r="I24">
-        <v>-0.22758677465104993</v>
+        <v>-0.26732370303095609</v>
       </c>
       <c r="J24">
-        <v>-0.29984310319552049</v>
+        <v>-0.3270005656427894</v>
       </c>
       <c r="K24">
-        <v>-0.30787287650249034</v>
+        <v>-0.33431064175664543</v>
       </c>
       <c r="L24">
-        <v>-0.35857870759930888</v>
+        <v>-0.37749481175084565</v>
       </c>
       <c r="M24">
-        <v>-0.050034961869197758</v>
+        <v>-0.079891486281387758</v>
       </c>
       <c r="N24">
-        <v>-0.13308490512355586</v>
+        <v>-0.15979253657577508</v>
       </c>
       <c r="O24">
-        <v>-0.21686520544625632</v>
+        <v>-0.24588801049600584</v>
       </c>
       <c r="P24">
-        <v>-0.0066518892006353289</v>
+        <v>-0.0067380919546416868</v>
       </c>
       <c r="Q24">
-        <v>-0.029827105296814704</v>
+        <v>-0.046786919553689334</v>
       </c>
       <c r="R24">
-        <v>-0.36516224868337366</v>
+        <v>-0.45273249912037317</v>
       </c>
       <c r="S24">
-        <v>-6.7111948568140321</v>
+        <v>-6.6777651451385935</v>
       </c>
       <c r="T24">
-        <v>0.1509240414534947</v>
+        <v>0.15014770985655335</v>
       </c>
       <c r="U24">
-        <v>0.094777318271895838</v>
+        <v>0.10026280869634341</v>
       </c>
       <c r="V24">
-        <v>-0.35534416664755697</v>
+        <v>-0.38394023251196063</v>
       </c>
       <c r="W24">
-        <v>-0.004946185645548884</v>
+        <v>-0.0044431365666540434</v>
       </c>
       <c r="X24">
-        <v>-0.071672496962146837</v>
+        <v>-0.085751391876631472</v>
       </c>
       <c r="Y24">
-        <v>74.451738070436477</v>
+        <v>74.116210877097956</v>
       </c>
     </row>
   </sheetData>

--- a/input/reg_education.xlsx
+++ b/input/reg_education.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\andy_local\SimPaths project files\SimPaths\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyFiles\99 DEV ENV\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE5A15D0-A842-4864-870C-A0B96A0384F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC2E87C0-1202-4B0C-A88E-BF9503F22D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="126">
   <si>
     <t>Description:</t>
   </si>
@@ -328,9 +328,6 @@
   </si>
   <si>
     <t>Constant_Medium</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Dag_u22</t>
@@ -2142,9 +2139,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2152,17 +2149,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -2170,7 +2167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -2178,7 +2175,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -2186,7 +2183,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -2194,17 +2191,17 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>13</v>
       </c>
@@ -2221,19 +2218,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="53" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>42</v>
       </c>
@@ -2247,7 +2244,7 @@
         <v>566.14741607222493</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>43</v>
       </c>
@@ -2261,12 +2258,12 @@
         <v>-9832.9118485546423</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="112" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -2280,7 +2277,7 @@
         <v>700.81685105164104</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>43</v>
       </c>
@@ -2294,12 +2291,12 @@
         <v>-3983.6778057276783</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="113" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -2307,7 +2304,7 @@
         <v>0.44601910529091759</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>43</v>
       </c>
@@ -2324,9 +2321,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>16</v>
       </c>
@@ -2403,7 +2400,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>17</v>
       </c>
@@ -2480,7 +2477,7 @@
         <v>-1.0467990983319257E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>18</v>
       </c>
@@ -2557,7 +2554,7 @@
         <v>-0.11408708249946239</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
         <v>19</v>
       </c>
@@ -2634,7 +2631,7 @@
         <v>2.8415250943395398E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5" s="13" t="s">
         <v>20</v>
       </c>
@@ -2711,7 +2708,7 @@
         <v>-6.0677992294312524E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
         <v>21</v>
       </c>
@@ -2788,7 +2785,7 @@
         <v>-1.7015524945483489E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A7" s="17" t="s">
         <v>22</v>
       </c>
@@ -2865,7 +2862,7 @@
         <v>-1.5327863749833069E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A8" s="19" t="s">
         <v>23</v>
       </c>
@@ -2942,7 +2939,7 @@
         <v>-2.3131031216598917E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A9" s="21" t="s">
         <v>24</v>
       </c>
@@ -3019,7 +3016,7 @@
         <v>-2.1396886179511935E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A10" s="23" t="s">
         <v>25</v>
       </c>
@@ -3096,7 +3093,7 @@
         <v>-8.5443346765786917E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A11" s="25" t="s">
         <v>26</v>
       </c>
@@ -3173,7 +3170,7 @@
         <v>-2.6705539023951039E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A12" s="27" t="s">
         <v>27</v>
       </c>
@@ -3250,7 +3247,7 @@
         <v>-2.0491136542521368E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A13" s="29" t="s">
         <v>28</v>
       </c>
@@ -3327,7 +3324,7 @@
         <v>-2.4006673650027086E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A14" s="31" t="s">
         <v>29</v>
       </c>
@@ -3404,7 +3401,7 @@
         <v>-3.1087019318487546E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A15" s="33" t="s">
         <v>30</v>
       </c>
@@ -3481,7 +3478,7 @@
         <v>-2.2224268835616713E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A16" s="35" t="s">
         <v>31</v>
       </c>
@@ -3558,7 +3555,7 @@
         <v>-2.8293279057869311E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A17" s="37" t="s">
         <v>32</v>
       </c>
@@ -3635,7 +3632,7 @@
         <v>-9.7595339758657141E-4</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A18" s="39" t="s">
         <v>33</v>
       </c>
@@ -3712,7 +3709,7 @@
         <v>-1.3352900393857913E-4</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A19" s="41" t="s">
         <v>34</v>
       </c>
@@ -3789,7 +3786,7 @@
         <v>6.6630802387617502E-4</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A20" s="43" t="s">
         <v>35</v>
       </c>
@@ -3866,7 +3863,7 @@
         <v>2.3838481364170743E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A21" s="45" t="s">
         <v>36</v>
       </c>
@@ -3943,7 +3940,7 @@
         <v>-1.3825023746867865E-4</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A22" s="47" t="s">
         <v>37</v>
       </c>
@@ -4020,7 +4017,7 @@
         <v>-2.4197667005215464E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A23" s="49" t="s">
         <v>38</v>
       </c>
@@ -4097,7 +4094,7 @@
         <v>-2.2391558354033282E-4</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A24" s="51" t="s">
         <v>39</v>
       </c>
@@ -4183,9 +4180,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:AD29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A1" s="54" t="s">
         <v>16</v>
       </c>
@@ -4277,7 +4274,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A2" s="56" t="s">
         <v>17</v>
       </c>
@@ -4369,7 +4366,7 @@
         <v>-1.4387676109756361E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A3" s="58" t="s">
         <v>18</v>
       </c>
@@ -4461,7 +4458,7 @@
         <v>-2.6858820714371383E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A4" s="60" t="s">
         <v>19</v>
       </c>
@@ -4553,7 +4550,7 @@
         <v>4.9454712347467983E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A5" s="62" t="s">
         <v>46</v>
       </c>
@@ -4645,7 +4642,7 @@
         <v>-3.1676229425260903E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A6" s="64" t="s">
         <v>47</v>
       </c>
@@ -4737,7 +4734,7 @@
         <v>-2.0123779576044706E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A7" s="66" t="s">
         <v>48</v>
       </c>
@@ -4829,7 +4826,7 @@
         <v>-6.2372033290646551E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A8" s="68" t="s">
         <v>49</v>
       </c>
@@ -4921,7 +4918,7 @@
         <v>-9.560495568672815E-4</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A9" s="70" t="s">
         <v>50</v>
       </c>
@@ -5013,7 +5010,7 @@
         <v>4.1022116317662796E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A10" s="72" t="s">
         <v>20</v>
       </c>
@@ -5105,7 +5102,7 @@
         <v>-2.1589802621188566E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A11" s="74" t="s">
         <v>21</v>
       </c>
@@ -5197,7 +5194,7 @@
         <v>-7.5681472674728294E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A12" s="76" t="s">
         <v>22</v>
       </c>
@@ -5289,7 +5286,7 @@
         <v>-2.8055517791006949E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A13" s="78" t="s">
         <v>23</v>
       </c>
@@ -5381,7 +5378,7 @@
         <v>-5.3261825802646632E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A14" s="80" t="s">
         <v>24</v>
       </c>
@@ -5473,7 +5470,7 @@
         <v>-1.9888358961703922E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A15" s="82" t="s">
         <v>25</v>
       </c>
@@ -5565,7 +5562,7 @@
         <v>-7.2268150820662411E-4</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A16" s="84" t="s">
         <v>26</v>
       </c>
@@ -5657,7 +5654,7 @@
         <v>-8.4296130571874951E-4</v>
       </c>
     </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A17" s="86" t="s">
         <v>27</v>
       </c>
@@ -5749,7 +5746,7 @@
         <v>-2.8785844740984046E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A18" s="88" t="s">
         <v>28</v>
       </c>
@@ -5841,7 +5838,7 @@
         <v>-2.8490219925102183E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A19" s="90" t="s">
         <v>29</v>
       </c>
@@ -5933,7 +5930,7 @@
         <v>-9.916339603318787E-4</v>
       </c>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A20" s="92" t="s">
         <v>30</v>
       </c>
@@ -6025,7 +6022,7 @@
         <v>-3.7060621689632292E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A21" s="94" t="s">
         <v>31</v>
       </c>
@@ -6117,7 +6114,7 @@
         <v>-7.3779384077685122E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A22" s="96" t="s">
         <v>32</v>
       </c>
@@ -6209,7 +6206,7 @@
         <v>-6.6681468687801318E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A23" s="98" t="s">
         <v>33</v>
       </c>
@@ -6301,7 +6298,7 @@
         <v>-1.7571635609555259E-4</v>
       </c>
     </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A24" s="100" t="s">
         <v>34</v>
       </c>
@@ -6393,7 +6390,7 @@
         <v>3.2530918479361376E-4</v>
       </c>
     </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A25" s="102" t="s">
         <v>35</v>
       </c>
@@ -6485,7 +6482,7 @@
         <v>9.0846738452928996E-4</v>
       </c>
     </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A26" s="104" t="s">
         <v>36</v>
       </c>
@@ -6577,7 +6574,7 @@
         <v>4.4105267956745364E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A27" s="106" t="s">
         <v>37</v>
       </c>
@@ -6669,7 +6666,7 @@
         <v>-9.3338449295081861E-4</v>
       </c>
     </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A28" s="108" t="s">
         <v>38</v>
       </c>
@@ -6761,7 +6758,7 @@
         <v>-5.4727146642710419E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A29" s="110" t="s">
         <v>39</v>
       </c>
@@ -6862,12 +6859,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{962FC46F-F678-4370-89CF-42AD800BEEA3}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:C89"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="114"/>
+    <col min="1" max="16384" width="9.1796875" style="114"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="114" t="s">
         <v>53</v>
       </c>
@@ -6878,7 +6875,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="114" t="s">
         <v>54</v>
       </c>
@@ -6889,7 +6886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="114" t="s">
         <v>54</v>
       </c>
@@ -6900,73 +6897,73 @@
         <v>-0.23868295427208672</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="114" t="s">
         <v>54</v>
       </c>
       <c r="B4" s="114" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C4" s="114">
         <v>26.459841778617882</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="114" t="s">
         <v>54</v>
       </c>
       <c r="B5" s="114" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C5" s="114">
         <v>-1.3476078694993459</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="114" t="s">
         <v>54</v>
       </c>
       <c r="B6" s="114" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C6" s="114">
         <v>2.3239543426083493E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="114" t="s">
         <v>54</v>
       </c>
       <c r="B7" s="114" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C7" s="114">
         <v>22.258993025125015</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="114" t="s">
         <v>54</v>
       </c>
       <c r="B8" s="114" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" s="114">
         <v>-0.92890188090335912</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="114" t="s">
         <v>54</v>
       </c>
       <c r="B9" s="114" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C9" s="114">
         <v>1.2879646182220098E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="114" t="s">
         <v>54</v>
       </c>
@@ -6977,7 +6974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="114" t="s">
         <v>54</v>
       </c>
@@ -6988,7 +6985,7 @@
         <v>-0.17411400651395767</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="114" t="s">
         <v>54</v>
       </c>
@@ -6999,7 +6996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="114" t="s">
         <v>54</v>
       </c>
@@ -7010,7 +7007,7 @@
         <v>-1.2828357162376567</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="114" t="s">
         <v>54</v>
       </c>
@@ -7021,7 +7018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="114" t="s">
         <v>54</v>
       </c>
@@ -7032,7 +7029,7 @@
         <v>-0.37766437024811178</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="114" t="s">
         <v>54</v>
       </c>
@@ -7043,7 +7040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="114" t="s">
         <v>54</v>
       </c>
@@ -7054,7 +7051,7 @@
         <v>-9.5634170684743169E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="114" t="s">
         <v>54</v>
       </c>
@@ -7065,7 +7062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="114" t="s">
         <v>54</v>
       </c>
@@ -7076,7 +7073,7 @@
         <v>-0.20313297212548728</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="114" t="s">
         <v>54</v>
       </c>
@@ -7087,7 +7084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="114" t="s">
         <v>54</v>
       </c>
@@ -7098,7 +7095,7 @@
         <v>-0.10526151803175728</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="114" t="s">
         <v>54</v>
       </c>
@@ -7109,7 +7106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="114" t="s">
         <v>54</v>
       </c>
@@ -7120,7 +7117,7 @@
         <v>-0.23558454346527694</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="114" t="s">
         <v>54</v>
       </c>
@@ -7131,7 +7128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="114" t="s">
         <v>54</v>
       </c>
@@ -7142,7 +7139,7 @@
         <v>0.16291931518420413</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="114" t="s">
         <v>54</v>
       </c>
@@ -7153,7 +7150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="114" t="s">
         <v>54</v>
       </c>
@@ -7164,7 +7161,7 @@
         <v>0.26901710732480755</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="114" t="s">
         <v>54</v>
       </c>
@@ -7175,7 +7172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="114" t="s">
         <v>54</v>
       </c>
@@ -7186,7 +7183,7 @@
         <v>3.4167211013976851E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="114" t="s">
         <v>54</v>
       </c>
@@ -7197,7 +7194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="114" t="s">
         <v>54</v>
       </c>
@@ -7208,7 +7205,7 @@
         <v>-0.47641471219977505</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="114" t="s">
         <v>54</v>
       </c>
@@ -7219,7 +7216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="114" t="s">
         <v>54</v>
       </c>
@@ -7230,7 +7227,7 @@
         <v>0.79483330030527444</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="114" t="s">
         <v>54</v>
       </c>
@@ -7241,7 +7238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="114" t="s">
         <v>54</v>
       </c>
@@ -7252,7 +7249,7 @@
         <v>-0.69491708221588244</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="114" t="s">
         <v>54</v>
       </c>
@@ -7263,7 +7260,7 @@
         <v>-5.6649996868764138E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="114" t="s">
         <v>54</v>
       </c>
@@ -7274,7 +7271,7 @@
         <v>-0.32473808439269847</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="114" t="s">
         <v>54</v>
       </c>
@@ -7285,7 +7282,7 @@
         <v>-2.8881113464886924E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="114" t="s">
         <v>54</v>
       </c>
@@ -7296,7 +7293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="114" t="s">
         <v>54</v>
       </c>
@@ -7307,7 +7304,7 @@
         <v>0.67051128709696939</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="114" t="s">
         <v>54</v>
       </c>
@@ -7318,7 +7315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="114" t="s">
         <v>54</v>
       </c>
@@ -7329,7 +7326,7 @@
         <v>-1.0157682506314987</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="114" t="s">
         <v>54</v>
       </c>
@@ -7340,7 +7337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="114" t="s">
         <v>54</v>
       </c>
@@ -7351,7 +7348,7 @@
         <v>-0.40071161835041108</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="114" t="s">
         <v>54</v>
       </c>
@@ -7362,7 +7359,7 @@
         <v>-170.58366176045175</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="114" t="s">
         <v>90</v>
       </c>
@@ -7373,7 +7370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="114" t="s">
         <v>90</v>
       </c>
@@ -7384,73 +7381,73 @@
         <v>-0.2386829542720868</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="114" t="s">
         <v>90</v>
       </c>
       <c r="B48" s="114" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C48" s="114">
         <v>238.52269879771666</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" s="114" t="s">
         <v>90</v>
       </c>
       <c r="B49" s="114" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C49" s="114">
         <v>-12.773354672279481</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="114" t="s">
         <v>90</v>
       </c>
       <c r="B50" s="114" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C50" s="114">
         <v>0.22857962437800042</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="114" t="s">
         <v>90</v>
       </c>
       <c r="B51" s="114" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C51" s="114">
         <v>190.08207226183538</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="114" t="s">
         <v>90</v>
       </c>
       <c r="B52" s="114" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C52" s="114">
         <v>-8.0532897637274061</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" s="114" t="s">
         <v>90</v>
       </c>
       <c r="B53" s="114" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C53" s="114">
         <v>0.11359149616661558</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" s="114" t="s">
         <v>90</v>
       </c>
@@ -7461,7 +7458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" s="114" t="s">
         <v>90</v>
       </c>
@@ -7472,7 +7469,7 @@
         <v>-0.17411400651395773</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="114" t="s">
         <v>90</v>
       </c>
@@ -7483,7 +7480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="114" t="s">
         <v>90</v>
       </c>
@@ -7494,7 +7491,7 @@
         <v>-0.32618083009238846</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="114" t="s">
         <v>90</v>
       </c>
@@ -7505,7 +7502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="114" t="s">
         <v>90</v>
       </c>
@@ -7516,7 +7513,7 @@
         <v>-0.37766437024811189</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="114" t="s">
         <v>90</v>
       </c>
@@ -7527,7 +7524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" s="114" t="s">
         <v>90</v>
       </c>
@@ -7538,7 +7535,7 @@
         <v>-9.5634170684743197E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="114" t="s">
         <v>90</v>
       </c>
@@ -7549,7 +7546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="114" t="s">
         <v>90</v>
       </c>
@@ -7560,7 +7557,7 @@
         <v>-0.20313297212548734</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" s="114" t="s">
         <v>90</v>
       </c>
@@ -7571,7 +7568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" s="114" t="s">
         <v>90</v>
       </c>
@@ -7582,7 +7579,7 @@
         <v>-0.1052615180317573</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" s="114" t="s">
         <v>90</v>
       </c>
@@ -7593,7 +7590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" s="114" t="s">
         <v>90</v>
       </c>
@@ -7604,7 +7601,7 @@
         <v>-0.23558454346527702</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" s="114" t="s">
         <v>90</v>
       </c>
@@ -7615,7 +7612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" s="114" t="s">
         <v>90</v>
       </c>
@@ -7626,7 +7623,7 @@
         <v>0.16291931518420419</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" s="114" t="s">
         <v>90</v>
       </c>
@@ -7637,7 +7634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" s="114" t="s">
         <v>90</v>
       </c>
@@ -7648,7 +7645,7 @@
         <v>0.26901710732480766</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" s="114" t="s">
         <v>90</v>
       </c>
@@ -7659,7 +7656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" s="114" t="s">
         <v>90</v>
       </c>
@@ -7670,7 +7667,7 @@
         <v>3.416721101397686E-3</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" s="114" t="s">
         <v>90</v>
       </c>
@@ -7681,7 +7678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" s="114" t="s">
         <v>90</v>
       </c>
@@ -7692,7 +7689,7 @@
         <v>-0.47641471219977516</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" s="114" t="s">
         <v>90</v>
       </c>
@@ -7703,7 +7700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" s="114" t="s">
         <v>90</v>
       </c>
@@ -7714,7 +7711,7 @@
         <v>-0.37509446315116929</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" s="114" t="s">
         <v>90</v>
       </c>
@@ -7725,7 +7722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" s="114" t="s">
         <v>90</v>
       </c>
@@ -7736,7 +7733,7 @@
         <v>-0.69491708221588266</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" s="114" t="s">
         <v>90</v>
       </c>
@@ -7747,7 +7744,7 @@
         <v>5.4717204458182303E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" s="114" t="s">
         <v>90</v>
       </c>
@@ -7758,7 +7755,7 @@
         <v>-0.32473808439269858</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" s="114" t="s">
         <v>90</v>
       </c>
@@ -7769,7 +7766,7 @@
         <v>-2.8881113464886931E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" s="114" t="s">
         <v>90</v>
       </c>
@@ -7780,7 +7777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" s="114" t="s">
         <v>90</v>
       </c>
@@ -7791,7 +7788,7 @@
         <v>-0.14574181816141929</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" s="114" t="s">
         <v>90</v>
       </c>
@@ -7802,7 +7799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" s="114" t="s">
         <v>90</v>
       </c>
@@ -7813,7 +7810,7 @@
         <v>-1.0157682506314991</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" s="114" t="s">
         <v>90</v>
       </c>
@@ -7824,7 +7821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" s="114" t="s">
         <v>90</v>
       </c>
@@ -7835,7 +7832,7 @@
         <v>-0.40071161835041119</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" s="114" t="s">
         <v>90</v>
       </c>
@@ -7854,13 +7851,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{208E10C7-3326-4A47-B55B-7B92800FD82B}">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:AF30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AE30"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="114"/>
+    <col min="1" max="16384" width="9.1796875" style="114"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" s="114" t="s">
         <v>16</v>
       </c>
@@ -7868,46 +7865,46 @@
         <v>40</v>
       </c>
       <c r="C1" s="114" t="s">
+        <v>107</v>
+      </c>
+      <c r="D1" s="114" t="s">
         <v>108</v>
       </c>
-      <c r="D1" s="114" t="s">
+      <c r="E1" s="114" t="s">
         <v>109</v>
       </c>
-      <c r="E1" s="114" t="s">
+      <c r="F1" s="114" t="s">
         <v>110</v>
       </c>
-      <c r="F1" s="114" t="s">
+      <c r="G1" s="114" t="s">
         <v>111</v>
       </c>
-      <c r="G1" s="114" t="s">
+      <c r="H1" s="114" t="s">
         <v>112</v>
       </c>
-      <c r="H1" s="114" t="s">
+      <c r="I1" s="114" t="s">
         <v>113</v>
       </c>
-      <c r="I1" s="114" t="s">
+      <c r="J1" s="114" t="s">
         <v>114</v>
-      </c>
-      <c r="J1" s="114" t="s">
-        <v>115</v>
       </c>
       <c r="K1" s="114" t="s">
         <v>91</v>
       </c>
       <c r="L1" s="114" t="s">
+        <v>115</v>
+      </c>
+      <c r="M1" s="114" t="s">
         <v>116</v>
       </c>
-      <c r="M1" s="114" t="s">
+      <c r="N1" s="114" t="s">
         <v>117</v>
       </c>
-      <c r="N1" s="114" t="s">
+      <c r="O1" s="114" t="s">
         <v>118</v>
       </c>
-      <c r="O1" s="114" t="s">
+      <c r="P1" s="114" t="s">
         <v>119</v>
-      </c>
-      <c r="P1" s="114" t="s">
-        <v>120</v>
       </c>
       <c r="Q1" s="114" t="s">
         <v>92</v>
@@ -7922,22 +7919,22 @@
         <v>95</v>
       </c>
       <c r="U1" s="114" t="s">
+        <v>120</v>
+      </c>
+      <c r="V1" s="114" t="s">
         <v>121</v>
       </c>
-      <c r="V1" s="114" t="s">
+      <c r="W1" s="114" t="s">
         <v>122</v>
       </c>
-      <c r="W1" s="114" t="s">
+      <c r="X1" s="114" t="s">
         <v>123</v>
       </c>
-      <c r="X1" s="114" t="s">
+      <c r="Y1" s="114" t="s">
         <v>124</v>
       </c>
-      <c r="Y1" s="114" t="s">
+      <c r="Z1" s="114" t="s">
         <v>125</v>
-      </c>
-      <c r="Z1" s="114" t="s">
-        <v>126</v>
       </c>
       <c r="AA1" s="114" t="s">
         <v>96</v>
@@ -7954,13 +7951,10 @@
       <c r="AE1" s="114" t="s">
         <v>100</v>
       </c>
-      <c r="AF1" s="114" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" s="114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B2" s="114">
         <v>-0.23868295427208672</v>
@@ -8053,9 +8047,9 @@
         <v>-0.90126743958671085</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" s="114" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B3" s="114">
         <v>26.459841778617882</v>
@@ -8148,9 +8142,9 @@
         <v>-245.31006325448107</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" s="114" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B4" s="114">
         <v>-1.3476078694993459</v>
@@ -8243,9 +8237,9 @@
         <v>13.454425185126183</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5" s="114" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B5" s="114">
         <v>2.3239543426083493E-2</v>
@@ -8338,9 +8332,9 @@
         <v>-0.24548433246276602</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6" s="114" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B6" s="114">
         <v>22.258993025125015</v>
@@ -8433,9 +8427,9 @@
         <v>-138.80647299867269</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7" s="114" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B7" s="114">
         <v>-0.92890188090335912</v>
@@ -8528,9 +8522,9 @@
         <v>3.5454353769039244</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8" s="114" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B8" s="114">
         <v>1.2879646182220098E-2</v>
@@ -8623,9 +8617,9 @@
         <v>-1.4222475671751056E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A9" s="114" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B9" s="114">
         <v>-0.17411400651395767</v>
@@ -8718,7 +8712,7 @@
         <v>-1.4654104087213113</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A10" s="114" t="s">
         <v>91</v>
       </c>
@@ -8813,9 +8807,9 @@
         <v>-2.1058176079248483</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A11" s="114" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B11" s="114">
         <v>-0.37766437024811178</v>
@@ -8908,9 +8902,9 @@
         <v>15.300031747279235</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A12" s="114" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B12" s="114">
         <v>-9.5634170684743169E-2</v>
@@ -9003,9 +8997,9 @@
         <v>17.330356638882932</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A13" s="114" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B13" s="114">
         <v>-0.20313297212548728</v>
@@ -9098,9 +9092,9 @@
         <v>18.616755998875476</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A14" s="114" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B14" s="114">
         <v>-0.10526151803175728</v>
@@ -9193,9 +9187,9 @@
         <v>16.110423346387876</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A15" s="114" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B15" s="114">
         <v>-0.23558454346527694</v>
@@ -9288,7 +9282,7 @@
         <v>14.071071214624737</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A16" s="114" t="s">
         <v>92</v>
       </c>
@@ -9383,7 +9377,7 @@
         <v>13.655830730618561</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A17" s="114" t="s">
         <v>93</v>
       </c>
@@ -9478,7 +9472,7 @@
         <v>0.55216794098745936</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A18" s="114" t="s">
         <v>94</v>
       </c>
@@ -9573,7 +9567,7 @@
         <v>3.4097162927709164</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A19" s="114" t="s">
         <v>95</v>
       </c>
@@ -9668,9 +9662,9 @@
         <v>1468.7449203376309</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A20" s="114" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B20" s="114">
         <v>238.52269879771666</v>
@@ -9763,9 +9757,9 @@
         <v>-44263.84064431861</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A21" s="114" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B21" s="114">
         <v>-12.773354672279481</v>
@@ -9858,9 +9852,9 @@
         <v>2292.9957780666882</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A22" s="114" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B22" s="114">
         <v>0.22857962437800042</v>
@@ -9953,9 +9947,9 @@
         <v>-39.497016936162254</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A23" s="114" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B23" s="114">
         <v>190.08207226183538</v>
@@ -10048,9 +10042,9 @@
         <v>-35897.56643436756</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A24" s="114" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B24" s="114">
         <v>-8.0532897637274061</v>
@@ -10143,9 +10137,9 @@
         <v>1508.7051257784478</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A25" s="114" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B25" s="114">
         <v>0.11359149616661558</v>
@@ -10238,7 +10232,7 @@
         <v>-21.090006195394835</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A26" s="114" t="s">
         <v>96</v>
       </c>
@@ -10333,7 +10327,7 @@
         <v>-16.823031628539994</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A27" s="114" t="s">
         <v>97</v>
       </c>
@@ -10428,7 +10422,7 @@
         <v>11.569273454649334</v>
       </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A28" s="114" t="s">
         <v>98</v>
       </c>
@@ -10523,7 +10517,7 @@
         <v>-0.54639740254059177</v>
       </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A29" s="114" t="s">
         <v>99</v>
       </c>
@@ -10618,7 +10612,7 @@
         <v>9.654281193899692</v>
       </c>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A30" s="114" t="s">
         <v>100</v>
       </c>

--- a/input/reg_education.xlsx
+++ b/input/reg_education.xlsx
@@ -1,31 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sonnewald/Desktop/initial_populations/regression_estimates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sonnewald/GitHub/SimPaths/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CDFB166-4C82-274C-9D62-D3D46987D101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B18E78D-894F-2344-A7A5-795ADBC62A24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17700" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17780" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
     <sheet name="Gof" sheetId="2" r:id="rId2"/>
-    <sheet name="UK_E1a" sheetId="3" r:id="rId3"/>
-    <sheet name="UK_E1b" sheetId="4" r:id="rId4"/>
-    <sheet name="UK_E2_raw" sheetId="5" r:id="rId5"/>
-    <sheet name="UK_E2" sheetId="6" r:id="rId6"/>
+    <sheet name="E1a" sheetId="3" r:id="rId3"/>
+    <sheet name="E1b" sheetId="4" r:id="rId4"/>
+    <sheet name="E2_raw" sheetId="5" r:id="rId5"/>
+    <sheet name="E2" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="101">
   <si>
     <t>Description:</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Authors: Patryk Bronka, Justin van de Ven, Daria Popova</t>
   </si>
   <si>
-    <t>Last edit: 19 Jan 2025 DP</t>
+    <t>Last edit: 4 Feb 2025 DP</t>
   </si>
   <si>
     <t>Process:</t>
@@ -166,9 +166,6 @@
   </si>
   <si>
     <t>Constant</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>E1a - Leaving education</t>
@@ -2955,18 +2952,18 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B5">
         <v>4.145040225410257E-2</v>
       </c>
       <c r="E5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F5">
         <v>456.59670628673632</v>
@@ -2974,13 +2971,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B6">
         <v>18155</v>
       </c>
       <c r="E6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F6">
         <v>-7008486.2326722071</v>
@@ -2988,18 +2985,18 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B10">
         <v>0.30750315031588693</v>
       </c>
       <c r="E10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F10">
         <v>3155.2546649037313</v>
@@ -3007,13 +3004,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B11">
         <v>225160</v>
       </c>
       <c r="E11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F11">
         <v>-5581382.5964865042</v>
@@ -3021,12 +3018,12 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="166" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B15">
         <v>0.3066809103140985</v>
@@ -3034,7 +3031,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B16">
         <v>6400</v>
@@ -3047,10 +3044,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AE29"/>
+  <dimension ref="A1:AD29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>17</v>
       </c>
@@ -3141,11 +3138,8 @@
       <c r="AD1" t="s">
         <v>46</v>
       </c>
-      <c r="AE1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -3237,7 +3231,7 @@
         <v>-2.2717717768675171E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -3329,7 +3323,7 @@
         <v>-0.10089183758558462</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -3421,7 +3415,7 @@
         <v>2.4140681021699757E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -3513,7 +3507,7 @@
         <v>2.6347738481708669E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -3605,7 +3599,7 @@
         <v>-7.840117168399767E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -3697,7 +3691,7 @@
         <v>-1.0434244631126785E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -3789,7 +3783,7 @@
         <v>-3.5145797560665742E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -3881,7 +3875,7 @@
         <v>-1.2489214833191348E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -3973,7 +3967,7 @@
         <v>-7.3274440947800334E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -4065,7 +4059,7 @@
         <v>-1.8819820110903329E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -4157,7 +4151,7 @@
         <v>-2.6067456020680141E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -4249,7 +4243,7 @@
         <v>7.9962246274989379E-4</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -4341,7 +4335,7 @@
         <v>2.3029419504215498E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>32</v>
       </c>
@@ -4433,7 +4427,7 @@
         <v>3.4093400236791388E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -5728,10 +5722,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:AF30"/>
+  <dimension ref="A1:AE30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>17</v>
       </c>
@@ -5748,13 +5742,13 @@
         <v>21</v>
       </c>
       <c r="F1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1" t="s">
         <v>53</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>54</v>
-      </c>
-      <c r="H1" t="s">
-        <v>55</v>
       </c>
       <c r="I1" t="s">
         <v>23</v>
@@ -5763,13 +5757,13 @@
         <v>24</v>
       </c>
       <c r="K1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L1" t="s">
         <v>56</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>57</v>
-      </c>
-      <c r="M1" t="s">
-        <v>58</v>
       </c>
       <c r="N1" t="s">
         <v>29</v>
@@ -5825,11 +5819,8 @@
       <c r="AE1" t="s">
         <v>46</v>
       </c>
-      <c r="AF1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -5924,7 +5915,7 @@
         <v>-1.0032220564844792E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -6019,7 +6010,7 @@
         <v>-7.6233553036842002E-4</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -6114,9 +6105,9 @@
         <v>8.7702234651593568E-6</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B5">
         <v>-0.19599865116342913</v>
@@ -6209,9 +6200,9 @@
         <v>8.2181491536342842E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B6">
         <v>5.9402158401511161E-2</v>
@@ -6304,9 +6295,9 @@
         <v>-2.1742023112397094E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B7">
         <v>-0.36804568524804571</v>
@@ -6399,7 +6390,7 @@
         <v>5.415636247217406E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -6494,7 +6485,7 @@
         <v>-1.8135734014951676E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -6589,9 +6580,9 @@
         <v>-2.478805968133446E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B10">
         <v>0.23884140819754321</v>
@@ -6684,9 +6675,9 @@
         <v>-4.9187777597450182E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B11">
         <v>8.0210600923109387E-2</v>
@@ -6779,9 +6770,9 @@
         <v>-1.0102693993953256E-4</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B12">
         <v>-0.27985803329838127</v>
@@ -6874,7 +6865,7 @@
         <v>-7.3647641855751906E-4</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -6969,7 +6960,7 @@
         <v>-4.2027541341126849E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -7064,7 +7055,7 @@
         <v>-2.4776886564612383E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -7159,7 +7150,7 @@
         <v>-2.4012043788536322E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -8596,7 +8587,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>17</v>
@@ -8607,10 +8598,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C2" s="12">
         <v>0</v>
@@ -8618,10 +8609,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C3" s="15">
         <v>-0.70604775962035093</v>
@@ -8629,7 +8620,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B4" s="17" t="s">
         <v>20</v>
@@ -8640,7 +8631,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B5" s="20" t="s">
         <v>21</v>
@@ -8651,10 +8642,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="22" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C6" s="24">
         <v>0</v>
@@ -8662,10 +8653,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C7" s="27">
         <v>-0.31380795560927338</v>
@@ -8673,10 +8664,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="28" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C8" s="30">
         <v>0</v>
@@ -8684,10 +8675,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="31" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C9" s="33">
         <v>-1.1156526501060477</v>
@@ -8695,7 +8686,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="34" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B10" s="35" t="s">
         <v>29</v>
@@ -8706,7 +8697,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="37" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B11" s="38" t="s">
         <v>30</v>
@@ -8717,7 +8708,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B12" s="41" t="s">
         <v>31</v>
@@ -8728,7 +8719,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="43" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B13" s="44" t="s">
         <v>32</v>
@@ -8739,7 +8730,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="46" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B14" s="47" t="s">
         <v>33</v>
@@ -8750,7 +8741,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="49" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B15" s="50" t="s">
         <v>34</v>
@@ -8761,7 +8752,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="52" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B16" s="53" t="s">
         <v>35</v>
@@ -8772,7 +8763,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="55" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B17" s="56" t="s">
         <v>36</v>
@@ -8783,7 +8774,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="58" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B18" s="59" t="s">
         <v>37</v>
@@ -8794,7 +8785,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="61" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B19" s="62" t="s">
         <v>38</v>
@@ -8805,7 +8796,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="64" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B20" s="65" t="s">
         <v>39</v>
@@ -8816,7 +8807,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="67" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B21" s="68" t="s">
         <v>40</v>
@@ -8827,7 +8818,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="70" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B22" s="71" t="s">
         <v>41</v>
@@ -8838,7 +8829,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="73" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B23" s="74" t="s">
         <v>42</v>
@@ -8849,7 +8840,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="76" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B24" s="77" t="s">
         <v>43</v>
@@ -8860,7 +8851,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="79" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B25" s="80" t="s">
         <v>44</v>
@@ -8871,7 +8862,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="82" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B26" s="83" t="s">
         <v>45</v>
@@ -8882,10 +8873,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="85" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B27" s="86" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C27" s="87">
         <v>-5.39669304173092</v>
@@ -8893,10 +8884,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="88" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" s="89" t="s">
         <v>61</v>
-      </c>
-      <c r="B28" s="89" t="s">
-        <v>62</v>
       </c>
       <c r="C28" s="90">
         <v>0</v>
@@ -8904,10 +8895,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="91" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B29" s="92" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C29" s="93">
         <v>9.3367855642362108E-2</v>
@@ -8915,7 +8906,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="94" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B30" s="95" t="s">
         <v>20</v>
@@ -8926,7 +8917,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="97" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B31" s="98" t="s">
         <v>21</v>
@@ -8937,10 +8928,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="100" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B32" s="101" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C32" s="102">
         <v>0</v>
@@ -8948,10 +8939,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="103" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B33" s="104" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C33" s="105">
         <v>-0.31380795560927338</v>
@@ -8959,10 +8950,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="106" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B34" s="107" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C34" s="108">
         <v>0</v>
@@ -8970,10 +8961,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="109" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B35" s="110" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C35" s="111">
         <v>-1.1156526501060477</v>
@@ -8981,7 +8972,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="112" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B36" s="113" t="s">
         <v>29</v>
@@ -8992,7 +8983,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="115" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B37" s="116" t="s">
         <v>30</v>
@@ -9003,7 +8994,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="118" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B38" s="119" t="s">
         <v>31</v>
@@ -9014,7 +9005,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" s="121" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B39" s="122" t="s">
         <v>32</v>
@@ -9025,7 +9016,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" s="124" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B40" s="125" t="s">
         <v>33</v>
@@ -9036,7 +9027,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" s="127" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B41" s="128" t="s">
         <v>34</v>
@@ -9047,7 +9038,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" s="130" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B42" s="131" t="s">
         <v>35</v>
@@ -9058,7 +9049,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" s="133" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B43" s="134" t="s">
         <v>36</v>
@@ -9069,7 +9060,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" s="136" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B44" s="137" t="s">
         <v>37</v>
@@ -9080,7 +9071,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" s="139" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B45" s="140" t="s">
         <v>38</v>
@@ -9091,7 +9082,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="142" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B46" s="143" t="s">
         <v>39</v>
@@ -9102,7 +9093,7 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" s="145" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B47" s="146" t="s">
         <v>40</v>
@@ -9113,7 +9104,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="148" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B48" s="149" t="s">
         <v>41</v>
@@ -9124,7 +9115,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="151" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B49" s="152" t="s">
         <v>42</v>
@@ -9135,7 +9126,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" s="154" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B50" s="155" t="s">
         <v>43</v>
@@ -9146,7 +9137,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" s="157" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B51" s="158" t="s">
         <v>44</v>
@@ -9157,7 +9148,7 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" s="160" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B52" s="161" t="s">
         <v>45</v>
@@ -9168,10 +9159,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" s="163" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B53" s="164" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C53" s="165">
         <v>-17.725972754028831</v>
@@ -9184,10 +9175,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:AH32"/>
+  <dimension ref="A1:AG32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>17</v>
       </c>
@@ -9195,105 +9186,102 @@
         <v>18</v>
       </c>
       <c r="C1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" t="s">
         <v>70</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>71</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>72</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>73</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>74</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>75</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>76</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>77</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>78</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>79</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>80</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>81</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>82</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>83</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>84</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>85</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>86</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>87</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>88</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>89</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>90</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>91</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>92</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>93</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>94</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>95</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>96</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>97</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>98</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>99</v>
       </c>
-      <c r="AG1" t="s">
-        <v>100</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B2">
         <v>-0.70604775962035093</v>
@@ -9392,9 +9380,9 @@
         <v>-5.3496866870877706E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B3">
         <v>0.70639883274178095</v>
@@ -9493,9 +9481,9 @@
         <v>-1.6717254660178656E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B4">
         <v>-9.20562429445697E-3</v>
@@ -9594,9 +9582,9 @@
         <v>2.1321632366227592E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B5">
         <v>-0.31380795560927338</v>
@@ -9695,9 +9683,9 @@
         <v>-1.0048907988433754E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B6">
         <v>-1.1156526501060477</v>
@@ -9796,9 +9784,9 @@
         <v>-6.5937624624882243E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B7">
         <v>-0.3611760335691413</v>
@@ -9897,9 +9885,9 @@
         <v>-1.8620788604037944E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B8">
         <v>-0.22038733440661432</v>
@@ -9998,9 +9986,9 @@
         <v>-2.1924504286460256E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B9">
         <v>0.27107102802396599</v>
@@ -10099,9 +10087,9 @@
         <v>-1.8973851946582687E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B10">
         <v>6.5901238322783634E-2</v>
@@ -10200,9 +10188,9 @@
         <v>-2.3664924661106923E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B11">
         <v>-1.439392561915008E-2</v>
@@ -10301,9 +10289,9 @@
         <v>-1.643614103668968E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B12">
         <v>9.3572140470573051E-2</v>
@@ -10402,9 +10390,9 @@
         <v>-2.2171734045420388E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B13">
         <v>0.11102301602483824</v>
@@ -10503,9 +10491,9 @@
         <v>-2.6400931472742056E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B14">
         <v>-0.20412902037797981</v>
@@ -10604,9 +10592,9 @@
         <v>-2.052721315022607E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B15">
         <v>-0.24306085224073692</v>
@@ -10705,9 +10693,9 @@
         <v>-2.0136955799613956E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B16">
         <v>0.64271644433694763</v>
@@ -10808,7 +10796,7 @@
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B17">
         <v>-0.70660743722157748</v>
@@ -10909,7 +10897,7 @@
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B18">
         <v>-4.2735229075933502E-2</v>
@@ -11010,7 +10998,7 @@
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B19">
         <v>-4.1998158232227467E-2</v>
@@ -11111,7 +11099,7 @@
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B20">
         <v>-4.478692814359247E-3</v>
@@ -11212,7 +11200,7 @@
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B21">
         <v>0.46052189955155354</v>
@@ -11313,7 +11301,7 @@
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B22">
         <v>-0.86946174215858618</v>
@@ -11414,7 +11402,7 @@
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B23">
         <v>-0.15980987143476788</v>
@@ -11515,7 +11503,7 @@
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B24">
         <v>-5.39669304173092</v>
@@ -11616,7 +11604,7 @@
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B25">
         <v>9.3367855642362108E-2</v>
@@ -11717,7 +11705,7 @@
     </row>
     <row r="26" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B26">
         <v>1.1140040647338469</v>
@@ -11818,7 +11806,7 @@
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B27">
         <v>-1.4477547084165675E-2</v>
@@ -11919,7 +11907,7 @@
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B28">
         <v>-0.47093949240012567</v>
@@ -12020,7 +12008,7 @@
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B29">
         <v>-0.71099544017905181</v>
@@ -12121,7 +12109,7 @@
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B30">
         <v>-9.8574098714366107E-2</v>
@@ -12222,7 +12210,7 @@
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B31">
         <v>2.5003063976162004E-2</v>
@@ -12323,7 +12311,7 @@
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B32">
         <v>-17.725972754028831</v>
